--- a/Templates/ketquadokiem_template1.xlsx
+++ b/Templates/ketquadokiem_template1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\TESMEA_TMS\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\source\repos\TESMEA_TMS\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6E60BA-3B22-4CA2-9511-59EBA3B8B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC62C33-FBB7-4151-B73D-0CACDE02C464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{067E25EF-8C5C-4BC1-9454-113A69F7CA1E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="1" activeTab="1" xr2:uid="{067E25EF-8C5C-4BC1-9454-113A69F7CA1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Form" sheetId="5" state="hidden" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Sheet2" sheetId="3" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="hinhanh">Calculation!$A$6:$F$14</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">Calculation!$B$58</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">2</definedName>
@@ -1756,10 +1757,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="60">
     <font>
@@ -2544,7 +2546,7 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="52" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2703,7 +2705,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2743,19 +2744,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="7" borderId="18" xfId="3" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2833,37 +2825,15 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="4" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="4" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="4" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="53" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="7" borderId="2" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2889,25 +2859,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3078,6 +3036,9 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3138,9 +3099,6 @@
     <xf numFmtId="0" fontId="34" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3185,6 +3143,64 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="7" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -18273,24 +18289,24 @@
   <sheetData>
     <row r="1" spans="2:7" ht="16.5" thickBot="1"/>
     <row r="2" spans="2:7" ht="30.75" customHeight="1">
-      <c r="B2" s="128" t="s">
+      <c r="B2" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="129"/>
+      <c r="C2" s="117"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7">
-      <c r="B3" s="130"/>
-      <c r="C3" s="131"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="119"/>
     </row>
     <row r="4" spans="2:7">
-      <c r="B4" s="134" t="s">
+      <c r="B4" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="135"/>
+      <c r="C4" s="123"/>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="4" t="s">
@@ -18311,10 +18327,10 @@
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="133"/>
+      <c r="C8" s="121"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="4" t="s">
@@ -18341,10 +18357,10 @@
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="2:7">
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="133"/>
+      <c r="C13" s="121"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="4" t="s">
@@ -18449,31 +18465,31 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="141" t="s">
+      <c r="A4" s="124" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="141"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="141"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="69" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="70"/>
+      <c r="A6" s="69"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" thickBot="1">
-      <c r="A7" s="70"/>
+      <c r="A7" s="69"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" thickBot="1">
-      <c r="A8" s="70"/>
-      <c r="G8" s="105"/>
+      <c r="A8" s="69"/>
+      <c r="G8" s="101"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" thickBot="1">
       <c r="G9" t="s">
@@ -18481,7 +18497,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" thickBot="1">
-      <c r="G10" s="85"/>
+      <c r="G10" s="82"/>
     </row>
     <row r="11" spans="1:8">
       <c r="G11" t="s">
@@ -18489,1414 +18505,1521 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="142" t="s">
+      <c r="A15" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="142"/>
-      <c r="C15" s="142"/>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="142"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="77" t="s">
+      <c r="A17" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
     </row>
     <row r="18" spans="1:20" ht="24" customHeight="1" thickBot="1">
-      <c r="A18" s="143" t="s">
+      <c r="A18" s="127" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="143"/>
-      <c r="C18" s="143"/>
-      <c r="D18" s="143"/>
-      <c r="E18" s="143"/>
-      <c r="F18" s="143"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="143"/>
-      <c r="I18" s="143"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="127"/>
     </row>
     <row r="19" spans="1:20" ht="16.5" thickBot="1">
       <c r="A19" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="106"/>
+      <c r="D19" s="102"/>
       <c r="E19" t="s">
         <v>197</v>
       </c>
-      <c r="H19" s="109"/>
+      <c r="H19" s="105"/>
     </row>
     <row r="20" spans="1:20" ht="16.5" thickBot="1">
       <c r="A20" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="106"/>
+      <c r="D20" s="102"/>
       <c r="E20" t="s">
         <v>1</v>
       </c>
-      <c r="H20" s="106"/>
+      <c r="H20" s="102"/>
     </row>
     <row r="21" spans="1:20" ht="16.5" thickBot="1">
       <c r="A21" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="107"/>
+      <c r="D21" s="103"/>
       <c r="E21" t="s">
         <v>198</v>
       </c>
-      <c r="H21" s="109"/>
+      <c r="H21" s="105"/>
     </row>
     <row r="22" spans="1:20" ht="16.5" thickBot="1">
-      <c r="A22" s="80" t="s">
+      <c r="A22" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="79"/>
+      <c r="H22" s="78"/>
     </row>
     <row r="23" spans="1:20" ht="16.5" thickBot="1">
       <c r="A23" t="s">
         <v>126</v>
       </c>
-      <c r="D23" s="106"/>
+      <c r="D23" s="102"/>
       <c r="E23" t="s">
         <v>183</v>
       </c>
-      <c r="H23" s="106"/>
+      <c r="H23" s="102"/>
     </row>
     <row r="24" spans="1:20" ht="16.5" thickBot="1">
       <c r="A24" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="106"/>
+      <c r="D24" s="102"/>
       <c r="E24" t="s">
         <v>184</v>
       </c>
-      <c r="H24" s="106"/>
+      <c r="H24" s="102"/>
     </row>
     <row r="25" spans="1:20" ht="16.5" thickBot="1">
       <c r="A25" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="106"/>
+      <c r="D25" s="102"/>
       <c r="E25" t="s">
         <v>185</v>
       </c>
-      <c r="H25" s="106"/>
+      <c r="H25" s="102"/>
     </row>
     <row r="26" spans="1:20" ht="16.5" thickBot="1">
       <c r="A26" t="s">
         <v>215</v>
       </c>
-      <c r="D26" s="106"/>
+      <c r="D26" s="102"/>
       <c r="E26" t="s">
         <v>199</v>
       </c>
-      <c r="H26" s="108"/>
+      <c r="H26" s="104"/>
     </row>
     <row r="28" spans="1:20" ht="29.25" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="57" customHeight="1">
-      <c r="A29" s="137" t="s">
+    <row r="29" spans="1:20" s="68" customFormat="1" ht="57" customHeight="1">
+      <c r="A29" s="219" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="137"/>
-      <c r="C29" s="118">
+      <c r="B29" s="219"/>
+      <c r="C29" s="220">
         <v>1</v>
       </c>
-      <c r="D29" s="118">
+      <c r="D29" s="220">
         <v>2</v>
       </c>
-      <c r="E29" s="118">
+      <c r="E29" s="220">
         <v>3</v>
       </c>
-      <c r="F29" s="118">
+      <c r="F29" s="220">
         <v>4</v>
       </c>
-      <c r="G29" s="118">
+      <c r="G29" s="220">
         <v>5</v>
       </c>
-      <c r="H29" s="118">
+      <c r="H29" s="220">
         <v>6</v>
       </c>
-      <c r="I29" s="118">
+      <c r="I29" s="220">
         <v>7</v>
       </c>
-      <c r="J29" s="118">
+      <c r="J29" s="220">
         <v>8</v>
       </c>
-      <c r="K29" s="118">
+      <c r="K29" s="220">
         <v>9</v>
       </c>
-      <c r="L29" s="118">
+      <c r="L29" s="220">
         <v>10</v>
       </c>
-      <c r="T29" s="60"/>
-    </row>
-    <row r="30" spans="1:20" ht="15.6" customHeight="1">
-      <c r="A30" s="139" t="s">
+      <c r="T29" s="112"/>
+    </row>
+    <row r="30" spans="1:20" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A30" s="221" t="s">
         <v>229</v>
       </c>
-      <c r="B30" s="140"/>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-    </row>
-    <row r="31" spans="1:20" ht="15.6" customHeight="1">
-      <c r="A31" s="139" t="s">
+      <c r="B30" s="222"/>
+      <c r="C30" s="220"/>
+      <c r="D30" s="220"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="223"/>
+      <c r="G30" s="223"/>
+      <c r="H30" s="220"/>
+      <c r="I30" s="220"/>
+      <c r="J30" s="220"/>
+      <c r="K30" s="220"/>
+      <c r="L30" s="220"/>
+    </row>
+    <row r="31" spans="1:20" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A31" s="221" t="s">
         <v>216</v>
       </c>
-      <c r="B31" s="140"/>
-      <c r="C31" s="118"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="120"/>
-      <c r="G31" s="120"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="118"/>
-      <c r="L31" s="118"/>
-    </row>
-    <row r="32" spans="1:20" ht="15.6" customHeight="1">
-      <c r="A32" s="139" t="s">
+      <c r="B31" s="222"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="220"/>
+      <c r="E31" s="223"/>
+      <c r="F31" s="223"/>
+      <c r="G31" s="223"/>
+      <c r="H31" s="220"/>
+      <c r="I31" s="220"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="220"/>
+      <c r="L31" s="220"/>
+    </row>
+    <row r="32" spans="1:20" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A32" s="221" t="s">
         <v>217</v>
       </c>
-      <c r="B32" s="140"/>
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="120"/>
-      <c r="G32" s="120"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="118"/>
-      <c r="J32" s="118"/>
-      <c r="K32" s="118"/>
-      <c r="L32" s="118"/>
-    </row>
-    <row r="33" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A33" s="139" t="s">
+      <c r="B32" s="222"/>
+      <c r="C32" s="220"/>
+      <c r="D32" s="220"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="223"/>
+      <c r="G32" s="223"/>
+      <c r="H32" s="220"/>
+      <c r="I32" s="220"/>
+      <c r="J32" s="220"/>
+      <c r="K32" s="220"/>
+      <c r="L32" s="220"/>
+    </row>
+    <row r="33" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A33" s="221" t="s">
         <v>218</v>
       </c>
-      <c r="B33" s="140"/>
-      <c r="C33" s="118"/>
-      <c r="D33" s="121"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="120"/>
-      <c r="H33" s="118"/>
-      <c r="I33" s="118"/>
-      <c r="J33" s="118"/>
-      <c r="K33" s="118"/>
-      <c r="L33" s="118"/>
-    </row>
-    <row r="34" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A34" s="139" t="s">
+      <c r="B33" s="222"/>
+      <c r="C33" s="220"/>
+      <c r="D33" s="224"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="223"/>
+      <c r="G33" s="223"/>
+      <c r="H33" s="220"/>
+      <c r="I33" s="220"/>
+      <c r="J33" s="220"/>
+      <c r="K33" s="220"/>
+      <c r="L33" s="220"/>
+    </row>
+    <row r="34" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A34" s="221" t="s">
         <v>219</v>
       </c>
-      <c r="B34" s="140"/>
-      <c r="C34" s="118"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="119"/>
-      <c r="F34" s="120"/>
-      <c r="G34" s="120"/>
-      <c r="H34" s="118"/>
-      <c r="I34" s="118"/>
-      <c r="J34" s="118"/>
-      <c r="K34" s="118"/>
-      <c r="L34" s="118"/>
-    </row>
-    <row r="35" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A35" s="139" t="s">
+      <c r="B34" s="222"/>
+      <c r="C34" s="220"/>
+      <c r="D34" s="220"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="223"/>
+      <c r="H34" s="220"/>
+      <c r="I34" s="220"/>
+      <c r="J34" s="220"/>
+      <c r="K34" s="220"/>
+      <c r="L34" s="220"/>
+    </row>
+    <row r="35" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A35" s="221" t="s">
         <v>220</v>
       </c>
-      <c r="B35" s="140"/>
-      <c r="C35" s="118"/>
-      <c r="D35" s="118"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="120"/>
-      <c r="H35" s="118"/>
-      <c r="I35" s="118"/>
-      <c r="J35" s="118"/>
-      <c r="K35" s="118"/>
-      <c r="L35" s="118"/>
-    </row>
-    <row r="36" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A36" s="139" t="s">
+      <c r="B35" s="222"/>
+      <c r="C35" s="220"/>
+      <c r="D35" s="220"/>
+      <c r="E35" s="223"/>
+      <c r="F35" s="223"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="220"/>
+      <c r="I35" s="220"/>
+      <c r="J35" s="220"/>
+      <c r="K35" s="220"/>
+      <c r="L35" s="220"/>
+    </row>
+    <row r="36" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A36" s="221" t="s">
         <v>221</v>
       </c>
-      <c r="B36" s="140"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="118"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="120"/>
-      <c r="G36" s="120"/>
-      <c r="H36" s="118"/>
-      <c r="I36" s="118"/>
-      <c r="J36" s="118"/>
-      <c r="K36" s="118"/>
-      <c r="L36" s="118"/>
-    </row>
-    <row r="37" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A37" s="139" t="s">
+      <c r="B36" s="222"/>
+      <c r="C36" s="220"/>
+      <c r="D36" s="220"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="220"/>
+      <c r="I36" s="220"/>
+      <c r="J36" s="220"/>
+      <c r="K36" s="220"/>
+      <c r="L36" s="220"/>
+    </row>
+    <row r="37" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A37" s="221" t="s">
         <v>222</v>
       </c>
-      <c r="B37" s="140"/>
-      <c r="C37" s="118"/>
-      <c r="D37" s="118"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="118"/>
-      <c r="I37" s="118"/>
-      <c r="J37" s="118"/>
-      <c r="K37" s="118"/>
-      <c r="L37" s="118"/>
-    </row>
-    <row r="38" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A38" s="139" t="s">
+      <c r="B37" s="222"/>
+      <c r="C37" s="220"/>
+      <c r="D37" s="220"/>
+      <c r="E37" s="223"/>
+      <c r="F37" s="223"/>
+      <c r="G37" s="223"/>
+      <c r="H37" s="220"/>
+      <c r="I37" s="220"/>
+      <c r="J37" s="220"/>
+      <c r="K37" s="220"/>
+      <c r="L37" s="220"/>
+    </row>
+    <row r="38" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A38" s="221" t="s">
         <v>223</v>
       </c>
-      <c r="B38" s="140"/>
-      <c r="C38" s="118"/>
-      <c r="D38" s="118"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="120"/>
-      <c r="G38" s="120"/>
-      <c r="H38" s="118"/>
-      <c r="I38" s="118"/>
-      <c r="J38" s="118"/>
-      <c r="K38" s="118"/>
-      <c r="L38" s="118"/>
-    </row>
-    <row r="39" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A39" s="139" t="s">
+      <c r="B38" s="222"/>
+      <c r="C38" s="220"/>
+      <c r="D38" s="220"/>
+      <c r="E38" s="223"/>
+      <c r="F38" s="223"/>
+      <c r="G38" s="223"/>
+      <c r="H38" s="220"/>
+      <c r="I38" s="220"/>
+      <c r="J38" s="220"/>
+      <c r="K38" s="220"/>
+      <c r="L38" s="220"/>
+    </row>
+    <row r="39" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A39" s="221" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="140"/>
-      <c r="C39" s="118"/>
-      <c r="D39" s="118"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="120"/>
-      <c r="H39" s="118"/>
-      <c r="I39" s="118"/>
-      <c r="J39" s="118"/>
-      <c r="K39" s="118"/>
-      <c r="L39" s="118"/>
-    </row>
-    <row r="40" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A40" s="139" t="s">
+      <c r="B39" s="222"/>
+      <c r="C39" s="220"/>
+      <c r="D39" s="220"/>
+      <c r="E39" s="223"/>
+      <c r="F39" s="223"/>
+      <c r="G39" s="223"/>
+      <c r="H39" s="220"/>
+      <c r="I39" s="220"/>
+      <c r="J39" s="220"/>
+      <c r="K39" s="220"/>
+      <c r="L39" s="220"/>
+    </row>
+    <row r="40" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A40" s="221" t="s">
         <v>225</v>
       </c>
-      <c r="B40" s="140"/>
-      <c r="C40" s="118"/>
-      <c r="D40" s="118"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
-      <c r="G40" s="120"/>
-      <c r="H40" s="118"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="118"/>
-      <c r="K40" s="118"/>
-      <c r="L40" s="118"/>
-    </row>
-    <row r="41" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A41" s="139" t="s">
+      <c r="B40" s="222"/>
+      <c r="C40" s="220"/>
+      <c r="D40" s="220"/>
+      <c r="E40" s="223"/>
+      <c r="F40" s="223"/>
+      <c r="G40" s="223"/>
+      <c r="H40" s="220"/>
+      <c r="I40" s="220"/>
+      <c r="J40" s="220"/>
+      <c r="K40" s="220"/>
+      <c r="L40" s="220"/>
+    </row>
+    <row r="41" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A41" s="221" t="s">
         <v>226</v>
       </c>
-      <c r="B41" s="140"/>
-      <c r="C41" s="118"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="120"/>
-      <c r="G41" s="120"/>
-      <c r="H41" s="118"/>
-      <c r="I41" s="118"/>
-      <c r="J41" s="118"/>
-      <c r="K41" s="118"/>
-      <c r="L41" s="118"/>
-    </row>
-    <row r="42" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A42" s="139" t="s">
+      <c r="B41" s="222"/>
+      <c r="C41" s="220"/>
+      <c r="D41" s="220"/>
+      <c r="E41" s="223"/>
+      <c r="F41" s="223"/>
+      <c r="G41" s="223"/>
+      <c r="H41" s="220"/>
+      <c r="I41" s="220"/>
+      <c r="J41" s="220"/>
+      <c r="K41" s="220"/>
+      <c r="L41" s="220"/>
+    </row>
+    <row r="42" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A42" s="221" t="s">
         <v>227</v>
       </c>
-      <c r="B42" s="140"/>
-      <c r="C42" s="118"/>
-      <c r="D42" s="118"/>
-      <c r="E42" s="119"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="120"/>
-      <c r="H42" s="118"/>
-      <c r="I42" s="118"/>
-      <c r="J42" s="118"/>
-      <c r="K42" s="118"/>
-      <c r="L42" s="118"/>
-    </row>
-    <row r="43" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A43" s="139" t="s">
+      <c r="B42" s="222"/>
+      <c r="C42" s="220"/>
+      <c r="D42" s="220"/>
+      <c r="E42" s="223"/>
+      <c r="F42" s="223"/>
+      <c r="G42" s="223"/>
+      <c r="H42" s="220"/>
+      <c r="I42" s="220"/>
+      <c r="J42" s="220"/>
+      <c r="K42" s="220"/>
+      <c r="L42" s="220"/>
+    </row>
+    <row r="43" spans="1:22" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A43" s="221" t="s">
         <v>228</v>
       </c>
-      <c r="B43" s="140"/>
-      <c r="C43" s="118"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="119"/>
-      <c r="F43" s="120"/>
-      <c r="G43" s="120"/>
-      <c r="H43" s="118"/>
-      <c r="I43" s="118"/>
-      <c r="J43" s="118"/>
-      <c r="K43" s="118"/>
-      <c r="L43" s="118"/>
-    </row>
-    <row r="44" spans="1:22">
-      <c r="A44" s="123"/>
-      <c r="B44" s="123"/>
-      <c r="C44" s="82"/>
-      <c r="D44" s="123"/>
-      <c r="E44" s="123"/>
-      <c r="F44" s="123"/>
-      <c r="G44" s="123"/>
-      <c r="H44" s="123"/>
-    </row>
-    <row r="45" spans="1:22">
-      <c r="A45" s="123"/>
-      <c r="B45" s="123"/>
-      <c r="C45" s="82"/>
-      <c r="D45" s="123"/>
-      <c r="E45" s="123"/>
-      <c r="F45" s="123"/>
-      <c r="G45" s="123"/>
-      <c r="H45" s="123"/>
-    </row>
-    <row r="46" spans="1:22">
-      <c r="A46" s="123"/>
-      <c r="B46" s="123"/>
-      <c r="C46" s="82"/>
-      <c r="D46" s="123"/>
-      <c r="E46" s="123"/>
-      <c r="F46" s="123"/>
-      <c r="G46" s="123"/>
-      <c r="H46" s="123"/>
-    </row>
-    <row r="47" spans="1:22">
-      <c r="A47" s="77" t="s">
+      <c r="B43" s="222"/>
+      <c r="C43" s="220"/>
+      <c r="D43" s="220"/>
+      <c r="E43" s="223"/>
+      <c r="F43" s="223"/>
+      <c r="G43" s="223"/>
+      <c r="H43" s="220"/>
+      <c r="I43" s="220"/>
+      <c r="J43" s="220"/>
+      <c r="K43" s="220"/>
+      <c r="L43" s="220"/>
+    </row>
+    <row r="44" spans="1:22" s="68" customFormat="1">
+      <c r="A44" s="225"/>
+      <c r="B44" s="225"/>
+      <c r="C44" s="226"/>
+      <c r="D44" s="225"/>
+      <c r="E44" s="225"/>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="225"/>
+      <c r="I44" s="227"/>
+      <c r="J44" s="227"/>
+      <c r="K44" s="227"/>
+      <c r="L44" s="227"/>
+    </row>
+    <row r="45" spans="1:22" s="68" customFormat="1">
+      <c r="A45" s="225"/>
+      <c r="B45" s="225"/>
+      <c r="C45" s="226"/>
+      <c r="D45" s="225"/>
+      <c r="E45" s="225"/>
+      <c r="F45" s="225"/>
+      <c r="G45" s="225"/>
+      <c r="H45" s="225"/>
+      <c r="I45" s="227"/>
+      <c r="J45" s="227"/>
+      <c r="K45" s="227"/>
+      <c r="L45" s="227"/>
+    </row>
+    <row r="46" spans="1:22" s="68" customFormat="1">
+      <c r="A46" s="225"/>
+      <c r="B46" s="225"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="225"/>
+      <c r="E46" s="225"/>
+      <c r="F46" s="225"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="227"/>
+      <c r="J46" s="227"/>
+      <c r="K46" s="227"/>
+      <c r="L46" s="227"/>
+    </row>
+    <row r="47" spans="1:22" s="68" customFormat="1">
+      <c r="A47" s="228" t="s">
         <v>230</v>
       </c>
-      <c r="E47" s="61"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="61"/>
-      <c r="J47" s="142"/>
-      <c r="K47" s="142"/>
-      <c r="L47" s="142"/>
-      <c r="M47" s="142"/>
-      <c r="N47" s="142"/>
-      <c r="O47" s="142"/>
-      <c r="P47" s="142"/>
-      <c r="Q47" s="142"/>
-      <c r="R47" s="142"/>
-      <c r="S47" s="142"/>
-      <c r="T47" s="142"/>
-      <c r="U47" s="142"/>
-      <c r="V47" s="142"/>
-    </row>
-    <row r="48" spans="1:22">
-      <c r="A48" s="83" t="s">
+      <c r="B47" s="227"/>
+      <c r="C47" s="227"/>
+      <c r="D47" s="227"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="227"/>
+      <c r="J47" s="229"/>
+      <c r="K47" s="229"/>
+      <c r="L47" s="229"/>
+      <c r="M47" s="126"/>
+      <c r="N47" s="126"/>
+      <c r="O47" s="126"/>
+      <c r="P47" s="126"/>
+      <c r="Q47" s="126"/>
+      <c r="R47" s="126"/>
+      <c r="S47" s="126"/>
+      <c r="T47" s="126"/>
+      <c r="U47" s="126"/>
+      <c r="V47" s="126"/>
+    </row>
+    <row r="48" spans="1:22" s="68" customFormat="1">
+      <c r="A48" s="230" t="s">
         <v>231</v>
       </c>
-      <c r="B48" s="61"/>
-      <c r="C48" s="82"/>
-      <c r="E48" s="61"/>
-      <c r="G48" s="61"/>
-    </row>
-    <row r="49" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A49" s="122" t="s">
+      <c r="B48" s="225"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="227"/>
+      <c r="E48" s="225"/>
+      <c r="F48" s="227"/>
+      <c r="G48" s="225"/>
+      <c r="H48" s="227"/>
+      <c r="I48" s="227"/>
+      <c r="J48" s="227"/>
+      <c r="K48" s="227"/>
+      <c r="L48" s="227"/>
+    </row>
+    <row r="49" spans="1:12" s="68" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A49" s="231" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="122" t="s">
+      <c r="B49" s="231" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="117">
+      <c r="C49" s="232">
         <v>1</v>
       </c>
-      <c r="D49" s="117">
+      <c r="D49" s="232">
         <v>2</v>
       </c>
-      <c r="E49" s="117">
+      <c r="E49" s="232">
         <v>3</v>
       </c>
-      <c r="F49" s="117">
+      <c r="F49" s="232">
         <v>4</v>
       </c>
-      <c r="G49" s="117">
+      <c r="G49" s="232">
         <v>5</v>
       </c>
-      <c r="H49" s="117">
+      <c r="H49" s="232">
         <v>6</v>
       </c>
-      <c r="I49" s="117">
+      <c r="I49" s="232">
         <v>7</v>
       </c>
-      <c r="J49" s="117">
+      <c r="J49" s="232">
         <v>8</v>
       </c>
-      <c r="K49" s="117">
+      <c r="K49" s="232">
         <v>9</v>
       </c>
-      <c r="L49" s="117">
+      <c r="L49" s="232">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="19.149999999999999" customHeight="1">
-      <c r="A50" s="122" t="s">
+    <row r="50" spans="1:12" s="68" customFormat="1" ht="19.149999999999999" customHeight="1">
+      <c r="A50" s="231" t="s">
         <v>129</v>
       </c>
-      <c r="B50" s="126" t="s">
+      <c r="B50" s="233" t="s">
         <v>200</v>
       </c>
-      <c r="C50" s="124"/>
-      <c r="D50" s="124"/>
-      <c r="E50" s="124"/>
-      <c r="F50" s="124"/>
-      <c r="G50" s="124"/>
-      <c r="H50" s="124"/>
-      <c r="I50" s="124"/>
-      <c r="J50" s="124"/>
-      <c r="K50" s="124"/>
-      <c r="L50" s="124"/>
-    </row>
-    <row r="51" spans="1:12" ht="21" customHeight="1">
-      <c r="A51" s="86" t="s">
+      <c r="C50" s="234"/>
+      <c r="D50" s="234"/>
+      <c r="E50" s="234"/>
+      <c r="F50" s="234"/>
+      <c r="G50" s="234"/>
+      <c r="H50" s="234"/>
+      <c r="I50" s="234"/>
+      <c r="J50" s="234"/>
+      <c r="K50" s="234"/>
+      <c r="L50" s="234"/>
+    </row>
+    <row r="51" spans="1:12" s="68" customFormat="1" ht="21" customHeight="1">
+      <c r="A51" s="235" t="s">
         <v>131</v>
       </c>
-      <c r="B51" s="126" t="s">
+      <c r="B51" s="233" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="124"/>
-      <c r="D51" s="124"/>
-      <c r="E51" s="124"/>
-      <c r="F51" s="124"/>
-      <c r="G51" s="124"/>
-      <c r="H51" s="124"/>
-      <c r="I51" s="124"/>
-      <c r="J51" s="124"/>
-      <c r="K51" s="124"/>
-      <c r="L51" s="124"/>
-    </row>
-    <row r="52" spans="1:12" ht="21" customHeight="1">
-      <c r="A52" s="122" t="s">
+      <c r="C51" s="234"/>
+      <c r="D51" s="234"/>
+      <c r="E51" s="234"/>
+      <c r="F51" s="234"/>
+      <c r="G51" s="234"/>
+      <c r="H51" s="234"/>
+      <c r="I51" s="234"/>
+      <c r="J51" s="234"/>
+      <c r="K51" s="234"/>
+      <c r="L51" s="234"/>
+    </row>
+    <row r="52" spans="1:12" s="68" customFormat="1" ht="21" customHeight="1">
+      <c r="A52" s="231" t="s">
         <v>132</v>
       </c>
-      <c r="B52" s="126" t="s">
+      <c r="B52" s="233" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="124"/>
-      <c r="D52" s="124"/>
-      <c r="E52" s="124"/>
-      <c r="F52" s="124"/>
-      <c r="G52" s="124"/>
-      <c r="H52" s="124"/>
-      <c r="I52" s="124"/>
-      <c r="J52" s="124"/>
-      <c r="K52" s="124"/>
-      <c r="L52" s="124"/>
-    </row>
-    <row r="53" spans="1:12" ht="20.45" customHeight="1">
-      <c r="A53" s="122" t="s">
+      <c r="C52" s="234"/>
+      <c r="D52" s="234"/>
+      <c r="E52" s="234"/>
+      <c r="F52" s="234"/>
+      <c r="G52" s="234"/>
+      <c r="H52" s="234"/>
+      <c r="I52" s="234"/>
+      <c r="J52" s="234"/>
+      <c r="K52" s="234"/>
+      <c r="L52" s="234"/>
+    </row>
+    <row r="53" spans="1:12" s="68" customFormat="1" ht="20.45" customHeight="1">
+      <c r="A53" s="231" t="s">
         <v>133</v>
       </c>
-      <c r="B53" s="126" t="s">
+      <c r="B53" s="233" t="s">
         <v>201</v>
       </c>
-      <c r="C53" s="124"/>
-      <c r="D53" s="124"/>
-      <c r="E53" s="124"/>
-      <c r="F53" s="124"/>
-      <c r="G53" s="124"/>
-      <c r="H53" s="124"/>
-      <c r="I53" s="124"/>
-      <c r="J53" s="124"/>
-      <c r="K53" s="124"/>
-      <c r="L53" s="124"/>
-    </row>
-    <row r="54" spans="1:12" ht="25.15" customHeight="1">
-      <c r="A54" s="137" t="s">
+      <c r="C53" s="234"/>
+      <c r="D53" s="234"/>
+      <c r="E53" s="234"/>
+      <c r="F53" s="234"/>
+      <c r="G53" s="234"/>
+      <c r="H53" s="234"/>
+      <c r="I53" s="234"/>
+      <c r="J53" s="234"/>
+      <c r="K53" s="234"/>
+      <c r="L53" s="234"/>
+    </row>
+    <row r="54" spans="1:12" s="68" customFormat="1" ht="25.15" customHeight="1">
+      <c r="A54" s="219" t="s">
         <v>134</v>
       </c>
-      <c r="B54" s="126" t="s">
+      <c r="B54" s="233" t="s">
         <v>212</v>
       </c>
-      <c r="C54" s="124"/>
-      <c r="D54" s="124"/>
-      <c r="E54" s="124"/>
-      <c r="F54" s="124"/>
-      <c r="G54" s="124"/>
-      <c r="H54" s="124"/>
-      <c r="I54" s="124"/>
-      <c r="J54" s="124"/>
-      <c r="K54" s="124"/>
-      <c r="L54" s="124"/>
-    </row>
-    <row r="55" spans="1:12" ht="34.9" customHeight="1">
-      <c r="A55" s="137"/>
-      <c r="B55" s="126" t="s">
+      <c r="C54" s="234"/>
+      <c r="D54" s="234"/>
+      <c r="E54" s="234"/>
+      <c r="F54" s="234"/>
+      <c r="G54" s="234"/>
+      <c r="H54" s="234"/>
+      <c r="I54" s="234"/>
+      <c r="J54" s="234"/>
+      <c r="K54" s="234"/>
+      <c r="L54" s="234"/>
+    </row>
+    <row r="55" spans="1:12" s="68" customFormat="1" ht="34.9" customHeight="1">
+      <c r="A55" s="219"/>
+      <c r="B55" s="233" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="124"/>
-      <c r="D55" s="124"/>
-      <c r="E55" s="124"/>
-      <c r="F55" s="124"/>
-      <c r="G55" s="124"/>
-      <c r="H55" s="124"/>
-      <c r="I55" s="124"/>
-      <c r="J55" s="124"/>
-      <c r="K55" s="124"/>
-      <c r="L55" s="124"/>
-    </row>
-    <row r="56" spans="1:12" ht="34.5" customHeight="1">
-      <c r="A56" s="137"/>
-      <c r="B56" s="126" t="s">
+      <c r="C55" s="234"/>
+      <c r="D55" s="234"/>
+      <c r="E55" s="234"/>
+      <c r="F55" s="234"/>
+      <c r="G55" s="234"/>
+      <c r="H55" s="234"/>
+      <c r="I55" s="234"/>
+      <c r="J55" s="234"/>
+      <c r="K55" s="234"/>
+      <c r="L55" s="234"/>
+    </row>
+    <row r="56" spans="1:12" s="68" customFormat="1" ht="34.5" customHeight="1">
+      <c r="A56" s="219"/>
+      <c r="B56" s="233" t="s">
         <v>202</v>
       </c>
-      <c r="C56" s="124"/>
-      <c r="D56" s="124"/>
-      <c r="E56" s="124"/>
-      <c r="F56" s="124"/>
-      <c r="G56" s="124"/>
-      <c r="H56" s="124"/>
-      <c r="I56" s="124"/>
-      <c r="J56" s="124"/>
-      <c r="K56" s="124"/>
-      <c r="L56" s="124"/>
-    </row>
-    <row r="57" spans="1:12" ht="21.6" customHeight="1">
-      <c r="A57" s="137"/>
-      <c r="B57" s="126" t="s">
+      <c r="C56" s="234"/>
+      <c r="D56" s="234"/>
+      <c r="E56" s="234"/>
+      <c r="F56" s="234"/>
+      <c r="G56" s="234"/>
+      <c r="H56" s="234"/>
+      <c r="I56" s="234"/>
+      <c r="J56" s="234"/>
+      <c r="K56" s="234"/>
+      <c r="L56" s="234"/>
+    </row>
+    <row r="57" spans="1:12" s="68" customFormat="1" ht="21.6" customHeight="1">
+      <c r="A57" s="219"/>
+      <c r="B57" s="233" t="s">
         <v>181</v>
       </c>
-      <c r="C57" s="124"/>
-      <c r="D57" s="124"/>
-      <c r="E57" s="124"/>
-      <c r="F57" s="124"/>
-      <c r="G57" s="124"/>
-      <c r="H57" s="124"/>
-      <c r="I57" s="124"/>
-      <c r="J57" s="124"/>
-      <c r="K57" s="124"/>
-      <c r="L57" s="124"/>
-    </row>
-    <row r="58" spans="1:12" ht="22.9" customHeight="1">
-      <c r="A58" s="122" t="s">
+      <c r="C57" s="234"/>
+      <c r="D57" s="234"/>
+      <c r="E57" s="234"/>
+      <c r="F57" s="234"/>
+      <c r="G57" s="234"/>
+      <c r="H57" s="234"/>
+      <c r="I57" s="234"/>
+      <c r="J57" s="234"/>
+      <c r="K57" s="234"/>
+      <c r="L57" s="234"/>
+    </row>
+    <row r="58" spans="1:12" s="68" customFormat="1" ht="22.9" customHeight="1">
+      <c r="A58" s="231" t="s">
         <v>136</v>
       </c>
-      <c r="B58" s="126" t="s">
+      <c r="B58" s="233" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="124"/>
-      <c r="D58" s="124"/>
-      <c r="E58" s="124"/>
-      <c r="F58" s="124"/>
-      <c r="G58" s="124"/>
-      <c r="H58" s="124"/>
-      <c r="I58" s="124"/>
-      <c r="J58" s="124"/>
-      <c r="K58" s="124"/>
-      <c r="L58" s="124"/>
-    </row>
-    <row r="59" spans="1:12" ht="19.149999999999999" customHeight="1">
-      <c r="A59" s="122" t="s">
+      <c r="C58" s="234"/>
+      <c r="D58" s="234"/>
+      <c r="E58" s="234"/>
+      <c r="F58" s="234"/>
+      <c r="G58" s="234"/>
+      <c r="H58" s="234"/>
+      <c r="I58" s="234"/>
+      <c r="J58" s="234"/>
+      <c r="K58" s="234"/>
+      <c r="L58" s="234"/>
+    </row>
+    <row r="59" spans="1:12" s="68" customFormat="1" ht="19.149999999999999" customHeight="1">
+      <c r="A59" s="231" t="s">
         <v>137</v>
       </c>
-      <c r="B59" s="126" t="s">
+      <c r="B59" s="233" t="s">
         <v>78</v>
       </c>
-      <c r="C59" s="124"/>
-      <c r="D59" s="124"/>
-      <c r="E59" s="124"/>
-      <c r="F59" s="124"/>
-      <c r="G59" s="124"/>
-      <c r="H59" s="124"/>
-      <c r="I59" s="124"/>
-      <c r="J59" s="124"/>
-      <c r="K59" s="124"/>
-      <c r="L59" s="124"/>
-    </row>
-    <row r="60" spans="1:12" ht="18.600000000000001" customHeight="1">
-      <c r="A60" s="122" t="s">
+      <c r="C59" s="234"/>
+      <c r="D59" s="234"/>
+      <c r="E59" s="234"/>
+      <c r="F59" s="234"/>
+      <c r="G59" s="234"/>
+      <c r="H59" s="234"/>
+      <c r="I59" s="234"/>
+      <c r="J59" s="234"/>
+      <c r="K59" s="234"/>
+      <c r="L59" s="234"/>
+    </row>
+    <row r="60" spans="1:12" s="68" customFormat="1" ht="18.600000000000001" customHeight="1">
+      <c r="A60" s="231" t="s">
         <v>138</v>
       </c>
-      <c r="B60" s="126" t="s">
+      <c r="B60" s="233" t="s">
         <v>203</v>
       </c>
-      <c r="C60" s="124"/>
-      <c r="D60" s="124"/>
-      <c r="E60" s="124"/>
-      <c r="F60" s="124"/>
-      <c r="G60" s="124"/>
-      <c r="H60" s="124"/>
-      <c r="I60" s="124"/>
-      <c r="J60" s="124"/>
-      <c r="K60" s="124"/>
-      <c r="L60" s="124"/>
-    </row>
-    <row r="61" spans="1:12">
-      <c r="A61" s="122" t="s">
+      <c r="C60" s="234"/>
+      <c r="D60" s="234"/>
+      <c r="E60" s="234"/>
+      <c r="F60" s="234"/>
+      <c r="G60" s="234"/>
+      <c r="H60" s="234"/>
+      <c r="I60" s="234"/>
+      <c r="J60" s="234"/>
+      <c r="K60" s="234"/>
+      <c r="L60" s="234"/>
+    </row>
+    <row r="61" spans="1:12" s="68" customFormat="1">
+      <c r="A61" s="231" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="126" t="s">
+      <c r="B61" s="233" t="s">
         <v>204</v>
       </c>
-      <c r="C61" s="124"/>
-      <c r="D61" s="124"/>
-      <c r="E61" s="124"/>
-      <c r="F61" s="124"/>
-      <c r="G61" s="124"/>
-      <c r="H61" s="124"/>
-      <c r="I61" s="124"/>
-      <c r="J61" s="124"/>
-      <c r="K61" s="124"/>
-      <c r="L61" s="124"/>
-    </row>
-    <row r="62" spans="1:12" ht="33" customHeight="1">
-      <c r="A62" s="122" t="s">
+      <c r="C61" s="234"/>
+      <c r="D61" s="234"/>
+      <c r="E61" s="234"/>
+      <c r="F61" s="234"/>
+      <c r="G61" s="234"/>
+      <c r="H61" s="234"/>
+      <c r="I61" s="234"/>
+      <c r="J61" s="234"/>
+      <c r="K61" s="234"/>
+      <c r="L61" s="234"/>
+    </row>
+    <row r="62" spans="1:12" s="68" customFormat="1" ht="33" customHeight="1">
+      <c r="A62" s="231" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="126" t="s">
+      <c r="B62" s="233" t="s">
         <v>205</v>
       </c>
-      <c r="C62" s="124"/>
-      <c r="D62" s="124"/>
-      <c r="E62" s="124"/>
-      <c r="F62" s="124"/>
-      <c r="G62" s="124"/>
-      <c r="H62" s="124"/>
-      <c r="I62" s="124"/>
-      <c r="J62" s="124"/>
-      <c r="K62" s="124"/>
-      <c r="L62" s="124"/>
-    </row>
-    <row r="63" spans="1:12">
-      <c r="A63" s="137" t="s">
+      <c r="C62" s="234"/>
+      <c r="D62" s="234"/>
+      <c r="E62" s="234"/>
+      <c r="F62" s="234"/>
+      <c r="G62" s="234"/>
+      <c r="H62" s="234"/>
+      <c r="I62" s="234"/>
+      <c r="J62" s="234"/>
+      <c r="K62" s="234"/>
+      <c r="L62" s="234"/>
+    </row>
+    <row r="63" spans="1:12" s="68" customFormat="1">
+      <c r="A63" s="219" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="126" t="s">
+      <c r="B63" s="233" t="s">
         <v>206</v>
       </c>
-      <c r="C63" s="124"/>
-      <c r="D63" s="124"/>
-      <c r="E63" s="124"/>
-      <c r="F63" s="124"/>
-      <c r="G63" s="124"/>
-      <c r="H63" s="124"/>
-      <c r="I63" s="124"/>
-      <c r="J63" s="124"/>
-      <c r="K63" s="124"/>
-      <c r="L63" s="124"/>
-    </row>
-    <row r="64" spans="1:12" ht="31.15" customHeight="1">
-      <c r="A64" s="137"/>
-      <c r="B64" s="126" t="s">
+      <c r="C63" s="234"/>
+      <c r="D63" s="234"/>
+      <c r="E63" s="234"/>
+      <c r="F63" s="234"/>
+      <c r="G63" s="234"/>
+      <c r="H63" s="234"/>
+      <c r="I63" s="234"/>
+      <c r="J63" s="234"/>
+      <c r="K63" s="234"/>
+      <c r="L63" s="234"/>
+    </row>
+    <row r="64" spans="1:12" s="68" customFormat="1" ht="31.15" customHeight="1">
+      <c r="A64" s="219"/>
+      <c r="B64" s="233" t="s">
         <v>207</v>
       </c>
-      <c r="C64" s="124"/>
-      <c r="D64" s="124"/>
-      <c r="E64" s="124"/>
-      <c r="F64" s="124"/>
-      <c r="G64" s="124"/>
-      <c r="H64" s="124"/>
-      <c r="I64" s="124"/>
-      <c r="J64" s="124"/>
-      <c r="K64" s="124"/>
-      <c r="L64" s="124"/>
-    </row>
-    <row r="65" spans="1:18">
-      <c r="A65" s="125" t="s">
+      <c r="C64" s="234"/>
+      <c r="D64" s="234"/>
+      <c r="E64" s="234"/>
+      <c r="F64" s="234"/>
+      <c r="G64" s="234"/>
+      <c r="H64" s="234"/>
+      <c r="I64" s="234"/>
+      <c r="J64" s="234"/>
+      <c r="K64" s="234"/>
+      <c r="L64" s="234"/>
+    </row>
+    <row r="65" spans="1:12" s="68" customFormat="1">
+      <c r="A65" s="236" t="s">
         <v>142</v>
       </c>
-      <c r="B65" s="126" t="s">
+      <c r="B65" s="233" t="s">
         <v>74</v>
       </c>
-      <c r="C65" s="124"/>
-      <c r="D65" s="124"/>
-      <c r="E65" s="124"/>
-      <c r="F65" s="124"/>
-      <c r="G65" s="124"/>
-      <c r="H65" s="124"/>
-      <c r="I65" s="124"/>
-      <c r="J65" s="124"/>
-      <c r="K65" s="124"/>
-      <c r="L65" s="124"/>
-    </row>
-    <row r="66" spans="1:18">
-      <c r="A66" s="125" t="s">
+      <c r="C65" s="234"/>
+      <c r="D65" s="234"/>
+      <c r="E65" s="234"/>
+      <c r="F65" s="234"/>
+      <c r="G65" s="234"/>
+      <c r="H65" s="234"/>
+      <c r="I65" s="234"/>
+      <c r="J65" s="234"/>
+      <c r="K65" s="234"/>
+      <c r="L65" s="234"/>
+    </row>
+    <row r="66" spans="1:12" s="68" customFormat="1">
+      <c r="A66" s="236" t="s">
         <v>143</v>
       </c>
-      <c r="B66" s="126" t="s">
+      <c r="B66" s="233" t="s">
         <v>79</v>
       </c>
-      <c r="C66" s="124"/>
-      <c r="D66" s="124"/>
-      <c r="E66" s="124"/>
-      <c r="F66" s="124"/>
-      <c r="G66" s="124"/>
-      <c r="H66" s="124"/>
-      <c r="I66" s="124"/>
-      <c r="J66" s="124"/>
-      <c r="K66" s="124"/>
-      <c r="L66" s="124"/>
-    </row>
-    <row r="67" spans="1:18">
-      <c r="A67" s="125" t="s">
+      <c r="C66" s="234"/>
+      <c r="D66" s="234"/>
+      <c r="E66" s="234"/>
+      <c r="F66" s="234"/>
+      <c r="G66" s="234"/>
+      <c r="H66" s="234"/>
+      <c r="I66" s="234"/>
+      <c r="J66" s="234"/>
+      <c r="K66" s="234"/>
+      <c r="L66" s="234"/>
+    </row>
+    <row r="67" spans="1:12" s="68" customFormat="1">
+      <c r="A67" s="236" t="s">
         <v>144</v>
       </c>
-      <c r="B67" s="126" t="s">
+      <c r="B67" s="233" t="s">
         <v>80</v>
       </c>
-      <c r="C67" s="124"/>
-      <c r="D67" s="124"/>
-      <c r="E67" s="124"/>
-      <c r="F67" s="124"/>
-      <c r="G67" s="124"/>
-      <c r="H67" s="124"/>
-      <c r="I67" s="124"/>
-      <c r="J67" s="124"/>
-      <c r="K67" s="124"/>
-      <c r="L67" s="124"/>
-    </row>
-    <row r="68" spans="1:18">
-      <c r="A68" s="138" t="s">
+      <c r="C67" s="234"/>
+      <c r="D67" s="234"/>
+      <c r="E67" s="234"/>
+      <c r="F67" s="234"/>
+      <c r="G67" s="234"/>
+      <c r="H67" s="234"/>
+      <c r="I67" s="234"/>
+      <c r="J67" s="234"/>
+      <c r="K67" s="234"/>
+      <c r="L67" s="234"/>
+    </row>
+    <row r="68" spans="1:12" s="68" customFormat="1">
+      <c r="A68" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="B68" s="126" t="s">
+      <c r="B68" s="233" t="s">
         <v>81</v>
       </c>
-      <c r="C68" s="124"/>
-      <c r="D68" s="124"/>
-      <c r="E68" s="124"/>
-      <c r="F68" s="124"/>
-      <c r="G68" s="124"/>
-      <c r="H68" s="124"/>
-      <c r="I68" s="124"/>
-      <c r="J68" s="124"/>
-      <c r="K68" s="124"/>
-      <c r="L68" s="124"/>
-    </row>
-    <row r="69" spans="1:18">
-      <c r="A69" s="138"/>
-      <c r="B69" s="126" t="s">
+      <c r="C68" s="234"/>
+      <c r="D68" s="234"/>
+      <c r="E68" s="234"/>
+      <c r="F68" s="234"/>
+      <c r="G68" s="234"/>
+      <c r="H68" s="234"/>
+      <c r="I68" s="234"/>
+      <c r="J68" s="234"/>
+      <c r="K68" s="234"/>
+      <c r="L68" s="234"/>
+    </row>
+    <row r="69" spans="1:12" s="68" customFormat="1">
+      <c r="A69" s="237"/>
+      <c r="B69" s="233" t="s">
         <v>120</v>
       </c>
-      <c r="C69" s="124"/>
-      <c r="D69" s="124"/>
-      <c r="E69" s="124"/>
-      <c r="F69" s="124"/>
-      <c r="G69" s="124"/>
-      <c r="H69" s="124"/>
-      <c r="I69" s="124"/>
-      <c r="J69" s="124"/>
-      <c r="K69" s="124"/>
-      <c r="L69" s="124"/>
-    </row>
-    <row r="70" spans="1:18" ht="31.5">
-      <c r="A70" s="125" t="s">
+      <c r="C69" s="234"/>
+      <c r="D69" s="234"/>
+      <c r="E69" s="234"/>
+      <c r="F69" s="234"/>
+      <c r="G69" s="234"/>
+      <c r="H69" s="234"/>
+      <c r="I69" s="234"/>
+      <c r="J69" s="234"/>
+      <c r="K69" s="234"/>
+      <c r="L69" s="234"/>
+    </row>
+    <row r="70" spans="1:12" s="68" customFormat="1" ht="31.5">
+      <c r="A70" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="B70" s="126" t="s">
+      <c r="B70" s="233" t="s">
         <v>214</v>
       </c>
-      <c r="C70" s="124"/>
-      <c r="D70" s="124"/>
-      <c r="E70" s="124"/>
-      <c r="F70" s="124"/>
-      <c r="G70" s="124"/>
-      <c r="H70" s="124"/>
-      <c r="I70" s="124"/>
-      <c r="J70" s="124"/>
-      <c r="K70" s="124"/>
-      <c r="L70" s="124"/>
-    </row>
-    <row r="71" spans="1:18">
-      <c r="A71" s="125" t="s">
+      <c r="C70" s="234"/>
+      <c r="D70" s="234"/>
+      <c r="E70" s="234"/>
+      <c r="F70" s="234"/>
+      <c r="G70" s="234"/>
+      <c r="H70" s="234"/>
+      <c r="I70" s="234"/>
+      <c r="J70" s="234"/>
+      <c r="K70" s="234"/>
+      <c r="L70" s="234"/>
+    </row>
+    <row r="71" spans="1:12" s="68" customFormat="1">
+      <c r="A71" s="236" t="s">
         <v>147</v>
       </c>
-      <c r="B71" s="126" t="s">
+      <c r="B71" s="233" t="s">
         <v>75</v>
       </c>
-      <c r="C71" s="124"/>
-      <c r="D71" s="124"/>
-      <c r="E71" s="124"/>
-      <c r="F71" s="124"/>
-      <c r="G71" s="124"/>
-      <c r="H71" s="124"/>
-      <c r="I71" s="124"/>
-      <c r="J71" s="124"/>
-      <c r="K71" s="124"/>
-      <c r="L71" s="124"/>
-    </row>
-    <row r="72" spans="1:18" ht="18.75" customHeight="1">
-      <c r="A72" s="125" t="s">
+      <c r="C71" s="234"/>
+      <c r="D71" s="234"/>
+      <c r="E71" s="234"/>
+      <c r="F71" s="234"/>
+      <c r="G71" s="234"/>
+      <c r="H71" s="234"/>
+      <c r="I71" s="234"/>
+      <c r="J71" s="234"/>
+      <c r="K71" s="234"/>
+      <c r="L71" s="234"/>
+    </row>
+    <row r="72" spans="1:12" s="68" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A72" s="236" t="s">
         <v>148</v>
       </c>
-      <c r="B72" s="127" t="s">
+      <c r="B72" s="233" t="s">
         <v>121</v>
       </c>
-      <c r="C72" s="124"/>
-      <c r="D72" s="124"/>
-      <c r="E72" s="124"/>
-      <c r="F72" s="124"/>
-      <c r="G72" s="124"/>
-      <c r="H72" s="124"/>
-      <c r="I72" s="124"/>
-      <c r="J72" s="124"/>
-      <c r="K72" s="124"/>
-      <c r="L72" s="124"/>
-    </row>
-    <row r="73" spans="1:18">
-      <c r="A73" s="125" t="s">
+      <c r="C72" s="234"/>
+      <c r="D72" s="234"/>
+      <c r="E72" s="234"/>
+      <c r="F72" s="234"/>
+      <c r="G72" s="234"/>
+      <c r="H72" s="234"/>
+      <c r="I72" s="234"/>
+      <c r="J72" s="234"/>
+      <c r="K72" s="234"/>
+      <c r="L72" s="234"/>
+    </row>
+    <row r="73" spans="1:12" s="68" customFormat="1">
+      <c r="A73" s="236" t="s">
         <v>182</v>
       </c>
-      <c r="B73" s="127" t="s">
+      <c r="B73" s="233" t="s">
         <v>122</v>
       </c>
-      <c r="C73" s="124"/>
-      <c r="D73" s="124"/>
-      <c r="E73" s="124"/>
-      <c r="F73" s="124"/>
-      <c r="G73" s="124"/>
-      <c r="H73" s="124"/>
-      <c r="I73" s="124"/>
-      <c r="J73" s="124"/>
-      <c r="K73" s="124"/>
-      <c r="L73" s="124"/>
-    </row>
-    <row r="77" spans="1:18">
-      <c r="A77" s="83" t="s">
+      <c r="C73" s="234"/>
+      <c r="D73" s="234"/>
+      <c r="E73" s="234"/>
+      <c r="F73" s="234"/>
+      <c r="G73" s="234"/>
+      <c r="H73" s="234"/>
+      <c r="I73" s="234"/>
+      <c r="J73" s="234"/>
+      <c r="K73" s="234"/>
+      <c r="L73" s="234"/>
+    </row>
+    <row r="74" spans="1:12" s="68" customFormat="1">
+      <c r="A74" s="227"/>
+      <c r="B74" s="227"/>
+      <c r="C74" s="227"/>
+      <c r="D74" s="227"/>
+      <c r="E74" s="227"/>
+      <c r="F74" s="227"/>
+      <c r="G74" s="227"/>
+      <c r="H74" s="227"/>
+      <c r="I74" s="227"/>
+      <c r="J74" s="227"/>
+      <c r="K74" s="227"/>
+      <c r="L74" s="227"/>
+    </row>
+    <row r="75" spans="1:12" s="68" customFormat="1">
+      <c r="A75" s="227"/>
+      <c r="B75" s="227"/>
+      <c r="C75" s="227"/>
+      <c r="D75" s="227"/>
+      <c r="E75" s="227"/>
+      <c r="F75" s="227"/>
+      <c r="G75" s="227"/>
+      <c r="H75" s="227"/>
+      <c r="I75" s="227"/>
+      <c r="J75" s="227"/>
+      <c r="K75" s="227"/>
+      <c r="L75" s="227"/>
+    </row>
+    <row r="76" spans="1:12" s="68" customFormat="1">
+      <c r="A76" s="227"/>
+      <c r="B76" s="227"/>
+      <c r="C76" s="227"/>
+      <c r="D76" s="227"/>
+      <c r="E76" s="227"/>
+      <c r="F76" s="227"/>
+      <c r="G76" s="227"/>
+      <c r="H76" s="227"/>
+      <c r="I76" s="227"/>
+      <c r="J76" s="227"/>
+      <c r="K76" s="227"/>
+      <c r="L76" s="227"/>
+    </row>
+    <row r="77" spans="1:12" s="68" customFormat="1">
+      <c r="A77" s="230" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" ht="24" customHeight="1">
-      <c r="A78" s="137" t="s">
+      <c r="B77" s="227"/>
+      <c r="C77" s="227"/>
+      <c r="D77" s="227"/>
+      <c r="E77" s="227"/>
+      <c r="F77" s="227"/>
+      <c r="G77" s="227"/>
+      <c r="H77" s="227"/>
+      <c r="I77" s="227"/>
+      <c r="J77" s="227"/>
+      <c r="K77" s="227"/>
+      <c r="L77" s="227"/>
+    </row>
+    <row r="78" spans="1:12" s="68" customFormat="1" ht="24" customHeight="1">
+      <c r="A78" s="219" t="s">
         <v>213</v>
       </c>
-      <c r="B78" s="137"/>
-      <c r="C78" s="117">
+      <c r="B78" s="219"/>
+      <c r="C78" s="232">
         <v>1</v>
       </c>
-      <c r="D78" s="117">
+      <c r="D78" s="232">
         <v>2</v>
       </c>
-      <c r="E78" s="117">
+      <c r="E78" s="232">
         <v>3</v>
       </c>
-      <c r="F78" s="117">
+      <c r="F78" s="232">
         <v>4</v>
       </c>
-      <c r="G78" s="117">
+      <c r="G78" s="232">
         <v>5</v>
       </c>
-      <c r="H78" s="117">
+      <c r="H78" s="232">
         <v>6</v>
       </c>
-      <c r="I78" s="117">
+      <c r="I78" s="232">
         <v>7</v>
       </c>
-      <c r="J78" s="117">
+      <c r="J78" s="232">
         <v>8</v>
       </c>
-      <c r="K78" s="117">
+      <c r="K78" s="232">
         <v>9</v>
       </c>
-      <c r="L78" s="117">
+      <c r="L78" s="232">
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="16.5" customHeight="1">
-      <c r="A79" s="136" t="s">
+    <row r="79" spans="1:12" s="68" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A79" s="238" t="s">
         <v>208</v>
       </c>
-      <c r="B79" s="136"/>
-      <c r="C79" s="124"/>
-      <c r="D79" s="124"/>
-      <c r="E79" s="124"/>
-      <c r="F79" s="124"/>
-      <c r="G79" s="124"/>
-      <c r="H79" s="124"/>
-      <c r="I79" s="124"/>
-      <c r="J79" s="124"/>
-      <c r="K79" s="124"/>
-      <c r="L79" s="124"/>
-    </row>
-    <row r="80" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A80" s="136" t="s">
+      <c r="B79" s="238"/>
+      <c r="C79" s="234"/>
+      <c r="D79" s="234"/>
+      <c r="E79" s="234"/>
+      <c r="F79" s="234"/>
+      <c r="G79" s="234"/>
+      <c r="H79" s="234"/>
+      <c r="I79" s="234"/>
+      <c r="J79" s="234"/>
+      <c r="K79" s="234"/>
+      <c r="L79" s="234"/>
+    </row>
+    <row r="80" spans="1:12" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A80" s="238" t="s">
         <v>209</v>
       </c>
-      <c r="B80" s="136"/>
-      <c r="C80" s="124"/>
-      <c r="D80" s="124"/>
-      <c r="E80" s="124"/>
-      <c r="F80" s="124"/>
-      <c r="G80" s="124"/>
-      <c r="H80" s="124"/>
-      <c r="I80" s="124"/>
-      <c r="J80" s="124"/>
-      <c r="K80" s="124"/>
-      <c r="L80" s="124"/>
-      <c r="R80" s="79"/>
-    </row>
-    <row r="81" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A81" s="136" t="s">
+      <c r="B80" s="238"/>
+      <c r="C80" s="234"/>
+      <c r="D80" s="234"/>
+      <c r="E80" s="234"/>
+      <c r="F80" s="234"/>
+      <c r="G80" s="234"/>
+      <c r="H80" s="234"/>
+      <c r="I80" s="234"/>
+      <c r="J80" s="234"/>
+      <c r="K80" s="234"/>
+      <c r="L80" s="234"/>
+    </row>
+    <row r="81" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A81" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="B81" s="136"/>
-      <c r="C81" s="124"/>
-      <c r="D81" s="124"/>
-      <c r="E81" s="124"/>
-      <c r="F81" s="124"/>
-      <c r="G81" s="124"/>
-      <c r="H81" s="124"/>
-      <c r="I81" s="124"/>
-      <c r="J81" s="124"/>
-      <c r="K81" s="124"/>
-      <c r="L81" s="124"/>
-      <c r="R81" s="79"/>
-    </row>
-    <row r="82" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A82" s="136" t="s">
+      <c r="B81" s="238"/>
+      <c r="C81" s="234"/>
+      <c r="D81" s="234"/>
+      <c r="E81" s="234"/>
+      <c r="F81" s="234"/>
+      <c r="G81" s="234"/>
+      <c r="H81" s="234"/>
+      <c r="I81" s="234"/>
+      <c r="J81" s="234"/>
+      <c r="K81" s="234"/>
+      <c r="L81" s="234"/>
+    </row>
+    <row r="82" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A82" s="238" t="s">
         <v>160</v>
       </c>
-      <c r="B82" s="136"/>
-      <c r="C82" s="124"/>
-      <c r="D82" s="124"/>
-      <c r="E82" s="124"/>
-      <c r="F82" s="124"/>
-      <c r="G82" s="124"/>
-      <c r="H82" s="124"/>
-      <c r="I82" s="124"/>
-      <c r="J82" s="124"/>
-      <c r="K82" s="124"/>
-      <c r="L82" s="124"/>
-      <c r="R82" s="79"/>
-    </row>
-    <row r="83" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A83" s="136" t="s">
+      <c r="B82" s="238"/>
+      <c r="C82" s="234"/>
+      <c r="D82" s="234"/>
+      <c r="E82" s="234"/>
+      <c r="F82" s="234"/>
+      <c r="G82" s="234"/>
+      <c r="H82" s="234"/>
+      <c r="I82" s="234"/>
+      <c r="J82" s="234"/>
+      <c r="K82" s="234"/>
+      <c r="L82" s="234"/>
+    </row>
+    <row r="83" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A83" s="238" t="s">
         <v>161</v>
       </c>
-      <c r="B83" s="136"/>
-      <c r="C83" s="124"/>
-      <c r="D83" s="124"/>
-      <c r="E83" s="124"/>
-      <c r="F83" s="124"/>
-      <c r="G83" s="124"/>
-      <c r="H83" s="124"/>
-      <c r="I83" s="124"/>
-      <c r="J83" s="124"/>
-      <c r="K83" s="124"/>
-      <c r="L83" s="124"/>
-    </row>
-    <row r="84" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A84" s="136" t="s">
+      <c r="B83" s="238"/>
+      <c r="C83" s="234"/>
+      <c r="D83" s="234"/>
+      <c r="E83" s="234"/>
+      <c r="F83" s="234"/>
+      <c r="G83" s="234"/>
+      <c r="H83" s="234"/>
+      <c r="I83" s="234"/>
+      <c r="J83" s="234"/>
+      <c r="K83" s="234"/>
+      <c r="L83" s="234"/>
+    </row>
+    <row r="84" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A84" s="238" t="s">
         <v>159</v>
       </c>
-      <c r="B84" s="136"/>
-      <c r="C84" s="124"/>
-      <c r="D84" s="124"/>
-      <c r="E84" s="124"/>
-      <c r="F84" s="124"/>
-      <c r="G84" s="124"/>
-      <c r="H84" s="124"/>
-      <c r="I84" s="124"/>
-      <c r="J84" s="124"/>
-      <c r="K84" s="124"/>
-      <c r="L84" s="124"/>
-    </row>
-    <row r="85" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A85" s="136" t="s">
+      <c r="B84" s="238"/>
+      <c r="C84" s="234"/>
+      <c r="D84" s="234"/>
+      <c r="E84" s="234"/>
+      <c r="F84" s="234"/>
+      <c r="G84" s="234"/>
+      <c r="H84" s="234"/>
+      <c r="I84" s="234"/>
+      <c r="J84" s="234"/>
+      <c r="K84" s="234"/>
+      <c r="L84" s="234"/>
+    </row>
+    <row r="85" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A85" s="238" t="s">
         <v>121</v>
       </c>
-      <c r="B85" s="136"/>
-      <c r="C85" s="124"/>
-      <c r="D85" s="124"/>
-      <c r="E85" s="124"/>
-      <c r="F85" s="124"/>
-      <c r="G85" s="124"/>
-      <c r="H85" s="124"/>
-      <c r="I85" s="124"/>
-      <c r="J85" s="124"/>
-      <c r="K85" s="124"/>
-      <c r="L85" s="124"/>
-    </row>
-    <row r="86" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A86" s="136" t="s">
+      <c r="B85" s="238"/>
+      <c r="C85" s="234"/>
+      <c r="D85" s="234"/>
+      <c r="E85" s="234"/>
+      <c r="F85" s="234"/>
+      <c r="G85" s="234"/>
+      <c r="H85" s="234"/>
+      <c r="I85" s="234"/>
+      <c r="J85" s="234"/>
+      <c r="K85" s="234"/>
+      <c r="L85" s="234"/>
+    </row>
+    <row r="86" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A86" s="238" t="s">
         <v>122</v>
       </c>
-      <c r="B86" s="136"/>
-      <c r="C86" s="124"/>
-      <c r="D86" s="124"/>
-      <c r="E86" s="124"/>
-      <c r="F86" s="124"/>
-      <c r="G86" s="124"/>
-      <c r="H86" s="124"/>
-      <c r="I86" s="124"/>
-      <c r="J86" s="124"/>
-      <c r="K86" s="124"/>
-      <c r="L86" s="124"/>
-    </row>
-    <row r="87" spans="1:24" ht="15.75" customHeight="1"/>
-    <row r="88" spans="1:24" ht="15.75" customHeight="1"/>
-    <row r="89" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A89" s="80" t="s">
+      <c r="B86" s="238"/>
+      <c r="C86" s="234"/>
+      <c r="D86" s="234"/>
+      <c r="E86" s="234"/>
+      <c r="F86" s="234"/>
+      <c r="G86" s="234"/>
+      <c r="H86" s="234"/>
+      <c r="I86" s="234"/>
+      <c r="J86" s="234"/>
+      <c r="K86" s="234"/>
+      <c r="L86" s="234"/>
+    </row>
+    <row r="87" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A87" s="227"/>
+      <c r="B87" s="227"/>
+      <c r="C87" s="227"/>
+      <c r="D87" s="227"/>
+      <c r="E87" s="227"/>
+      <c r="F87" s="227"/>
+      <c r="G87" s="227"/>
+      <c r="H87" s="227"/>
+      <c r="I87" s="227"/>
+      <c r="J87" s="227"/>
+      <c r="K87" s="227"/>
+      <c r="L87" s="227"/>
+    </row>
+    <row r="88" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A88" s="227"/>
+      <c r="B88" s="227"/>
+      <c r="C88" s="227"/>
+      <c r="D88" s="227"/>
+      <c r="E88" s="227"/>
+      <c r="F88" s="227"/>
+      <c r="G88" s="227"/>
+      <c r="H88" s="227"/>
+      <c r="I88" s="227"/>
+      <c r="J88" s="227"/>
+      <c r="K88" s="227"/>
+      <c r="L88" s="227"/>
+    </row>
+    <row r="89" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A89" s="239" t="s">
         <v>233</v>
       </c>
-      <c r="M89" s="62"/>
-      <c r="N89" s="62"/>
-    </row>
-    <row r="90" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A90" s="137" t="s">
+      <c r="B89" s="227"/>
+      <c r="C89" s="227"/>
+      <c r="D89" s="227"/>
+      <c r="E89" s="227"/>
+      <c r="F89" s="227"/>
+      <c r="G89" s="227"/>
+      <c r="H89" s="227"/>
+      <c r="I89" s="227"/>
+      <c r="J89" s="227"/>
+      <c r="K89" s="227"/>
+      <c r="L89" s="227"/>
+      <c r="M89" s="113"/>
+      <c r="N89" s="113"/>
+    </row>
+    <row r="90" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A90" s="219" t="s">
         <v>213</v>
       </c>
-      <c r="B90" s="137"/>
-      <c r="C90" s="117">
+      <c r="B90" s="219"/>
+      <c r="C90" s="232">
         <v>1</v>
       </c>
-      <c r="D90" s="117">
+      <c r="D90" s="232">
         <v>2</v>
       </c>
-      <c r="E90" s="117">
+      <c r="E90" s="232">
         <v>3</v>
       </c>
-      <c r="F90" s="117">
+      <c r="F90" s="232">
         <v>4</v>
       </c>
-      <c r="G90" s="117">
+      <c r="G90" s="232">
         <v>5</v>
       </c>
-      <c r="H90" s="117">
+      <c r="H90" s="232">
         <v>6</v>
       </c>
-      <c r="I90" s="117">
+      <c r="I90" s="232">
         <v>7</v>
       </c>
-      <c r="J90" s="117">
+      <c r="J90" s="232">
         <v>8</v>
       </c>
-      <c r="K90" s="117">
+      <c r="K90" s="232">
         <v>9</v>
       </c>
-      <c r="L90" s="117">
+      <c r="L90" s="232">
         <v>10</v>
       </c>
-      <c r="T90" s="62"/>
-      <c r="U90" s="62"/>
-      <c r="V90" s="62"/>
-      <c r="W90" s="62"/>
-      <c r="X90" s="62"/>
-    </row>
-    <row r="91" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A91" s="136" t="s">
+      <c r="T90" s="113"/>
+      <c r="U90" s="113"/>
+      <c r="V90" s="113"/>
+      <c r="W90" s="113"/>
+      <c r="X90" s="113"/>
+    </row>
+    <row r="91" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A91" s="238" t="s">
         <v>163</v>
       </c>
-      <c r="B91" s="136"/>
-      <c r="C91" s="124"/>
-      <c r="D91" s="124"/>
-      <c r="E91" s="124"/>
-      <c r="F91" s="124"/>
-      <c r="G91" s="124"/>
-      <c r="H91" s="124"/>
-      <c r="I91" s="124"/>
-      <c r="J91" s="124"/>
-      <c r="K91" s="124"/>
-      <c r="L91" s="124"/>
-      <c r="T91" s="62"/>
-      <c r="U91" s="62"/>
-      <c r="V91" s="62"/>
-      <c r="W91" s="62"/>
-      <c r="X91" s="62"/>
-    </row>
-    <row r="92" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A92" s="136" t="s">
+      <c r="B91" s="238"/>
+      <c r="C91" s="234"/>
+      <c r="D91" s="234"/>
+      <c r="E91" s="234"/>
+      <c r="F91" s="234"/>
+      <c r="G91" s="234"/>
+      <c r="H91" s="234"/>
+      <c r="I91" s="234"/>
+      <c r="J91" s="234"/>
+      <c r="K91" s="234"/>
+      <c r="L91" s="234"/>
+      <c r="T91" s="113"/>
+      <c r="U91" s="113"/>
+      <c r="V91" s="113"/>
+      <c r="W91" s="113"/>
+      <c r="X91" s="113"/>
+    </row>
+    <row r="92" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A92" s="238" t="s">
         <v>210</v>
       </c>
-      <c r="B92" s="136"/>
-      <c r="C92" s="124"/>
-      <c r="D92" s="124"/>
-      <c r="E92" s="124"/>
-      <c r="F92" s="124"/>
-      <c r="G92" s="124"/>
-      <c r="H92" s="124"/>
-      <c r="I92" s="124"/>
-      <c r="J92" s="124"/>
-      <c r="K92" s="124"/>
-      <c r="L92" s="124"/>
-      <c r="P92" s="64"/>
-      <c r="Q92" s="64"/>
-      <c r="R92" s="64"/>
-      <c r="S92" s="60"/>
-      <c r="T92" s="63"/>
-      <c r="U92" s="64"/>
-      <c r="V92" s="64"/>
-      <c r="W92" s="64"/>
-      <c r="X92" s="64"/>
-    </row>
-    <row r="93" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A93" s="136" t="s">
+      <c r="B92" s="238"/>
+      <c r="C92" s="234"/>
+      <c r="D92" s="234"/>
+      <c r="E92" s="234"/>
+      <c r="F92" s="234"/>
+      <c r="G92" s="234"/>
+      <c r="H92" s="234"/>
+      <c r="I92" s="234"/>
+      <c r="J92" s="234"/>
+      <c r="K92" s="234"/>
+      <c r="L92" s="234"/>
+      <c r="P92" s="114"/>
+      <c r="Q92" s="114"/>
+      <c r="R92" s="114"/>
+      <c r="S92" s="112"/>
+      <c r="T92" s="115"/>
+      <c r="U92" s="114"/>
+      <c r="V92" s="114"/>
+      <c r="W92" s="114"/>
+      <c r="X92" s="114"/>
+    </row>
+    <row r="93" spans="1:24" s="68" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A93" s="238" t="s">
         <v>211</v>
       </c>
-      <c r="B93" s="136"/>
-      <c r="C93" s="124"/>
-      <c r="D93" s="124"/>
-      <c r="E93" s="124"/>
-      <c r="F93" s="124"/>
-      <c r="G93" s="124"/>
-      <c r="H93" s="124"/>
-      <c r="I93" s="124"/>
-      <c r="J93" s="124"/>
-      <c r="K93" s="124"/>
-      <c r="L93" s="124"/>
-      <c r="P93" s="64"/>
-      <c r="Q93" s="64"/>
-      <c r="R93" s="64"/>
-      <c r="S93" s="60"/>
-      <c r="T93" s="63"/>
-      <c r="U93" s="64"/>
-      <c r="V93" s="64"/>
-      <c r="W93" s="64"/>
-      <c r="X93" s="64"/>
-    </row>
-    <row r="94" spans="1:24" ht="22.9" customHeight="1">
-      <c r="A94" s="136" t="s">
+      <c r="B93" s="238"/>
+      <c r="C93" s="234"/>
+      <c r="D93" s="234"/>
+      <c r="E93" s="234"/>
+      <c r="F93" s="234"/>
+      <c r="G93" s="234"/>
+      <c r="H93" s="234"/>
+      <c r="I93" s="234"/>
+      <c r="J93" s="234"/>
+      <c r="K93" s="234"/>
+      <c r="L93" s="234"/>
+      <c r="P93" s="114"/>
+      <c r="Q93" s="114"/>
+      <c r="R93" s="114"/>
+      <c r="S93" s="112"/>
+      <c r="T93" s="115"/>
+      <c r="U93" s="114"/>
+      <c r="V93" s="114"/>
+      <c r="W93" s="114"/>
+      <c r="X93" s="114"/>
+    </row>
+    <row r="94" spans="1:24" s="68" customFormat="1" ht="22.9" customHeight="1">
+      <c r="A94" s="238" t="s">
         <v>164</v>
       </c>
-      <c r="B94" s="136"/>
-      <c r="C94" s="124"/>
-      <c r="D94" s="124"/>
-      <c r="E94" s="124"/>
-      <c r="F94" s="124"/>
-      <c r="G94" s="124"/>
-      <c r="H94" s="124"/>
-      <c r="I94" s="124"/>
-      <c r="J94" s="124"/>
-      <c r="K94" s="124"/>
-      <c r="L94" s="124"/>
-      <c r="M94" s="65"/>
-      <c r="N94" s="61"/>
-    </row>
-    <row r="95" spans="1:24" ht="20.45" customHeight="1">
-      <c r="A95" s="136" t="s">
+      <c r="B94" s="238"/>
+      <c r="C94" s="234"/>
+      <c r="D94" s="234"/>
+      <c r="E94" s="234"/>
+      <c r="F94" s="234"/>
+      <c r="G94" s="234"/>
+      <c r="H94" s="234"/>
+      <c r="I94" s="234"/>
+      <c r="J94" s="234"/>
+      <c r="K94" s="234"/>
+      <c r="L94" s="234"/>
+      <c r="M94" s="64"/>
+      <c r="N94" s="64"/>
+    </row>
+    <row r="95" spans="1:24" s="68" customFormat="1" ht="20.45" customHeight="1">
+      <c r="A95" s="238" t="s">
         <v>165</v>
       </c>
-      <c r="B95" s="136"/>
-      <c r="C95" s="124"/>
-      <c r="D95" s="124"/>
-      <c r="E95" s="124"/>
-      <c r="F95" s="124"/>
-      <c r="G95" s="124"/>
-      <c r="H95" s="124"/>
-      <c r="I95" s="124"/>
-      <c r="J95" s="124"/>
-      <c r="K95" s="124"/>
-      <c r="L95" s="124"/>
-      <c r="M95" s="65"/>
-      <c r="N95" s="61"/>
-    </row>
-    <row r="96" spans="1:24" ht="24" customHeight="1">
-      <c r="A96" s="136" t="s">
+      <c r="B95" s="238"/>
+      <c r="C95" s="234"/>
+      <c r="D95" s="234"/>
+      <c r="E95" s="234"/>
+      <c r="F95" s="234"/>
+      <c r="G95" s="234"/>
+      <c r="H95" s="234"/>
+      <c r="I95" s="234"/>
+      <c r="J95" s="234"/>
+      <c r="K95" s="234"/>
+      <c r="L95" s="234"/>
+      <c r="M95" s="64"/>
+      <c r="N95" s="64"/>
+    </row>
+    <row r="96" spans="1:24" s="68" customFormat="1" ht="24" customHeight="1">
+      <c r="A96" s="238" t="s">
         <v>166</v>
       </c>
-      <c r="B96" s="136"/>
-      <c r="C96" s="124"/>
-      <c r="D96" s="124"/>
-      <c r="E96" s="124"/>
-      <c r="F96" s="124"/>
-      <c r="G96" s="124"/>
-      <c r="H96" s="124"/>
-      <c r="I96" s="124"/>
-      <c r="J96" s="124"/>
-      <c r="K96" s="124"/>
-      <c r="L96" s="124"/>
-      <c r="M96" s="65"/>
-      <c r="N96" s="61"/>
-    </row>
-    <row r="97" spans="1:25" ht="20.25" customHeight="1">
-      <c r="A97" s="136" t="s">
+      <c r="B96" s="238"/>
+      <c r="C96" s="234"/>
+      <c r="D96" s="234"/>
+      <c r="E96" s="234"/>
+      <c r="F96" s="234"/>
+      <c r="G96" s="234"/>
+      <c r="H96" s="234"/>
+      <c r="I96" s="234"/>
+      <c r="J96" s="234"/>
+      <c r="K96" s="234"/>
+      <c r="L96" s="234"/>
+      <c r="M96" s="64"/>
+      <c r="N96" s="64"/>
+    </row>
+    <row r="97" spans="1:25" s="68" customFormat="1" ht="20.25" customHeight="1">
+      <c r="A97" s="238" t="s">
         <v>159</v>
       </c>
-      <c r="B97" s="136"/>
-      <c r="C97" s="124"/>
-      <c r="D97" s="124"/>
-      <c r="E97" s="124"/>
-      <c r="F97" s="124"/>
-      <c r="G97" s="124"/>
-      <c r="H97" s="124"/>
-      <c r="I97" s="124"/>
-      <c r="J97" s="124"/>
-      <c r="K97" s="124"/>
-      <c r="L97" s="124"/>
-    </row>
-    <row r="98" spans="1:25" ht="20.25" customHeight="1">
-      <c r="A98" s="136" t="s">
+      <c r="B97" s="238"/>
+      <c r="C97" s="234"/>
+      <c r="D97" s="234"/>
+      <c r="E97" s="234"/>
+      <c r="F97" s="234"/>
+      <c r="G97" s="234"/>
+      <c r="H97" s="234"/>
+      <c r="I97" s="234"/>
+      <c r="J97" s="234"/>
+      <c r="K97" s="234"/>
+      <c r="L97" s="234"/>
+    </row>
+    <row r="98" spans="1:25" s="68" customFormat="1" ht="20.25" customHeight="1">
+      <c r="A98" s="238" t="s">
         <v>121</v>
       </c>
-      <c r="B98" s="136"/>
-      <c r="C98" s="124"/>
-      <c r="D98" s="124"/>
-      <c r="E98" s="124"/>
-      <c r="F98" s="124"/>
-      <c r="G98" s="124"/>
-      <c r="H98" s="124"/>
-      <c r="I98" s="124"/>
-      <c r="J98" s="124"/>
-      <c r="K98" s="124"/>
-      <c r="L98" s="124"/>
-    </row>
-    <row r="99" spans="1:25" ht="15.6" customHeight="1">
-      <c r="A99" s="136" t="s">
+      <c r="B98" s="238"/>
+      <c r="C98" s="234"/>
+      <c r="D98" s="234"/>
+      <c r="E98" s="234"/>
+      <c r="F98" s="234"/>
+      <c r="G98" s="234"/>
+      <c r="H98" s="234"/>
+      <c r="I98" s="234"/>
+      <c r="J98" s="234"/>
+      <c r="K98" s="234"/>
+      <c r="L98" s="234"/>
+    </row>
+    <row r="99" spans="1:25" s="68" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A99" s="238" t="s">
         <v>122</v>
       </c>
-      <c r="B99" s="136"/>
-      <c r="C99" s="124"/>
-      <c r="D99" s="124"/>
-      <c r="E99" s="124"/>
-      <c r="F99" s="124"/>
-      <c r="G99" s="124"/>
-      <c r="H99" s="124"/>
-      <c r="I99" s="124"/>
-      <c r="J99" s="124"/>
-      <c r="K99" s="124"/>
-      <c r="L99" s="124"/>
-      <c r="P99" s="67"/>
-      <c r="Q99" s="67"/>
-      <c r="R99" s="67"/>
+      <c r="B99" s="238"/>
+      <c r="C99" s="234"/>
+      <c r="D99" s="234"/>
+      <c r="E99" s="234"/>
+      <c r="F99" s="234"/>
+      <c r="G99" s="234"/>
+      <c r="H99" s="234"/>
+      <c r="I99" s="234"/>
+      <c r="J99" s="234"/>
+      <c r="K99" s="234"/>
+      <c r="L99" s="234"/>
     </row>
     <row r="100" spans="1:25" ht="15.75" customHeight="1">
-      <c r="P100" s="67"/>
-      <c r="Q100" s="67"/>
-      <c r="R100" s="67"/>
+      <c r="P100" s="66"/>
+      <c r="Q100" s="66"/>
+      <c r="R100" s="66"/>
     </row>
     <row r="101" spans="1:25" ht="18" customHeight="1"/>
     <row r="106" spans="1:25">
-      <c r="Q106" s="63"/>
-      <c r="R106" s="64"/>
-      <c r="S106" s="64"/>
-      <c r="T106" s="64"/>
-      <c r="U106" s="64"/>
-      <c r="V106" s="64"/>
+      <c r="Q106" s="62"/>
+      <c r="R106" s="63"/>
+      <c r="S106" s="63"/>
+      <c r="T106" s="63"/>
+      <c r="U106" s="63"/>
+      <c r="V106" s="63"/>
       <c r="X106" s="60"/>
       <c r="Y106" s="60"/>
     </row>
     <row r="107" spans="1:25">
-      <c r="P107" s="69"/>
+      <c r="P107" s="68"/>
       <c r="Q107" s="61"/>
-      <c r="R107" s="68"/>
-      <c r="S107" s="66"/>
-      <c r="T107" s="67"/>
-      <c r="U107" s="67"/>
+      <c r="R107" s="67"/>
+      <c r="S107" s="65"/>
+      <c r="T107" s="66"/>
+      <c r="U107" s="66"/>
     </row>
     <row r="108" spans="1:25">
-      <c r="F108" s="69"/>
+      <c r="F108" s="68"/>
       <c r="G108" s="61"/>
-      <c r="H108" s="68"/>
-      <c r="I108" s="66"/>
-      <c r="J108" s="67"/>
-      <c r="K108" s="67"/>
+      <c r="H108" s="67"/>
+      <c r="I108" s="65"/>
+      <c r="J108" s="66"/>
+      <c r="K108" s="66"/>
     </row>
     <row r="109" spans="1:25">
-      <c r="F109" s="69"/>
+      <c r="F109" s="68"/>
       <c r="G109" s="61"/>
-      <c r="H109" s="68"/>
-      <c r="I109" s="66"/>
-      <c r="J109" s="67"/>
-      <c r="K109" s="67"/>
+      <c r="H109" s="67"/>
+      <c r="I109" s="65"/>
+      <c r="J109" s="66"/>
+      <c r="K109" s="66"/>
     </row>
     <row r="110" spans="1:25">
-      <c r="F110" s="69"/>
+      <c r="F110" s="68"/>
       <c r="G110" s="61"/>
-      <c r="H110" s="68"/>
-      <c r="I110" s="66"/>
-      <c r="J110" s="67"/>
-      <c r="K110" s="67"/>
+      <c r="H110" s="67"/>
+      <c r="I110" s="65"/>
+      <c r="J110" s="66"/>
+      <c r="K110" s="66"/>
     </row>
     <row r="111" spans="1:25">
-      <c r="F111" s="69"/>
+      <c r="F111" s="68"/>
       <c r="G111" s="61"/>
-      <c r="H111" s="68"/>
-      <c r="I111" s="66"/>
-      <c r="J111" s="67"/>
-      <c r="K111" s="67"/>
+      <c r="H111" s="67"/>
+      <c r="I111" s="65"/>
+      <c r="J111" s="66"/>
+      <c r="K111" s="66"/>
     </row>
     <row r="116" spans="1:16">
-      <c r="G116" s="70"/>
-      <c r="H116" s="70"/>
-      <c r="I116" s="70"/>
-      <c r="J116" s="70"/>
-      <c r="K116" s="70"/>
-      <c r="L116" s="70"/>
+      <c r="G116" s="69"/>
+      <c r="H116" s="69"/>
+      <c r="I116" s="69"/>
+      <c r="J116" s="69"/>
+      <c r="K116" s="69"/>
+      <c r="L116" s="69"/>
     </row>
     <row r="117" spans="1:16">
-      <c r="P117" s="81"/>
+      <c r="P117" s="80"/>
     </row>
     <row r="125" spans="1:16">
-      <c r="A125" s="71"/>
+      <c r="A125" s="70"/>
       <c r="M125" s="60"/>
-      <c r="N125" s="63"/>
-      <c r="O125" s="64"/>
+      <c r="N125" s="62"/>
+      <c r="O125" s="63"/>
     </row>
     <row r="137" spans="1:10">
-      <c r="A137" s="84"/>
-      <c r="B137" s="84"/>
-      <c r="C137" s="84"/>
-      <c r="D137" s="84"/>
-      <c r="E137" s="84"/>
-      <c r="F137" s="84"/>
-      <c r="G137" s="84"/>
-      <c r="H137" s="84"/>
-      <c r="I137" s="84"/>
-      <c r="J137" s="84"/>
+      <c r="A137" s="81"/>
+      <c r="B137" s="81"/>
+      <c r="C137" s="81"/>
+      <c r="D137" s="81"/>
+      <c r="E137" s="81"/>
+      <c r="F137" s="81"/>
+      <c r="G137" s="81"/>
+      <c r="H137" s="81"/>
+      <c r="I137" s="81"/>
+      <c r="J137" s="81"/>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="84"/>
-      <c r="B138" s="84"/>
-      <c r="C138" s="84"/>
-      <c r="D138" s="84"/>
-      <c r="E138" s="84"/>
-      <c r="F138" s="84"/>
-      <c r="G138" s="84"/>
-      <c r="H138" s="84"/>
-      <c r="I138" s="84"/>
-      <c r="J138" s="84"/>
+      <c r="A138" s="81"/>
+      <c r="B138" s="81"/>
+      <c r="C138" s="81"/>
+      <c r="D138" s="81"/>
+      <c r="E138" s="81"/>
+      <c r="F138" s="81"/>
+      <c r="G138" s="81"/>
+      <c r="H138" s="81"/>
+      <c r="I138" s="81"/>
+      <c r="J138" s="81"/>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="84"/>
-      <c r="B139" s="84"/>
-      <c r="C139" s="84"/>
-      <c r="D139" s="84"/>
-      <c r="E139" s="84"/>
-      <c r="F139" s="84"/>
-      <c r="G139" s="84"/>
-      <c r="H139" s="84"/>
-      <c r="I139" s="84"/>
-      <c r="J139" s="84"/>
+      <c r="A139" s="81"/>
+      <c r="B139" s="81"/>
+      <c r="C139" s="81"/>
+      <c r="D139" s="81"/>
+      <c r="E139" s="81"/>
+      <c r="F139" s="81"/>
+      <c r="G139" s="81"/>
+      <c r="H139" s="81"/>
+      <c r="I139" s="81"/>
+      <c r="J139" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -19963,14 +20086,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15">
-      <c r="D1" s="155" t="s">
+      <c r="D1" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
       <c r="J1" s="12"/>
       <c r="K1" s="12"/>
     </row>
@@ -20050,30 +20173,30 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="2:15" ht="19.5">
-      <c r="B12" s="171" t="s">
+      <c r="B12" s="155" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="171"/>
-      <c r="D12" s="171"/>
-      <c r="E12" s="171"/>
-      <c r="F12" s="171"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="171"/>
-      <c r="I12" s="171"/>
-      <c r="J12" s="171"/>
+      <c r="C12" s="155"/>
+      <c r="D12" s="155"/>
+      <c r="E12" s="155"/>
+      <c r="F12" s="155"/>
+      <c r="G12" s="155"/>
+      <c r="H12" s="155"/>
+      <c r="I12" s="155"/>
+      <c r="J12" s="155"/>
     </row>
     <row r="13" spans="2:15" ht="20.25">
-      <c r="B13" s="172" t="s">
+      <c r="B13" s="156" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="172"/>
-      <c r="D13" s="172"/>
-      <c r="E13" s="172"/>
-      <c r="F13" s="172"/>
-      <c r="G13" s="172"/>
-      <c r="H13" s="172"/>
-      <c r="I13" s="172"/>
-      <c r="J13" s="172"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="156"/>
+      <c r="H13" s="156"/>
+      <c r="I13" s="156"/>
+      <c r="J13" s="156"/>
     </row>
     <row r="14" spans="2:15">
       <c r="B14" s="7"/>
@@ -20087,11 +20210,11 @@
     </row>
     <row r="15" spans="2:15" ht="17.25">
       <c r="B15" s="7"/>
-      <c r="C15" s="169" t="s">
+      <c r="C15" s="153" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="169"/>
-      <c r="E15" s="169"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -20109,11 +20232,11 @@
     </row>
     <row r="17" spans="2:9" ht="17.25">
       <c r="B17" s="7"/>
-      <c r="C17" s="169" t="s">
+      <c r="C17" s="153" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="169"/>
-      <c r="E17" s="169"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -20131,11 +20254,11 @@
     </row>
     <row r="19" spans="2:9" ht="17.25">
       <c r="B19" s="7"/>
-      <c r="C19" s="170" t="s">
+      <c r="C19" s="154" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="170"/>
-      <c r="E19" s="170"/>
+      <c r="D19" s="154"/>
+      <c r="E19" s="154"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -20170,11 +20293,11 @@
     </row>
     <row r="23" spans="2:9" ht="17.25">
       <c r="B23" s="7"/>
-      <c r="C23" s="170" t="s">
+      <c r="C23" s="154" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="170"/>
-      <c r="E23" s="170"/>
+      <c r="D23" s="154"/>
+      <c r="E23" s="154"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -20399,30 +20522,30 @@
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="2:10" ht="41.25" customHeight="1">
-      <c r="B45" s="173" t="s">
+      <c r="B45" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="173"/>
-      <c r="D45" s="173"/>
-      <c r="E45" s="173"/>
-      <c r="F45" s="173"/>
-      <c r="G45" s="173"/>
-      <c r="H45" s="173"/>
-      <c r="I45" s="173"/>
-      <c r="J45" s="173"/>
+      <c r="C45" s="157"/>
+      <c r="D45" s="157"/>
+      <c r="E45" s="157"/>
+      <c r="F45" s="157"/>
+      <c r="G45" s="157"/>
+      <c r="H45" s="157"/>
+      <c r="I45" s="157"/>
+      <c r="J45" s="157"/>
     </row>
     <row r="46" spans="2:10">
-      <c r="B46" s="174" t="s">
+      <c r="B46" s="158" t="s">
         <v>40</v>
       </c>
-      <c r="C46" s="174"/>
-      <c r="D46" s="174"/>
-      <c r="E46" s="174"/>
-      <c r="F46" s="174"/>
-      <c r="G46" s="174"/>
-      <c r="H46" s="174"/>
-      <c r="I46" s="174"/>
-      <c r="J46" s="174"/>
+      <c r="C46" s="158"/>
+      <c r="D46" s="158"/>
+      <c r="E46" s="158"/>
+      <c r="F46" s="158"/>
+      <c r="G46" s="158"/>
+      <c r="H46" s="158"/>
+      <c r="I46" s="158"/>
+      <c r="J46" s="158"/>
     </row>
     <row r="47" spans="2:10">
       <c r="B47" s="8"/>
@@ -20436,30 +20559,30 @@
       <c r="J47" s="8"/>
     </row>
     <row r="48" spans="2:10">
-      <c r="B48" s="161" t="s">
+      <c r="B48" s="145" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="161"/>
-      <c r="D48" s="161"/>
-      <c r="E48" s="161"/>
-      <c r="F48" s="161"/>
-      <c r="G48" s="161"/>
-      <c r="H48" s="161"/>
-      <c r="I48" s="161"/>
-      <c r="J48" s="161"/>
+      <c r="C48" s="145"/>
+      <c r="D48" s="145"/>
+      <c r="E48" s="145"/>
+      <c r="F48" s="145"/>
+      <c r="G48" s="145"/>
+      <c r="H48" s="145"/>
+      <c r="I48" s="145"/>
+      <c r="J48" s="145"/>
     </row>
     <row r="49" spans="2:10">
-      <c r="B49" s="161" t="s">
+      <c r="B49" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="161"/>
-      <c r="D49" s="161"/>
-      <c r="E49" s="161"/>
-      <c r="F49" s="161"/>
-      <c r="G49" s="161"/>
-      <c r="H49" s="161"/>
-      <c r="I49" s="161"/>
-      <c r="J49" s="161"/>
+      <c r="C49" s="145"/>
+      <c r="D49" s="145"/>
+      <c r="E49" s="145"/>
+      <c r="F49" s="145"/>
+      <c r="G49" s="145"/>
+      <c r="H49" s="145"/>
+      <c r="I49" s="145"/>
+      <c r="J49" s="145"/>
     </row>
     <row r="50" spans="2:10">
       <c r="B50" s="7"/>
@@ -20491,63 +20614,63 @@
     </row>
     <row r="53" spans="2:10" ht="33" customHeight="1">
       <c r="B53" s="7"/>
-      <c r="C53" s="162" t="s">
+      <c r="C53" s="146" t="s">
         <v>57</v>
       </c>
-      <c r="D53" s="163"/>
-      <c r="E53" s="163"/>
-      <c r="F53" s="167"/>
-      <c r="G53" s="167"/>
-      <c r="H53" s="167"/>
-      <c r="I53" s="168"/>
+      <c r="D53" s="147"/>
+      <c r="E53" s="147"/>
+      <c r="F53" s="151"/>
+      <c r="G53" s="151"/>
+      <c r="H53" s="151"/>
+      <c r="I53" s="152"/>
     </row>
     <row r="54" spans="2:10" ht="38.25" customHeight="1">
       <c r="B54" s="7"/>
-      <c r="C54" s="162" t="s">
+      <c r="C54" s="146" t="s">
         <v>58</v>
       </c>
-      <c r="D54" s="163"/>
-      <c r="E54" s="163"/>
+      <c r="D54" s="147"/>
+      <c r="E54" s="147"/>
       <c r="F54" s="34"/>
       <c r="G54" s="35"/>
-      <c r="H54" s="165"/>
-      <c r="I54" s="165"/>
+      <c r="H54" s="149"/>
+      <c r="I54" s="149"/>
     </row>
     <row r="55" spans="2:10" ht="32.25" customHeight="1">
       <c r="B55" s="7"/>
-      <c r="C55" s="162" t="s">
+      <c r="C55" s="146" t="s">
         <v>59</v>
       </c>
-      <c r="D55" s="163"/>
-      <c r="E55" s="163"/>
-      <c r="F55" s="163"/>
-      <c r="G55" s="164"/>
-      <c r="H55" s="165"/>
-      <c r="I55" s="165"/>
+      <c r="D55" s="147"/>
+      <c r="E55" s="147"/>
+      <c r="F55" s="147"/>
+      <c r="G55" s="148"/>
+      <c r="H55" s="149"/>
+      <c r="I55" s="149"/>
     </row>
     <row r="56" spans="2:10" ht="34.5" customHeight="1">
       <c r="B56" s="7"/>
-      <c r="C56" s="162" t="s">
+      <c r="C56" s="146" t="s">
         <v>60</v>
       </c>
-      <c r="D56" s="163"/>
-      <c r="E56" s="163"/>
-      <c r="F56" s="163"/>
-      <c r="G56" s="164"/>
-      <c r="H56" s="166"/>
-      <c r="I56" s="166"/>
+      <c r="D56" s="147"/>
+      <c r="E56" s="147"/>
+      <c r="F56" s="147"/>
+      <c r="G56" s="148"/>
+      <c r="H56" s="150"/>
+      <c r="I56" s="150"/>
     </row>
     <row r="57" spans="2:10" ht="33" customHeight="1">
       <c r="B57" s="7"/>
-      <c r="C57" s="162" t="s">
+      <c r="C57" s="146" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="163"/>
-      <c r="E57" s="163"/>
-      <c r="F57" s="163"/>
-      <c r="G57" s="164"/>
-      <c r="H57" s="166"/>
-      <c r="I57" s="166"/>
+      <c r="D57" s="147"/>
+      <c r="E57" s="147"/>
+      <c r="F57" s="147"/>
+      <c r="G57" s="148"/>
+      <c r="H57" s="150"/>
+      <c r="I57" s="150"/>
     </row>
     <row r="58" spans="2:10">
       <c r="B58" s="7"/>
@@ -20584,17 +20707,17 @@
       <c r="B62" s="17"/>
     </row>
     <row r="72" spans="2:15">
-      <c r="B72" s="159" t="s">
+      <c r="B72" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="C72" s="160"/>
-      <c r="D72" s="160"/>
-      <c r="E72" s="160"/>
-      <c r="F72" s="160"/>
-      <c r="G72" s="160"/>
-      <c r="H72" s="160"/>
-      <c r="I72" s="160"/>
-      <c r="J72" s="160"/>
+      <c r="C72" s="144"/>
+      <c r="D72" s="144"/>
+      <c r="E72" s="144"/>
+      <c r="F72" s="144"/>
+      <c r="G72" s="144"/>
+      <c r="H72" s="144"/>
+      <c r="I72" s="144"/>
+      <c r="J72" s="144"/>
     </row>
     <row r="73" spans="2:15">
       <c r="B73" s="20" t="s">
@@ -20643,65 +20766,65 @@
       <c r="O81" s="15"/>
     </row>
     <row r="82" spans="2:15" ht="31.5" customHeight="1">
-      <c r="B82" s="156" t="s">
+      <c r="B82" s="140" t="s">
         <v>101</v>
       </c>
-      <c r="C82" s="157"/>
-      <c r="D82" s="157"/>
-      <c r="E82" s="157"/>
-      <c r="F82" s="157"/>
-      <c r="G82" s="157"/>
-      <c r="H82" s="157"/>
-      <c r="I82" s="157"/>
-      <c r="J82" s="158"/>
+      <c r="C82" s="141"/>
+      <c r="D82" s="141"/>
+      <c r="E82" s="141"/>
+      <c r="F82" s="141"/>
+      <c r="G82" s="141"/>
+      <c r="H82" s="141"/>
+      <c r="I82" s="141"/>
+      <c r="J82" s="142"/>
     </row>
     <row r="83" spans="2:15" ht="34.5" customHeight="1">
-      <c r="B83" s="153" t="s">
+      <c r="B83" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="C83" s="154"/>
-      <c r="D83" s="154"/>
-      <c r="E83" s="154"/>
-      <c r="F83" s="154"/>
-      <c r="G83" s="154"/>
-      <c r="H83" s="154"/>
-      <c r="I83" s="146">
+      <c r="C83" s="138"/>
+      <c r="D83" s="138"/>
+      <c r="E83" s="138"/>
+      <c r="F83" s="138"/>
+      <c r="G83" s="138"/>
+      <c r="H83" s="138"/>
+      <c r="I83" s="130">
         <f>Calculation!D19</f>
         <v>0</v>
       </c>
-      <c r="J83" s="147"/>
+      <c r="J83" s="131"/>
     </row>
     <row r="84" spans="2:15" ht="34.5" customHeight="1">
-      <c r="B84" s="153" t="s">
+      <c r="B84" s="137" t="s">
         <v>47</v>
       </c>
-      <c r="C84" s="154"/>
-      <c r="D84" s="154"/>
-      <c r="E84" s="154"/>
-      <c r="F84" s="154"/>
-      <c r="G84" s="154"/>
-      <c r="H84" s="154"/>
-      <c r="I84" s="146">
+      <c r="C84" s="138"/>
+      <c r="D84" s="138"/>
+      <c r="E84" s="138"/>
+      <c r="F84" s="138"/>
+      <c r="G84" s="138"/>
+      <c r="H84" s="138"/>
+      <c r="I84" s="130">
         <f>Calculation!D21</f>
         <v>0</v>
       </c>
-      <c r="J84" s="147"/>
+      <c r="J84" s="131"/>
     </row>
     <row r="85" spans="2:15" ht="33" customHeight="1" thickBot="1">
-      <c r="B85" s="190" t="s">
+      <c r="B85" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="C85" s="191"/>
-      <c r="D85" s="191"/>
-      <c r="E85" s="191"/>
-      <c r="F85" s="191"/>
-      <c r="G85" s="191"/>
-      <c r="H85" s="191"/>
-      <c r="I85" s="176">
+      <c r="C85" s="175"/>
+      <c r="D85" s="175"/>
+      <c r="E85" s="175"/>
+      <c r="F85" s="175"/>
+      <c r="G85" s="175"/>
+      <c r="H85" s="175"/>
+      <c r="I85" s="160">
         <f>Calculation!D20</f>
         <v>0</v>
       </c>
-      <c r="J85" s="177"/>
+      <c r="J85" s="161"/>
     </row>
     <row r="86" spans="2:15" ht="19.5" customHeight="1">
       <c r="B86" s="25"/>
@@ -20726,81 +20849,81 @@
       <c r="J87" s="21"/>
     </row>
     <row r="88" spans="2:15" ht="35.25" customHeight="1">
-      <c r="B88" s="156" t="s">
+      <c r="B88" s="140" t="s">
         <v>100</v>
       </c>
-      <c r="C88" s="157"/>
-      <c r="D88" s="157"/>
-      <c r="E88" s="157"/>
-      <c r="F88" s="157"/>
-      <c r="G88" s="157"/>
-      <c r="H88" s="157"/>
-      <c r="I88" s="157"/>
-      <c r="J88" s="158"/>
+      <c r="C88" s="141"/>
+      <c r="D88" s="141"/>
+      <c r="E88" s="141"/>
+      <c r="F88" s="141"/>
+      <c r="G88" s="141"/>
+      <c r="H88" s="141"/>
+      <c r="I88" s="141"/>
+      <c r="J88" s="142"/>
     </row>
     <row r="89" spans="2:15" ht="33.75" customHeight="1">
-      <c r="B89" s="178" t="s">
+      <c r="B89" s="162" t="s">
         <v>52</v>
       </c>
-      <c r="C89" s="179"/>
-      <c r="D89" s="179"/>
-      <c r="E89" s="179"/>
-      <c r="F89" s="179"/>
-      <c r="G89" s="179"/>
-      <c r="H89" s="179"/>
-      <c r="I89" s="146">
+      <c r="C89" s="163"/>
+      <c r="D89" s="163"/>
+      <c r="E89" s="163"/>
+      <c r="F89" s="163"/>
+      <c r="G89" s="163"/>
+      <c r="H89" s="163"/>
+      <c r="I89" s="130">
         <f>Calculation!D24</f>
         <v>0</v>
       </c>
-      <c r="J89" s="147"/>
+      <c r="J89" s="131"/>
     </row>
     <row r="90" spans="2:15" ht="33.75" customHeight="1">
-      <c r="B90" s="178" t="s">
+      <c r="B90" s="162" t="s">
         <v>49</v>
       </c>
-      <c r="C90" s="179"/>
-      <c r="D90" s="179"/>
-      <c r="E90" s="179"/>
-      <c r="F90" s="179"/>
-      <c r="G90" s="179"/>
-      <c r="H90" s="179"/>
-      <c r="I90" s="146">
+      <c r="C90" s="163"/>
+      <c r="D90" s="163"/>
+      <c r="E90" s="163"/>
+      <c r="F90" s="163"/>
+      <c r="G90" s="163"/>
+      <c r="H90" s="163"/>
+      <c r="I90" s="130">
         <f>Calculation!D23</f>
         <v>0</v>
       </c>
-      <c r="J90" s="147"/>
+      <c r="J90" s="131"/>
     </row>
     <row r="91" spans="2:15" ht="33.75" customHeight="1">
-      <c r="B91" s="178" t="s">
+      <c r="B91" s="162" t="s">
         <v>50</v>
       </c>
-      <c r="C91" s="179"/>
-      <c r="D91" s="179"/>
-      <c r="E91" s="179"/>
-      <c r="F91" s="179"/>
-      <c r="G91" s="179"/>
-      <c r="H91" s="179"/>
-      <c r="I91" s="146">
+      <c r="C91" s="163"/>
+      <c r="D91" s="163"/>
+      <c r="E91" s="163"/>
+      <c r="F91" s="163"/>
+      <c r="G91" s="163"/>
+      <c r="H91" s="163"/>
+      <c r="I91" s="130">
         <f>Calculation!D25</f>
         <v>0</v>
       </c>
-      <c r="J91" s="147"/>
+      <c r="J91" s="131"/>
     </row>
     <row r="92" spans="2:15" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B92" s="151" t="s">
+      <c r="B92" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="C92" s="152"/>
-      <c r="D92" s="152"/>
-      <c r="E92" s="152"/>
-      <c r="F92" s="152"/>
-      <c r="G92" s="152"/>
-      <c r="H92" s="152"/>
-      <c r="I92" s="176">
+      <c r="C92" s="136"/>
+      <c r="D92" s="136"/>
+      <c r="E92" s="136"/>
+      <c r="F92" s="136"/>
+      <c r="G92" s="136"/>
+      <c r="H92" s="136"/>
+      <c r="I92" s="160">
         <f>Calculation!H23</f>
         <v>0</v>
       </c>
-      <c r="J92" s="177"/>
+      <c r="J92" s="161"/>
     </row>
     <row r="93" spans="2:15" ht="21" customHeight="1">
       <c r="B93" s="8"/>
@@ -20825,96 +20948,96 @@
       <c r="J94" s="22"/>
     </row>
     <row r="95" spans="2:15" ht="32.25" customHeight="1">
-      <c r="B95" s="148" t="s">
+      <c r="B95" s="132" t="s">
         <v>99</v>
       </c>
-      <c r="C95" s="149"/>
-      <c r="D95" s="149"/>
-      <c r="E95" s="149"/>
-      <c r="F95" s="149"/>
-      <c r="G95" s="149"/>
-      <c r="H95" s="149"/>
-      <c r="I95" s="149"/>
-      <c r="J95" s="150"/>
+      <c r="C95" s="133"/>
+      <c r="D95" s="133"/>
+      <c r="E95" s="133"/>
+      <c r="F95" s="133"/>
+      <c r="G95" s="133"/>
+      <c r="H95" s="133"/>
+      <c r="I95" s="133"/>
+      <c r="J95" s="134"/>
     </row>
     <row r="96" spans="2:15" ht="34.5" customHeight="1">
-      <c r="B96" s="153" t="s">
+      <c r="B96" s="137" t="s">
         <v>53</v>
       </c>
-      <c r="C96" s="154"/>
-      <c r="D96" s="154"/>
-      <c r="E96" s="154"/>
-      <c r="F96" s="154"/>
-      <c r="G96" s="154"/>
-      <c r="H96" s="154"/>
-      <c r="I96" s="146">
+      <c r="C96" s="138"/>
+      <c r="D96" s="138"/>
+      <c r="E96" s="138"/>
+      <c r="F96" s="138"/>
+      <c r="G96" s="138"/>
+      <c r="H96" s="138"/>
+      <c r="I96" s="130">
         <f>Calculation!H24</f>
         <v>0</v>
       </c>
-      <c r="J96" s="147"/>
+      <c r="J96" s="131"/>
     </row>
     <row r="97" spans="2:17" ht="33.75" customHeight="1">
-      <c r="B97" s="153" t="s">
+      <c r="B97" s="137" t="s">
         <v>54</v>
       </c>
-      <c r="C97" s="154"/>
-      <c r="D97" s="154"/>
-      <c r="E97" s="154"/>
-      <c r="F97" s="154"/>
-      <c r="G97" s="154"/>
-      <c r="H97" s="154"/>
-      <c r="I97" s="146">
+      <c r="C97" s="138"/>
+      <c r="D97" s="138"/>
+      <c r="E97" s="138"/>
+      <c r="F97" s="138"/>
+      <c r="G97" s="138"/>
+      <c r="H97" s="138"/>
+      <c r="I97" s="130">
         <f>Calculation!H25</f>
         <v>0</v>
       </c>
-      <c r="J97" s="147"/>
+      <c r="J97" s="131"/>
     </row>
     <row r="98" spans="2:17" ht="31.5" customHeight="1">
-      <c r="B98" s="153" t="s">
+      <c r="B98" s="137" t="s">
         <v>55</v>
       </c>
-      <c r="C98" s="154"/>
-      <c r="D98" s="154"/>
-      <c r="E98" s="154"/>
-      <c r="F98" s="154"/>
-      <c r="G98" s="154"/>
-      <c r="H98" s="154"/>
-      <c r="I98" s="146">
+      <c r="C98" s="138"/>
+      <c r="D98" s="138"/>
+      <c r="E98" s="138"/>
+      <c r="F98" s="138"/>
+      <c r="G98" s="138"/>
+      <c r="H98" s="138"/>
+      <c r="I98" s="130">
         <f>Calculation!C30</f>
         <v>0</v>
       </c>
-      <c r="J98" s="147"/>
+      <c r="J98" s="131"/>
     </row>
     <row r="99" spans="2:17" ht="35.25" customHeight="1">
-      <c r="B99" s="153" t="s">
+      <c r="B99" s="137" t="s">
         <v>56</v>
       </c>
-      <c r="C99" s="154"/>
-      <c r="D99" s="154"/>
-      <c r="E99" s="154"/>
-      <c r="F99" s="154"/>
-      <c r="G99" s="154"/>
-      <c r="H99" s="154"/>
-      <c r="I99" s="146">
+      <c r="C99" s="138"/>
+      <c r="D99" s="138"/>
+      <c r="E99" s="138"/>
+      <c r="F99" s="138"/>
+      <c r="G99" s="138"/>
+      <c r="H99" s="138"/>
+      <c r="I99" s="130">
         <f>Calculation!D30</f>
         <v>0</v>
       </c>
-      <c r="J99" s="147"/>
+      <c r="J99" s="131"/>
     </row>
     <row r="100" spans="2:17" ht="41.25" customHeight="1" thickBot="1">
-      <c r="B100" s="184" t="s">
+      <c r="B100" s="168" t="s">
         <v>62</v>
       </c>
-      <c r="C100" s="185"/>
-      <c r="D100" s="185"/>
-      <c r="E100" s="185"/>
-      <c r="F100" s="185"/>
-      <c r="G100" s="185"/>
-      <c r="H100" s="185"/>
-      <c r="I100" s="186" t="s">
+      <c r="C100" s="169"/>
+      <c r="D100" s="169"/>
+      <c r="E100" s="169"/>
+      <c r="F100" s="169"/>
+      <c r="G100" s="169"/>
+      <c r="H100" s="169"/>
+      <c r="I100" s="170" t="s">
         <v>82</v>
       </c>
-      <c r="J100" s="177"/>
+      <c r="J100" s="161"/>
     </row>
     <row r="101" spans="2:17">
       <c r="F101" s="23"/>
@@ -20933,38 +21056,38 @@
       <c r="J104" s="24"/>
     </row>
     <row r="105" spans="2:17" ht="24" customHeight="1">
-      <c r="B105" s="187" t="s">
+      <c r="B105" s="171" t="s">
         <v>96</v>
       </c>
-      <c r="C105" s="187"/>
-      <c r="D105" s="187"/>
-      <c r="E105" s="187"/>
-      <c r="F105" s="187"/>
-      <c r="G105" s="187"/>
-      <c r="H105" s="187"/>
-      <c r="I105" s="187"/>
-      <c r="J105" s="187"/>
+      <c r="C105" s="171"/>
+      <c r="D105" s="171"/>
+      <c r="E105" s="171"/>
+      <c r="F105" s="171"/>
+      <c r="G105" s="171"/>
+      <c r="H105" s="171"/>
+      <c r="I105" s="171"/>
+      <c r="J105" s="171"/>
     </row>
     <row r="106" spans="2:17" ht="50.25" customHeight="1">
       <c r="B106" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C106" s="175" t="s">
+      <c r="C106" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="D106" s="175"/>
-      <c r="E106" s="175" t="s">
+      <c r="D106" s="159"/>
+      <c r="E106" s="159" t="s">
         <v>70</v>
       </c>
-      <c r="F106" s="175"/>
-      <c r="G106" s="175" t="s">
+      <c r="F106" s="159"/>
+      <c r="G106" s="159" t="s">
         <v>64</v>
       </c>
-      <c r="H106" s="175"/>
-      <c r="I106" s="175" t="s">
+      <c r="H106" s="159"/>
+      <c r="I106" s="159" t="s">
         <v>65</v>
       </c>
-      <c r="J106" s="175"/>
+      <c r="J106" s="159"/>
       <c r="K106" s="19"/>
       <c r="L106" s="19"/>
       <c r="M106" s="19"/>
@@ -20977,723 +21100,723 @@
       <c r="B107" s="27">
         <v>1</v>
       </c>
-      <c r="C107" s="145">
+      <c r="C107" s="129">
         <f>Calculation!F30</f>
         <v>0</v>
       </c>
-      <c r="D107" s="145"/>
-      <c r="E107" s="145">
+      <c r="D107" s="129"/>
+      <c r="E107" s="129">
         <f>Calculation!G30</f>
         <v>0</v>
       </c>
-      <c r="F107" s="145"/>
-      <c r="G107" s="144">
+      <c r="F107" s="129"/>
+      <c r="G107" s="128">
         <f>Calculation!H30</f>
         <v>0</v>
       </c>
-      <c r="H107" s="144"/>
-      <c r="I107" s="144" t="e">
+      <c r="H107" s="128"/>
+      <c r="I107" s="128" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J107" s="144"/>
+      <c r="J107" s="128"/>
     </row>
     <row r="108" spans="2:17">
       <c r="B108" s="27">
         <v>2</v>
       </c>
-      <c r="C108" s="145">
+      <c r="C108" s="129">
         <f>Calculation!F31</f>
         <v>0</v>
       </c>
-      <c r="D108" s="145"/>
-      <c r="E108" s="145">
+      <c r="D108" s="129"/>
+      <c r="E108" s="129">
         <f>Calculation!G31</f>
         <v>0</v>
       </c>
-      <c r="F108" s="145"/>
-      <c r="G108" s="144">
+      <c r="F108" s="129"/>
+      <c r="G108" s="128">
         <f>Calculation!H31</f>
         <v>0</v>
       </c>
-      <c r="H108" s="144"/>
-      <c r="I108" s="144" t="e">
+      <c r="H108" s="128"/>
+      <c r="I108" s="128" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J108" s="144"/>
+      <c r="J108" s="128"/>
     </row>
     <row r="109" spans="2:17">
       <c r="B109" s="27">
         <v>3</v>
       </c>
-      <c r="C109" s="145">
+      <c r="C109" s="129">
         <f>Calculation!F32</f>
         <v>0</v>
       </c>
-      <c r="D109" s="145"/>
-      <c r="E109" s="145">
+      <c r="D109" s="129"/>
+      <c r="E109" s="129">
         <f>Calculation!G32</f>
         <v>0</v>
       </c>
-      <c r="F109" s="145"/>
-      <c r="G109" s="144">
+      <c r="F109" s="129"/>
+      <c r="G109" s="128">
         <f>Calculation!H32</f>
         <v>0</v>
       </c>
-      <c r="H109" s="144"/>
-      <c r="I109" s="144" t="e">
+      <c r="H109" s="128"/>
+      <c r="I109" s="128" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J109" s="144"/>
+      <c r="J109" s="128"/>
     </row>
     <row r="110" spans="2:17">
       <c r="B110" s="27">
         <v>4</v>
       </c>
-      <c r="C110" s="145">
+      <c r="C110" s="129">
         <f>Calculation!F33</f>
         <v>0</v>
       </c>
-      <c r="D110" s="145"/>
-      <c r="E110" s="145">
+      <c r="D110" s="129"/>
+      <c r="E110" s="129">
         <f>Calculation!G33</f>
         <v>0</v>
       </c>
-      <c r="F110" s="145"/>
-      <c r="G110" s="144">
+      <c r="F110" s="129"/>
+      <c r="G110" s="128">
         <f>Calculation!H33</f>
         <v>0</v>
       </c>
-      <c r="H110" s="144"/>
-      <c r="I110" s="144" t="e">
+      <c r="H110" s="128"/>
+      <c r="I110" s="128" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J110" s="144"/>
+      <c r="J110" s="128"/>
     </row>
     <row r="111" spans="2:17">
       <c r="B111" s="27">
         <v>5</v>
       </c>
-      <c r="C111" s="145">
+      <c r="C111" s="129">
         <f>Calculation!F34</f>
         <v>0</v>
       </c>
-      <c r="D111" s="145"/>
-      <c r="E111" s="145">
+      <c r="D111" s="129"/>
+      <c r="E111" s="129">
         <f>Calculation!G34</f>
         <v>0</v>
       </c>
-      <c r="F111" s="145"/>
-      <c r="G111" s="144">
+      <c r="F111" s="129"/>
+      <c r="G111" s="128">
         <f>Calculation!H34</f>
         <v>0</v>
       </c>
-      <c r="H111" s="144"/>
-      <c r="I111" s="144" t="e">
+      <c r="H111" s="128"/>
+      <c r="I111" s="128" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J111" s="144"/>
+      <c r="J111" s="128"/>
     </row>
     <row r="112" spans="2:17">
       <c r="B112" s="27">
         <v>6</v>
       </c>
-      <c r="C112" s="145">
+      <c r="C112" s="129">
         <f>Calculation!F35</f>
         <v>0</v>
       </c>
-      <c r="D112" s="145"/>
-      <c r="E112" s="145">
+      <c r="D112" s="129"/>
+      <c r="E112" s="129">
         <f>Calculation!G35</f>
         <v>0</v>
       </c>
-      <c r="F112" s="145"/>
-      <c r="G112" s="144">
+      <c r="F112" s="129"/>
+      <c r="G112" s="128">
         <f>Calculation!H35</f>
         <v>0</v>
       </c>
-      <c r="H112" s="144"/>
-      <c r="I112" s="144" t="e">
+      <c r="H112" s="128"/>
+      <c r="I112" s="128" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J112" s="144"/>
+      <c r="J112" s="128"/>
     </row>
     <row r="113" spans="2:14">
       <c r="B113" s="27">
         <v>7</v>
       </c>
-      <c r="C113" s="145">
+      <c r="C113" s="129">
         <f>Calculation!F36</f>
         <v>0</v>
       </c>
-      <c r="D113" s="145"/>
-      <c r="E113" s="145">
+      <c r="D113" s="129"/>
+      <c r="E113" s="129">
         <f>Calculation!G36</f>
         <v>0</v>
       </c>
-      <c r="F113" s="145"/>
-      <c r="G113" s="144">
+      <c r="F113" s="129"/>
+      <c r="G113" s="128">
         <f>Calculation!H36</f>
         <v>0</v>
       </c>
-      <c r="H113" s="144"/>
-      <c r="I113" s="144" t="e">
+      <c r="H113" s="128"/>
+      <c r="I113" s="128" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J113" s="144"/>
+      <c r="J113" s="128"/>
     </row>
     <row r="114" spans="2:14">
       <c r="B114" s="27">
         <v>8</v>
       </c>
-      <c r="C114" s="188"/>
-      <c r="D114" s="188"/>
-      <c r="E114" s="189"/>
-      <c r="F114" s="189"/>
-      <c r="G114" s="144"/>
-      <c r="H114" s="144"/>
-      <c r="I114" s="144"/>
-      <c r="J114" s="144"/>
+      <c r="C114" s="172"/>
+      <c r="D114" s="172"/>
+      <c r="E114" s="173"/>
+      <c r="F114" s="173"/>
+      <c r="G114" s="128"/>
+      <c r="H114" s="128"/>
+      <c r="I114" s="128"/>
+      <c r="J114" s="128"/>
     </row>
     <row r="115" spans="2:14">
       <c r="B115" s="27">
         <v>9</v>
       </c>
-      <c r="C115" s="188"/>
-      <c r="D115" s="188"/>
-      <c r="E115" s="189"/>
-      <c r="F115" s="189"/>
-      <c r="G115" s="144"/>
-      <c r="H115" s="144"/>
-      <c r="I115" s="144"/>
-      <c r="J115" s="144"/>
+      <c r="C115" s="172"/>
+      <c r="D115" s="172"/>
+      <c r="E115" s="173"/>
+      <c r="F115" s="173"/>
+      <c r="G115" s="128"/>
+      <c r="H115" s="128"/>
+      <c r="I115" s="128"/>
+      <c r="J115" s="128"/>
     </row>
     <row r="116" spans="2:14">
       <c r="B116" s="27">
         <v>10</v>
       </c>
-      <c r="C116" s="188"/>
-      <c r="D116" s="188"/>
-      <c r="E116" s="189"/>
-      <c r="F116" s="189"/>
-      <c r="G116" s="144"/>
-      <c r="H116" s="144"/>
-      <c r="I116" s="144"/>
-      <c r="J116" s="144"/>
+      <c r="C116" s="172"/>
+      <c r="D116" s="172"/>
+      <c r="E116" s="173"/>
+      <c r="F116" s="173"/>
+      <c r="G116" s="128"/>
+      <c r="H116" s="128"/>
+      <c r="I116" s="128"/>
+      <c r="J116" s="128"/>
     </row>
     <row r="117" spans="2:14" ht="31.5" customHeight="1">
-      <c r="B117" s="194" t="s">
+      <c r="B117" s="178" t="s">
         <v>97</v>
       </c>
-      <c r="C117" s="195"/>
-      <c r="D117" s="195"/>
-      <c r="E117" s="195"/>
-      <c r="F117" s="195"/>
-      <c r="G117" s="195"/>
-      <c r="H117" s="195"/>
-      <c r="I117" s="195"/>
-      <c r="J117" s="195"/>
+      <c r="C117" s="179"/>
+      <c r="D117" s="179"/>
+      <c r="E117" s="179"/>
+      <c r="F117" s="179"/>
+      <c r="G117" s="179"/>
+      <c r="H117" s="179"/>
+      <c r="I117" s="179"/>
+      <c r="J117" s="179"/>
     </row>
     <row r="118" spans="2:14" ht="33" customHeight="1">
       <c r="B118" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C118" s="193" t="s">
+      <c r="C118" s="177" t="s">
         <v>68</v>
       </c>
-      <c r="D118" s="193"/>
-      <c r="E118" s="193" t="s">
+      <c r="D118" s="177"/>
+      <c r="E118" s="177" t="s">
         <v>69</v>
       </c>
-      <c r="F118" s="193"/>
-      <c r="G118" s="193" t="s">
+      <c r="F118" s="177"/>
+      <c r="G118" s="177" t="s">
         <v>71</v>
       </c>
-      <c r="H118" s="193"/>
-      <c r="I118" s="193" t="s">
+      <c r="H118" s="177"/>
+      <c r="I118" s="177" t="s">
         <v>72</v>
       </c>
-      <c r="J118" s="193"/>
+      <c r="J118" s="177"/>
     </row>
     <row r="119" spans="2:14">
       <c r="B119" s="29">
         <v>1</v>
       </c>
-      <c r="C119" s="180">
+      <c r="C119" s="164">
         <f>Calculation!F58*3600</f>
         <v>0</v>
       </c>
-      <c r="D119" s="180"/>
-      <c r="E119" s="181" t="e">
+      <c r="D119" s="164"/>
+      <c r="E119" s="165" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F119" s="181"/>
-      <c r="G119" s="182" t="e">
+      <c r="F119" s="165"/>
+      <c r="G119" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H119" s="182"/>
-      <c r="I119" s="182" t="e">
+      <c r="H119" s="166"/>
+      <c r="I119" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J119" s="183"/>
+      <c r="J119" s="167"/>
     </row>
     <row r="120" spans="2:14">
       <c r="B120" s="29">
         <v>2</v>
       </c>
-      <c r="C120" s="180">
+      <c r="C120" s="164">
         <f>Calculation!F59*3600</f>
         <v>0</v>
       </c>
-      <c r="D120" s="180"/>
-      <c r="E120" s="181" t="e">
+      <c r="D120" s="164"/>
+      <c r="E120" s="165" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F120" s="181"/>
-      <c r="G120" s="182" t="e">
+      <c r="F120" s="165"/>
+      <c r="G120" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H120" s="182"/>
-      <c r="I120" s="182" t="e">
+      <c r="H120" s="166"/>
+      <c r="I120" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J120" s="183"/>
+      <c r="J120" s="167"/>
     </row>
     <row r="121" spans="2:14">
       <c r="B121" s="29">
         <v>3</v>
       </c>
-      <c r="C121" s="180">
+      <c r="C121" s="164">
         <f>Calculation!F60*3600</f>
         <v>0</v>
       </c>
-      <c r="D121" s="180"/>
-      <c r="E121" s="181" t="e">
+      <c r="D121" s="164"/>
+      <c r="E121" s="165" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F121" s="181"/>
-      <c r="G121" s="182" t="e">
+      <c r="F121" s="165"/>
+      <c r="G121" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H121" s="182"/>
-      <c r="I121" s="182" t="e">
+      <c r="H121" s="166"/>
+      <c r="I121" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J121" s="183"/>
+      <c r="J121" s="167"/>
     </row>
     <row r="122" spans="2:14">
       <c r="B122" s="29">
         <v>4</v>
       </c>
-      <c r="C122" s="180">
+      <c r="C122" s="164">
         <f>Calculation!F61*3600</f>
         <v>0</v>
       </c>
-      <c r="D122" s="180"/>
-      <c r="E122" s="181" t="e">
+      <c r="D122" s="164"/>
+      <c r="E122" s="165" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F122" s="181"/>
-      <c r="G122" s="182" t="e">
+      <c r="F122" s="165"/>
+      <c r="G122" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H122" s="182"/>
-      <c r="I122" s="182" t="e">
+      <c r="H122" s="166"/>
+      <c r="I122" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J122" s="183"/>
+      <c r="J122" s="167"/>
     </row>
     <row r="123" spans="2:14">
       <c r="B123" s="29">
         <v>5</v>
       </c>
-      <c r="C123" s="180">
+      <c r="C123" s="164">
         <f>Calculation!F62*3600</f>
         <v>0</v>
       </c>
-      <c r="D123" s="180"/>
-      <c r="E123" s="181" t="e">
+      <c r="D123" s="164"/>
+      <c r="E123" s="165" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F123" s="181"/>
-      <c r="G123" s="182" t="e">
+      <c r="F123" s="165"/>
+      <c r="G123" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H123" s="182"/>
-      <c r="I123" s="182">
+      <c r="H123" s="166"/>
+      <c r="I123" s="166">
         <f>Calculation!J105</f>
         <v>0</v>
       </c>
-      <c r="J123" s="183"/>
+      <c r="J123" s="167"/>
     </row>
     <row r="124" spans="2:14">
       <c r="B124" s="29">
         <v>6</v>
       </c>
-      <c r="C124" s="180">
+      <c r="C124" s="164">
         <f>Calculation!F63*3600</f>
         <v>0</v>
       </c>
-      <c r="D124" s="180"/>
-      <c r="E124" s="181" t="e">
+      <c r="D124" s="164"/>
+      <c r="E124" s="165" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F124" s="181"/>
-      <c r="G124" s="182" t="e">
+      <c r="F124" s="165"/>
+      <c r="G124" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H124" s="182"/>
-      <c r="I124" s="182">
+      <c r="H124" s="166"/>
+      <c r="I124" s="166">
         <f>Calculation!J106</f>
         <v>0</v>
       </c>
-      <c r="J124" s="183"/>
+      <c r="J124" s="167"/>
       <c r="N124" s="16"/>
     </row>
     <row r="125" spans="2:14">
       <c r="B125" s="29">
         <v>7</v>
       </c>
-      <c r="C125" s="180">
+      <c r="C125" s="164">
         <f>Calculation!F64*3600</f>
         <v>0</v>
       </c>
-      <c r="D125" s="180"/>
-      <c r="E125" s="181" t="e">
+      <c r="D125" s="164"/>
+      <c r="E125" s="165" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F125" s="181"/>
-      <c r="G125" s="182" t="e">
+      <c r="F125" s="165"/>
+      <c r="G125" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H125" s="182"/>
-      <c r="I125" s="182">
+      <c r="H125" s="166"/>
+      <c r="I125" s="166">
         <f>Calculation!J107</f>
         <v>0</v>
       </c>
-      <c r="J125" s="183"/>
+      <c r="J125" s="167"/>
     </row>
     <row r="126" spans="2:14">
       <c r="B126" s="29">
         <v>8</v>
       </c>
-      <c r="C126" s="192"/>
-      <c r="D126" s="192"/>
-      <c r="E126" s="192"/>
-      <c r="F126" s="192"/>
-      <c r="G126" s="183"/>
-      <c r="H126" s="183"/>
-      <c r="I126" s="183"/>
-      <c r="J126" s="183"/>
+      <c r="C126" s="176"/>
+      <c r="D126" s="176"/>
+      <c r="E126" s="176"/>
+      <c r="F126" s="176"/>
+      <c r="G126" s="167"/>
+      <c r="H126" s="167"/>
+      <c r="I126" s="167"/>
+      <c r="J126" s="167"/>
     </row>
     <row r="127" spans="2:14">
       <c r="B127" s="29">
         <v>9</v>
       </c>
-      <c r="C127" s="192"/>
-      <c r="D127" s="192"/>
-      <c r="E127" s="192"/>
-      <c r="F127" s="192"/>
-      <c r="G127" s="183"/>
-      <c r="H127" s="183"/>
-      <c r="I127" s="183"/>
-      <c r="J127" s="183"/>
+      <c r="C127" s="176"/>
+      <c r="D127" s="176"/>
+      <c r="E127" s="176"/>
+      <c r="F127" s="176"/>
+      <c r="G127" s="167"/>
+      <c r="H127" s="167"/>
+      <c r="I127" s="167"/>
+      <c r="J127" s="167"/>
     </row>
     <row r="128" spans="2:14">
       <c r="B128" s="29">
         <v>10</v>
       </c>
-      <c r="C128" s="192"/>
-      <c r="D128" s="192"/>
-      <c r="E128" s="192"/>
-      <c r="F128" s="192"/>
-      <c r="G128" s="183"/>
-      <c r="H128" s="183"/>
-      <c r="I128" s="183"/>
-      <c r="J128" s="183"/>
+      <c r="C128" s="176"/>
+      <c r="D128" s="176"/>
+      <c r="E128" s="176"/>
+      <c r="F128" s="176"/>
+      <c r="G128" s="167"/>
+      <c r="H128" s="167"/>
+      <c r="I128" s="167"/>
+      <c r="J128" s="167"/>
     </row>
     <row r="129" spans="2:10">
-      <c r="B129" s="196" t="s">
+      <c r="B129" s="180" t="s">
         <v>98</v>
       </c>
-      <c r="C129" s="197"/>
-      <c r="D129" s="197"/>
-      <c r="E129" s="197"/>
-      <c r="F129" s="197"/>
-      <c r="G129" s="197"/>
-      <c r="H129" s="197"/>
-      <c r="I129" s="197"/>
-      <c r="J129" s="197"/>
+      <c r="C129" s="181"/>
+      <c r="D129" s="181"/>
+      <c r="E129" s="181"/>
+      <c r="F129" s="181"/>
+      <c r="G129" s="181"/>
+      <c r="H129" s="181"/>
+      <c r="I129" s="181"/>
+      <c r="J129" s="181"/>
     </row>
     <row r="130" spans="2:10">
-      <c r="B130" s="198"/>
-      <c r="C130" s="198"/>
-      <c r="D130" s="198"/>
-      <c r="E130" s="198"/>
-      <c r="F130" s="198"/>
-      <c r="G130" s="198"/>
-      <c r="H130" s="198"/>
-      <c r="I130" s="198"/>
-      <c r="J130" s="198"/>
+      <c r="B130" s="182"/>
+      <c r="C130" s="182"/>
+      <c r="D130" s="182"/>
+      <c r="E130" s="182"/>
+      <c r="F130" s="182"/>
+      <c r="G130" s="182"/>
+      <c r="H130" s="182"/>
+      <c r="I130" s="182"/>
+      <c r="J130" s="182"/>
     </row>
     <row r="131" spans="2:10" ht="33" customHeight="1">
       <c r="B131" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C131" s="193" t="s">
+      <c r="C131" s="177" t="s">
         <v>68</v>
       </c>
-      <c r="D131" s="193"/>
-      <c r="E131" s="193" t="s">
+      <c r="D131" s="177"/>
+      <c r="E131" s="177" t="s">
         <v>69</v>
       </c>
-      <c r="F131" s="193"/>
-      <c r="G131" s="193" t="s">
+      <c r="F131" s="177"/>
+      <c r="G131" s="177" t="s">
         <v>71</v>
       </c>
-      <c r="H131" s="193"/>
-      <c r="I131" s="193" t="s">
+      <c r="H131" s="177"/>
+      <c r="I131" s="177" t="s">
         <v>72</v>
       </c>
-      <c r="J131" s="193"/>
+      <c r="J131" s="177"/>
     </row>
     <row r="132" spans="2:10">
       <c r="B132" s="29">
         <v>1</v>
       </c>
-      <c r="C132" s="180">
+      <c r="C132" s="164">
         <f>Calculation!G58*3600</f>
         <v>0</v>
       </c>
-      <c r="D132" s="180"/>
-      <c r="E132" s="180" t="e">
+      <c r="D132" s="164"/>
+      <c r="E132" s="164" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F132" s="180"/>
-      <c r="G132" s="182" t="e">
+      <c r="F132" s="164"/>
+      <c r="G132" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H132" s="183"/>
-      <c r="I132" s="182" t="e">
+      <c r="H132" s="167"/>
+      <c r="I132" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J132" s="183"/>
+      <c r="J132" s="167"/>
     </row>
     <row r="133" spans="2:10">
       <c r="B133" s="29">
         <v>2</v>
       </c>
-      <c r="C133" s="180">
+      <c r="C133" s="164">
         <f>Calculation!G59*3600</f>
         <v>0</v>
       </c>
-      <c r="D133" s="180"/>
-      <c r="E133" s="180" t="e">
+      <c r="D133" s="164"/>
+      <c r="E133" s="164" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F133" s="180"/>
-      <c r="G133" s="182" t="e">
+      <c r="F133" s="164"/>
+      <c r="G133" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H133" s="183"/>
-      <c r="I133" s="182" t="e">
+      <c r="H133" s="167"/>
+      <c r="I133" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J133" s="183"/>
+      <c r="J133" s="167"/>
     </row>
     <row r="134" spans="2:10">
       <c r="B134" s="29">
         <v>3</v>
       </c>
-      <c r="C134" s="180">
+      <c r="C134" s="164">
         <f>Calculation!G60*3600</f>
         <v>0</v>
       </c>
-      <c r="D134" s="180"/>
-      <c r="E134" s="180" t="e">
+      <c r="D134" s="164"/>
+      <c r="E134" s="164" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F134" s="180"/>
-      <c r="G134" s="182" t="e">
+      <c r="F134" s="164"/>
+      <c r="G134" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H134" s="183"/>
-      <c r="I134" s="182" t="e">
+      <c r="H134" s="167"/>
+      <c r="I134" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J134" s="183"/>
+      <c r="J134" s="167"/>
     </row>
     <row r="135" spans="2:10">
       <c r="B135" s="29">
         <v>4</v>
       </c>
-      <c r="C135" s="180">
+      <c r="C135" s="164">
         <f>Calculation!G61*3600</f>
         <v>0</v>
       </c>
-      <c r="D135" s="180"/>
-      <c r="E135" s="180" t="e">
+      <c r="D135" s="164"/>
+      <c r="E135" s="164" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F135" s="180"/>
-      <c r="G135" s="182" t="e">
+      <c r="F135" s="164"/>
+      <c r="G135" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H135" s="183"/>
-      <c r="I135" s="182" t="e">
+      <c r="H135" s="167"/>
+      <c r="I135" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J135" s="183"/>
+      <c r="J135" s="167"/>
     </row>
     <row r="136" spans="2:10">
       <c r="B136" s="29">
         <v>5</v>
       </c>
-      <c r="C136" s="180">
+      <c r="C136" s="164">
         <f>Calculation!G62*3600</f>
         <v>0</v>
       </c>
-      <c r="D136" s="180"/>
-      <c r="E136" s="180">
+      <c r="D136" s="164"/>
+      <c r="E136" s="164">
         <f>Calculation!G119</f>
         <v>0</v>
       </c>
-      <c r="F136" s="180"/>
-      <c r="G136" s="182" t="e">
+      <c r="F136" s="164"/>
+      <c r="G136" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H136" s="183"/>
-      <c r="I136" s="182" t="e">
+      <c r="H136" s="167"/>
+      <c r="I136" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J136" s="183"/>
+      <c r="J136" s="167"/>
     </row>
     <row r="137" spans="2:10">
       <c r="B137" s="29">
         <v>6</v>
       </c>
-      <c r="C137" s="180">
+      <c r="C137" s="164">
         <f>Calculation!G63*3600</f>
         <v>0</v>
       </c>
-      <c r="D137" s="180"/>
-      <c r="E137" s="180">
+      <c r="D137" s="164"/>
+      <c r="E137" s="164">
         <f>Calculation!G120</f>
         <v>0</v>
       </c>
-      <c r="F137" s="180"/>
-      <c r="G137" s="182" t="e">
+      <c r="F137" s="164"/>
+      <c r="G137" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H137" s="183"/>
-      <c r="I137" s="182" t="e">
+      <c r="H137" s="167"/>
+      <c r="I137" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J137" s="183"/>
+      <c r="J137" s="167"/>
     </row>
     <row r="138" spans="2:10">
       <c r="B138" s="29">
         <v>7</v>
       </c>
-      <c r="C138" s="180">
+      <c r="C138" s="164">
         <f>Calculation!G64*3600</f>
         <v>0</v>
       </c>
-      <c r="D138" s="180"/>
-      <c r="E138" s="180">
+      <c r="D138" s="164"/>
+      <c r="E138" s="164">
         <f>Calculation!G121</f>
         <v>0</v>
       </c>
-      <c r="F138" s="180"/>
-      <c r="G138" s="182" t="e">
+      <c r="F138" s="164"/>
+      <c r="G138" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H138" s="183"/>
-      <c r="I138" s="182" t="e">
+      <c r="H138" s="167"/>
+      <c r="I138" s="166" t="e">
         <f>Calculation!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J138" s="183"/>
+      <c r="J138" s="167"/>
     </row>
     <row r="139" spans="2:10">
       <c r="B139" s="29">
         <v>8</v>
       </c>
-      <c r="C139" s="192"/>
-      <c r="D139" s="192"/>
-      <c r="E139" s="192"/>
-      <c r="F139" s="192"/>
-      <c r="G139" s="183"/>
-      <c r="H139" s="183"/>
-      <c r="I139" s="183"/>
-      <c r="J139" s="183"/>
+      <c r="C139" s="176"/>
+      <c r="D139" s="176"/>
+      <c r="E139" s="176"/>
+      <c r="F139" s="176"/>
+      <c r="G139" s="167"/>
+      <c r="H139" s="167"/>
+      <c r="I139" s="167"/>
+      <c r="J139" s="167"/>
     </row>
     <row r="140" spans="2:10">
       <c r="B140" s="29">
         <v>9</v>
       </c>
-      <c r="C140" s="192"/>
-      <c r="D140" s="192"/>
-      <c r="E140" s="192"/>
-      <c r="F140" s="192"/>
-      <c r="G140" s="183"/>
-      <c r="H140" s="183"/>
-      <c r="I140" s="183"/>
-      <c r="J140" s="183"/>
+      <c r="C140" s="176"/>
+      <c r="D140" s="176"/>
+      <c r="E140" s="176"/>
+      <c r="F140" s="176"/>
+      <c r="G140" s="167"/>
+      <c r="H140" s="167"/>
+      <c r="I140" s="167"/>
+      <c r="J140" s="167"/>
     </row>
     <row r="141" spans="2:10">
       <c r="B141" s="29">
         <v>10</v>
       </c>
-      <c r="C141" s="192"/>
-      <c r="D141" s="192"/>
-      <c r="E141" s="192"/>
-      <c r="F141" s="192"/>
-      <c r="G141" s="183"/>
-      <c r="H141" s="183"/>
-      <c r="I141" s="183"/>
-      <c r="J141" s="183"/>
+      <c r="C141" s="176"/>
+      <c r="D141" s="176"/>
+      <c r="E141" s="176"/>
+      <c r="F141" s="176"/>
+      <c r="G141" s="167"/>
+      <c r="H141" s="167"/>
+      <c r="I141" s="167"/>
+      <c r="J141" s="167"/>
     </row>
     <row r="142" spans="2:10">
       <c r="B142" s="31"/>
@@ -21932,55 +22055,55 @@
     <row r="4" spans="1:14" ht="15" customHeight="1"/>
     <row r="5" spans="1:14" ht="15" customHeight="1"/>
     <row r="6" spans="1:14" ht="18">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="189" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="204"/>
-      <c r="C6" s="204"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="204"/>
-      <c r="I6" s="204"/>
-      <c r="J6" s="204"/>
-      <c r="K6" s="204"/>
-      <c r="L6" s="204"/>
-      <c r="M6" s="204"/>
+      <c r="B6" s="189"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="189"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+      <c r="M6" s="189"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="205" t="s">
+      <c r="A7" s="190" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="205"/>
-      <c r="L7" s="205"/>
-      <c r="M7" s="205"/>
+      <c r="B7" s="190"/>
+      <c r="C7" s="190"/>
+      <c r="D7" s="190"/>
+      <c r="E7" s="190"/>
+      <c r="F7" s="190"/>
+      <c r="G7" s="190"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="190"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="190"/>
+      <c r="L7" s="190"/>
+      <c r="M7" s="190"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="206" t="s">
+      <c r="A8" s="191" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="206"/>
-      <c r="C8" s="206"/>
-      <c r="D8" s="206"/>
-      <c r="E8" s="206"/>
-      <c r="F8" s="206"/>
-      <c r="G8" s="206"/>
-      <c r="H8" s="206"/>
-      <c r="I8" s="206"/>
-      <c r="J8" s="206"/>
-      <c r="K8" s="206"/>
-      <c r="L8" s="206"/>
-      <c r="M8" s="206"/>
+      <c r="B8" s="191"/>
+      <c r="C8" s="191"/>
+      <c r="D8" s="191"/>
+      <c r="E8" s="191"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="191"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="191"/>
+      <c r="J8" s="191"/>
+      <c r="K8" s="191"/>
+      <c r="L8" s="191"/>
+      <c r="M8" s="191"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="59"/>
@@ -21998,147 +22121,147 @@
       <c r="M9" s="59"/>
     </row>
     <row r="11" spans="1:14" ht="21.95" customHeight="1">
-      <c r="A11" s="199" t="s">
+      <c r="A11" s="184" t="s">
         <v>186</v>
       </c>
-      <c r="B11" s="199"/>
-      <c r="C11" s="199"/>
-      <c r="D11" s="199"/>
-      <c r="E11" s="199"/>
-      <c r="F11" s="199"/>
-      <c r="G11" s="199"/>
-      <c r="H11" s="199"/>
-      <c r="I11" s="199"/>
-      <c r="J11" s="199"/>
-      <c r="K11" s="199"/>
-      <c r="L11" s="199"/>
-      <c r="M11" s="199"/>
-      <c r="N11" s="199"/>
+      <c r="B11" s="184"/>
+      <c r="C11" s="184"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="184"/>
+      <c r="K11" s="184"/>
+      <c r="L11" s="184"/>
+      <c r="M11" s="184"/>
+      <c r="N11" s="184"/>
     </row>
     <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="200" t="s">
+      <c r="A12" s="185" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="200"/>
-      <c r="C12" s="209"/>
-      <c r="D12" s="209"/>
-      <c r="E12" s="209"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="194"/>
+      <c r="D12" s="194"/>
+      <c r="E12" s="194"/>
       <c r="F12" s="38"/>
-      <c r="G12" s="201" t="s">
+      <c r="G12" s="186" t="s">
         <v>192</v>
       </c>
-      <c r="H12" s="201"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="201"/>
-      <c r="K12" s="201"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="116"/>
-      <c r="N12" s="116"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="186"/>
+      <c r="L12" s="240"/>
+      <c r="M12" s="240"/>
+      <c r="N12" s="240"/>
     </row>
     <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="200" t="s">
+      <c r="A13" s="185" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="200"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
       <c r="F13" s="41"/>
-      <c r="G13" s="202" t="s">
+      <c r="G13" s="187" t="s">
         <v>193</v>
       </c>
-      <c r="H13" s="202"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="202"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="116"/>
-      <c r="M13" s="116"/>
-      <c r="N13" s="116"/>
+      <c r="H13" s="187"/>
+      <c r="I13" s="187"/>
+      <c r="J13" s="187"/>
+      <c r="K13" s="187"/>
+      <c r="L13" s="240"/>
+      <c r="M13" s="240"/>
+      <c r="N13" s="240"/>
     </row>
     <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="208" t="s">
+      <c r="A14" s="193" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="208"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
       <c r="F14" s="37"/>
-      <c r="G14" s="202" t="s">
+      <c r="G14" s="187" t="s">
         <v>194</v>
       </c>
-      <c r="H14" s="202"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="116"/>
-      <c r="M14" s="116"/>
-      <c r="N14" s="116"/>
+      <c r="H14" s="187"/>
+      <c r="I14" s="187"/>
+      <c r="J14" s="187"/>
+      <c r="K14" s="187"/>
+      <c r="L14" s="240"/>
+      <c r="M14" s="240"/>
+      <c r="N14" s="240"/>
     </row>
     <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="208" t="s">
+      <c r="A15" s="193" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="208"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="195"/>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195"/>
       <c r="F15" s="37"/>
-      <c r="G15" s="200" t="s">
+      <c r="G15" s="185" t="s">
         <v>195</v>
       </c>
-      <c r="H15" s="200"/>
-      <c r="I15" s="200"/>
-      <c r="J15" s="200"/>
-      <c r="K15" s="200"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="116"/>
+      <c r="H15" s="185"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="240"/>
+      <c r="M15" s="240"/>
+      <c r="N15" s="240"/>
     </row>
     <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="208" t="s">
+      <c r="A16" s="193" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="208"/>
-      <c r="C16" s="207"/>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="200" t="s">
+      <c r="B16" s="193"/>
+      <c r="C16" s="192"/>
+      <c r="D16" s="192"/>
+      <c r="E16" s="192"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="185" t="s">
         <v>196</v>
       </c>
-      <c r="H16" s="200"/>
-      <c r="I16" s="200"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="200"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="116"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="185"/>
+      <c r="L16" s="183"/>
+      <c r="M16" s="183"/>
+      <c r="N16" s="183"/>
     </row>
     <row r="17" spans="1:13" ht="21.95" customHeight="1"/>
     <row r="18" spans="1:13" ht="30" customHeight="1">
-      <c r="A18" s="218" t="s">
+      <c r="A18" s="203" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="218"/>
-      <c r="C18" s="218"/>
-      <c r="D18" s="218"/>
-      <c r="E18" s="218"/>
-      <c r="F18" s="218"/>
-      <c r="G18" s="218"/>
-      <c r="H18" s="218"/>
-      <c r="I18" s="218"/>
-      <c r="J18" s="218"/>
-      <c r="K18" s="218"/>
-      <c r="L18" s="218"/>
-      <c r="M18" s="218"/>
+      <c r="B18" s="203"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="203"/>
+      <c r="H18" s="203"/>
+      <c r="I18" s="203"/>
+      <c r="J18" s="203"/>
+      <c r="K18" s="203"/>
+      <c r="L18" s="203"/>
+      <c r="M18" s="203"/>
     </row>
     <row r="19" spans="1:13" ht="30" customHeight="1">
-      <c r="A19" s="217" t="s">
+      <c r="A19" s="202" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="217"/>
-      <c r="C19" s="73" t="s">
+      <c r="B19" s="202"/>
+      <c r="C19" s="72" t="s">
         <v>151</v>
       </c>
       <c r="D19" s="42">
@@ -22173,143 +22296,143 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A20" s="211" t="s">
+      <c r="A20" s="196" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="211"/>
-      <c r="C20" s="74" t="s">
+      <c r="B20" s="196"/>
+      <c r="C20" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="75"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="75"/>
-      <c r="L20" s="75"/>
-      <c r="M20" s="75"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="74"/>
     </row>
     <row r="21" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A21" s="211" t="s">
+      <c r="A21" s="196" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="211"/>
-      <c r="C21" s="74" t="s">
+      <c r="B21" s="196"/>
+      <c r="C21" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="75"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="75"/>
-      <c r="M21" s="75"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
     </row>
     <row r="22" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A22" s="211" t="s">
+      <c r="A22" s="196" t="s">
         <v>154</v>
       </c>
-      <c r="B22" s="211"/>
-      <c r="C22" s="74" t="s">
+      <c r="B22" s="196"/>
+      <c r="C22" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
     </row>
     <row r="23" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A23" s="211" t="s">
+      <c r="A23" s="196" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="211"/>
-      <c r="C23" s="74" t="s">
+      <c r="B23" s="196"/>
+      <c r="C23" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="75"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="75"/>
     </row>
     <row r="24" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A24" s="211" t="s">
+      <c r="A24" s="196" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="211"/>
-      <c r="C24" s="74" t="s">
+      <c r="B24" s="196"/>
+      <c r="C24" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
     </row>
     <row r="25" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A25" s="211" t="s">
+      <c r="A25" s="196" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="211"/>
-      <c r="C25" s="74" t="s">
+      <c r="B25" s="196"/>
+      <c r="C25" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
     </row>
     <row r="26" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A26" s="203"/>
-      <c r="B26" s="203"/>
+      <c r="A26" s="188"/>
+      <c r="B26" s="188"/>
     </row>
     <row r="27" spans="1:13" ht="24.95" customHeight="1"/>
     <row r="28" spans="1:13" ht="24.95" customHeight="1"/>
     <row r="29" spans="1:13" ht="24.95" customHeight="1"/>
     <row r="30" spans="1:13" ht="24.95" customHeight="1"/>
     <row r="32" spans="1:13">
-      <c r="A32" s="213" t="s">
+      <c r="A32" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="213"/>
-      <c r="C32" s="213"/>
-      <c r="D32" s="213"/>
-      <c r="E32" s="213"/>
-      <c r="F32" s="213"/>
-      <c r="G32" s="213"/>
-      <c r="H32" s="213"/>
-      <c r="I32" s="213"/>
-      <c r="J32" s="213"/>
-      <c r="K32" s="213"/>
-      <c r="L32" s="213"/>
-      <c r="M32" s="213"/>
+      <c r="B32" s="198"/>
+      <c r="C32" s="198"/>
+      <c r="D32" s="198"/>
+      <c r="E32" s="198"/>
+      <c r="F32" s="198"/>
+      <c r="G32" s="198"/>
+      <c r="H32" s="198"/>
+      <c r="I32" s="198"/>
+      <c r="J32" s="198"/>
+      <c r="K32" s="198"/>
+      <c r="L32" s="198"/>
+      <c r="M32" s="198"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="36"/>
@@ -22705,106 +22828,106 @@
       <c r="A59" s="46"/>
       <c r="B59" s="46"/>
       <c r="C59" s="46"/>
-      <c r="D59" s="212"/>
-      <c r="E59" s="212"/>
-      <c r="F59" s="212"/>
-      <c r="G59" s="212"/>
+      <c r="D59" s="197"/>
+      <c r="E59" s="197"/>
+      <c r="F59" s="197"/>
+      <c r="G59" s="197"/>
       <c r="H59" s="47"/>
-      <c r="I59" s="212"/>
-      <c r="J59" s="212"/>
-      <c r="K59" s="212"/>
-      <c r="L59" s="212"/>
-      <c r="M59" s="212"/>
+      <c r="I59" s="197"/>
+      <c r="J59" s="197"/>
+      <c r="K59" s="197"/>
+      <c r="L59" s="197"/>
+      <c r="M59" s="197"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="46"/>
       <c r="B60" s="46"/>
       <c r="C60" s="46"/>
-      <c r="D60" s="212"/>
-      <c r="E60" s="212"/>
-      <c r="F60" s="212"/>
-      <c r="G60" s="212"/>
+      <c r="D60" s="197"/>
+      <c r="E60" s="197"/>
+      <c r="F60" s="197"/>
+      <c r="G60" s="197"/>
       <c r="H60" s="47"/>
-      <c r="I60" s="212"/>
-      <c r="J60" s="212"/>
-      <c r="K60" s="212"/>
-      <c r="L60" s="212"/>
-      <c r="M60" s="212"/>
+      <c r="I60" s="197"/>
+      <c r="J60" s="197"/>
+      <c r="K60" s="197"/>
+      <c r="L60" s="197"/>
+      <c r="M60" s="197"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="46"/>
       <c r="B61" s="46"/>
       <c r="C61" s="46"/>
-      <c r="D61" s="212"/>
-      <c r="E61" s="212"/>
-      <c r="F61" s="212"/>
-      <c r="G61" s="212"/>
+      <c r="D61" s="197"/>
+      <c r="E61" s="197"/>
+      <c r="F61" s="197"/>
+      <c r="G61" s="197"/>
       <c r="H61" s="47"/>
-      <c r="I61" s="212"/>
-      <c r="J61" s="212"/>
-      <c r="K61" s="212"/>
-      <c r="L61" s="212"/>
-      <c r="M61" s="212"/>
+      <c r="I61" s="197"/>
+      <c r="J61" s="197"/>
+      <c r="K61" s="197"/>
+      <c r="L61" s="197"/>
+      <c r="M61" s="197"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="46"/>
       <c r="B62" s="46"/>
       <c r="C62" s="46"/>
-      <c r="D62" s="212"/>
-      <c r="E62" s="212"/>
-      <c r="F62" s="212"/>
-      <c r="G62" s="212"/>
+      <c r="D62" s="197"/>
+      <c r="E62" s="197"/>
+      <c r="F62" s="197"/>
+      <c r="G62" s="197"/>
       <c r="H62" s="47"/>
-      <c r="I62" s="212"/>
-      <c r="J62" s="212"/>
-      <c r="K62" s="212"/>
-      <c r="L62" s="212"/>
-      <c r="M62" s="212"/>
+      <c r="I62" s="197"/>
+      <c r="J62" s="197"/>
+      <c r="K62" s="197"/>
+      <c r="L62" s="197"/>
+      <c r="M62" s="197"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="46"/>
       <c r="B63" s="46"/>
       <c r="C63" s="46"/>
-      <c r="D63" s="212"/>
-      <c r="E63" s="212"/>
-      <c r="F63" s="212"/>
-      <c r="G63" s="212"/>
+      <c r="D63" s="197"/>
+      <c r="E63" s="197"/>
+      <c r="F63" s="197"/>
+      <c r="G63" s="197"/>
       <c r="H63" s="47"/>
-      <c r="I63" s="212"/>
-      <c r="J63" s="212"/>
-      <c r="K63" s="212"/>
-      <c r="L63" s="212"/>
-      <c r="M63" s="212"/>
+      <c r="I63" s="197"/>
+      <c r="J63" s="197"/>
+      <c r="K63" s="197"/>
+      <c r="L63" s="197"/>
+      <c r="M63" s="197"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="46"/>
       <c r="B64" s="46"/>
       <c r="C64" s="46"/>
-      <c r="D64" s="212"/>
-      <c r="E64" s="212"/>
-      <c r="F64" s="212"/>
-      <c r="G64" s="212"/>
+      <c r="D64" s="197"/>
+      <c r="E64" s="197"/>
+      <c r="F64" s="197"/>
+      <c r="G64" s="197"/>
       <c r="H64" s="47"/>
-      <c r="I64" s="212"/>
-      <c r="J64" s="212"/>
-      <c r="K64" s="212"/>
-      <c r="L64" s="212"/>
-      <c r="M64" s="212"/>
+      <c r="I64" s="197"/>
+      <c r="J64" s="197"/>
+      <c r="K64" s="197"/>
+      <c r="L64" s="197"/>
+      <c r="M64" s="197"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="46"/>
       <c r="B65" s="46"/>
       <c r="C65" s="46"/>
-      <c r="D65" s="212"/>
-      <c r="E65" s="212"/>
-      <c r="F65" s="212"/>
-      <c r="G65" s="212"/>
+      <c r="D65" s="197"/>
+      <c r="E65" s="197"/>
+      <c r="F65" s="197"/>
+      <c r="G65" s="197"/>
       <c r="H65" s="47"/>
-      <c r="I65" s="212"/>
-      <c r="J65" s="212"/>
-      <c r="K65" s="212"/>
-      <c r="L65" s="212"/>
-      <c r="M65" s="212"/>
+      <c r="I65" s="197"/>
+      <c r="J65" s="197"/>
+      <c r="K65" s="197"/>
+      <c r="L65" s="197"/>
+      <c r="M65" s="197"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="36"/>
@@ -22882,21 +23005,21 @@
       <c r="M70" s="36"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="213" t="s">
+      <c r="A71" s="198" t="s">
         <v>113</v>
       </c>
-      <c r="B71" s="213"/>
-      <c r="C71" s="213"/>
-      <c r="D71" s="213"/>
-      <c r="E71" s="213"/>
-      <c r="F71" s="213"/>
-      <c r="G71" s="213"/>
-      <c r="H71" s="213"/>
-      <c r="I71" s="213"/>
-      <c r="J71" s="213"/>
-      <c r="K71" s="213"/>
-      <c r="L71" s="213"/>
-      <c r="M71" s="213"/>
+      <c r="B71" s="198"/>
+      <c r="C71" s="198"/>
+      <c r="D71" s="198"/>
+      <c r="E71" s="198"/>
+      <c r="F71" s="198"/>
+      <c r="G71" s="198"/>
+      <c r="H71" s="198"/>
+      <c r="I71" s="198"/>
+      <c r="J71" s="198"/>
+      <c r="K71" s="198"/>
+      <c r="L71" s="198"/>
+      <c r="M71" s="198"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="52"/>
@@ -22944,46 +23067,46 @@
       <c r="M74" s="36"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="215" t="s">
+      <c r="A75" s="200" t="s">
         <v>114</v>
       </c>
-      <c r="B75" s="215"/>
-      <c r="C75" s="215"/>
-      <c r="D75" s="215"/>
-      <c r="E75" s="215"/>
-      <c r="F75" s="216" t="s">
+      <c r="B75" s="200"/>
+      <c r="C75" s="200"/>
+      <c r="D75" s="200"/>
+      <c r="E75" s="200"/>
+      <c r="F75" s="201" t="s">
         <v>115</v>
       </c>
-      <c r="G75" s="216"/>
-      <c r="H75" s="216"/>
-      <c r="I75" s="216"/>
-      <c r="J75" s="216"/>
-      <c r="K75" s="216" t="s">
+      <c r="G75" s="201"/>
+      <c r="H75" s="201"/>
+      <c r="I75" s="201"/>
+      <c r="J75" s="201"/>
+      <c r="K75" s="201" t="s">
         <v>116</v>
       </c>
-      <c r="L75" s="216"/>
-      <c r="M75" s="216"/>
+      <c r="L75" s="201"/>
+      <c r="M75" s="201"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="214" t="s">
+      <c r="A76" s="199" t="s">
         <v>117</v>
       </c>
-      <c r="B76" s="214"/>
-      <c r="C76" s="214"/>
-      <c r="D76" s="214"/>
-      <c r="E76" s="214"/>
-      <c r="F76" s="214" t="s">
+      <c r="B76" s="199"/>
+      <c r="C76" s="199"/>
+      <c r="D76" s="199"/>
+      <c r="E76" s="199"/>
+      <c r="F76" s="199" t="s">
         <v>118</v>
       </c>
-      <c r="G76" s="214"/>
-      <c r="H76" s="214"/>
-      <c r="I76" s="214"/>
-      <c r="J76" s="214"/>
-      <c r="K76" s="214" t="s">
+      <c r="G76" s="199"/>
+      <c r="H76" s="199"/>
+      <c r="I76" s="199"/>
+      <c r="J76" s="199"/>
+      <c r="K76" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="L76" s="214"/>
-      <c r="M76" s="214"/>
+      <c r="L76" s="199"/>
+      <c r="M76" s="199"/>
     </row>
     <row r="82" spans="15:27">
       <c r="O82" s="58"/>
@@ -23116,10 +23239,7 @@
       <c r="AA91" s="56"/>
     </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A21:B21"/>
+  <mergeCells count="69">
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A18:M18"/>
@@ -23160,9 +23280,6 @@
     <mergeCell ref="F59:G59"/>
     <mergeCell ref="I59:J59"/>
     <mergeCell ref="K59:M59"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="G16:K16"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A7:M7"/>
@@ -23176,11 +23293,22 @@
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
     <mergeCell ref="A11:N11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="G12:K12"/>
     <mergeCell ref="G13:K13"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="G16:K16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -23202,55 +23330,55 @@
     <row r="4" spans="1:14" ht="15" customHeight="1"/>
     <row r="5" spans="1:14" ht="15" customHeight="1"/>
     <row r="6" spans="1:14" ht="18">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="189" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="204"/>
-      <c r="C6" s="204"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="204"/>
-      <c r="I6" s="204"/>
-      <c r="J6" s="204"/>
-      <c r="K6" s="204"/>
-      <c r="L6" s="204"/>
-      <c r="M6" s="204"/>
+      <c r="B6" s="189"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="189"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+      <c r="M6" s="189"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="205" t="s">
+      <c r="A7" s="190" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="205"/>
-      <c r="L7" s="205"/>
-      <c r="M7" s="205"/>
+      <c r="B7" s="190"/>
+      <c r="C7" s="190"/>
+      <c r="D7" s="190"/>
+      <c r="E7" s="190"/>
+      <c r="F7" s="190"/>
+      <c r="G7" s="190"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="190"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="190"/>
+      <c r="L7" s="190"/>
+      <c r="M7" s="190"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="206" t="s">
+      <c r="A8" s="191" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="206"/>
-      <c r="C8" s="206"/>
-      <c r="D8" s="206"/>
-      <c r="E8" s="206"/>
-      <c r="F8" s="206"/>
-      <c r="G8" s="206"/>
-      <c r="H8" s="206"/>
-      <c r="I8" s="206"/>
-      <c r="J8" s="206"/>
-      <c r="K8" s="206"/>
-      <c r="L8" s="206"/>
-      <c r="M8" s="206"/>
+      <c r="B8" s="191"/>
+      <c r="C8" s="191"/>
+      <c r="D8" s="191"/>
+      <c r="E8" s="191"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="191"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="191"/>
+      <c r="J8" s="191"/>
+      <c r="K8" s="191"/>
+      <c r="L8" s="191"/>
+      <c r="M8" s="191"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="59"/>
@@ -23268,147 +23396,147 @@
       <c r="M9" s="59"/>
     </row>
     <row r="11" spans="1:14" ht="21.95" customHeight="1">
-      <c r="A11" s="199" t="s">
+      <c r="A11" s="184" t="s">
         <v>186</v>
       </c>
-      <c r="B11" s="199"/>
-      <c r="C11" s="199"/>
-      <c r="D11" s="199"/>
-      <c r="E11" s="199"/>
-      <c r="F11" s="199"/>
-      <c r="G11" s="199"/>
-      <c r="H11" s="199"/>
-      <c r="I11" s="199"/>
-      <c r="J11" s="199"/>
-      <c r="K11" s="199"/>
-      <c r="L11" s="199"/>
-      <c r="M11" s="199"/>
-      <c r="N11" s="199"/>
+      <c r="B11" s="184"/>
+      <c r="C11" s="184"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="184"/>
+      <c r="K11" s="184"/>
+      <c r="L11" s="184"/>
+      <c r="M11" s="184"/>
+      <c r="N11" s="184"/>
     </row>
     <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="200" t="s">
+      <c r="A12" s="185" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="200"/>
-      <c r="C12" s="209"/>
-      <c r="D12" s="209"/>
-      <c r="E12" s="209"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="194"/>
+      <c r="D12" s="194"/>
+      <c r="E12" s="194"/>
       <c r="F12" s="38"/>
-      <c r="G12" s="201" t="s">
+      <c r="G12" s="186" t="s">
         <v>192</v>
       </c>
-      <c r="H12" s="201"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="201"/>
-      <c r="K12" s="201"/>
-      <c r="L12" s="219"/>
-      <c r="M12" s="219"/>
-      <c r="N12" s="219"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="186"/>
+      <c r="L12" s="240"/>
+      <c r="M12" s="240"/>
+      <c r="N12" s="240"/>
     </row>
     <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="200" t="s">
+      <c r="A13" s="185" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="200"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
       <c r="F13" s="41"/>
-      <c r="G13" s="202" t="s">
+      <c r="G13" s="187" t="s">
         <v>193</v>
       </c>
-      <c r="H13" s="202"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="202"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="219"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="219"/>
+      <c r="H13" s="187"/>
+      <c r="I13" s="187"/>
+      <c r="J13" s="187"/>
+      <c r="K13" s="187"/>
+      <c r="L13" s="240"/>
+      <c r="M13" s="240"/>
+      <c r="N13" s="240"/>
     </row>
     <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="208" t="s">
+      <c r="A14" s="193" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="208"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
       <c r="F14" s="37"/>
-      <c r="G14" s="202" t="s">
+      <c r="G14" s="187" t="s">
         <v>194</v>
       </c>
-      <c r="H14" s="202"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="219"/>
-      <c r="M14" s="219"/>
-      <c r="N14" s="219"/>
+      <c r="H14" s="187"/>
+      <c r="I14" s="187"/>
+      <c r="J14" s="187"/>
+      <c r="K14" s="187"/>
+      <c r="L14" s="240"/>
+      <c r="M14" s="240"/>
+      <c r="N14" s="240"/>
     </row>
     <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="208" t="s">
+      <c r="A15" s="193" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="208"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="195"/>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195"/>
       <c r="F15" s="37"/>
-      <c r="G15" s="200" t="s">
+      <c r="G15" s="185" t="s">
         <v>195</v>
       </c>
-      <c r="H15" s="200"/>
-      <c r="I15" s="200"/>
-      <c r="J15" s="200"/>
-      <c r="K15" s="200"/>
-      <c r="L15" s="219"/>
-      <c r="M15" s="219"/>
-      <c r="N15" s="219"/>
+      <c r="H15" s="185"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="240"/>
+      <c r="M15" s="240"/>
+      <c r="N15" s="240"/>
     </row>
     <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="208" t="s">
+      <c r="A16" s="193" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="208"/>
-      <c r="C16" s="207"/>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="200" t="s">
+      <c r="B16" s="193"/>
+      <c r="C16" s="192"/>
+      <c r="D16" s="192"/>
+      <c r="E16" s="192"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="185" t="s">
         <v>196</v>
       </c>
-      <c r="H16" s="200"/>
-      <c r="I16" s="200"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="200"/>
-      <c r="L16" s="219"/>
-      <c r="M16" s="219"/>
-      <c r="N16" s="219"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="185"/>
+      <c r="L16" s="183"/>
+      <c r="M16" s="183"/>
+      <c r="N16" s="183"/>
     </row>
     <row r="17" spans="1:13" ht="21.95" customHeight="1"/>
     <row r="18" spans="1:13" ht="30" customHeight="1">
-      <c r="A18" s="218" t="s">
+      <c r="A18" s="203" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="218"/>
-      <c r="C18" s="218"/>
-      <c r="D18" s="218"/>
-      <c r="E18" s="218"/>
-      <c r="F18" s="218"/>
-      <c r="G18" s="218"/>
-      <c r="H18" s="218"/>
-      <c r="I18" s="218"/>
-      <c r="J18" s="218"/>
-      <c r="K18" s="218"/>
-      <c r="L18" s="218"/>
-      <c r="M18" s="218"/>
+      <c r="B18" s="203"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="203"/>
+      <c r="H18" s="203"/>
+      <c r="I18" s="203"/>
+      <c r="J18" s="203"/>
+      <c r="K18" s="203"/>
+      <c r="L18" s="203"/>
+      <c r="M18" s="203"/>
     </row>
     <row r="19" spans="1:13" ht="30" customHeight="1">
-      <c r="A19" s="217" t="s">
+      <c r="A19" s="202" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="217"/>
-      <c r="C19" s="73" t="s">
+      <c r="B19" s="202"/>
+      <c r="C19" s="72" t="s">
         <v>151</v>
       </c>
       <c r="D19" s="42">
@@ -23443,125 +23571,125 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A20" s="211" t="s">
+      <c r="A20" s="196" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="211"/>
-      <c r="C20" s="74" t="s">
+      <c r="B20" s="196"/>
+      <c r="C20" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="D20" s="75"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="75"/>
-      <c r="L20" s="75"/>
-      <c r="M20" s="75"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="74"/>
     </row>
     <row r="21" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A21" s="211" t="s">
+      <c r="A21" s="196" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="211"/>
-      <c r="C21" s="74" t="s">
+      <c r="B21" s="196"/>
+      <c r="C21" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="75"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="75"/>
-      <c r="M21" s="75"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
     </row>
     <row r="22" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A22" s="211" t="s">
+      <c r="A22" s="196" t="s">
         <v>154</v>
       </c>
-      <c r="B22" s="211"/>
-      <c r="C22" s="74" t="s">
+      <c r="B22" s="196"/>
+      <c r="C22" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
     </row>
     <row r="23" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A23" s="211" t="s">
+      <c r="A23" s="196" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="211"/>
-      <c r="C23" s="74" t="s">
+      <c r="B23" s="196"/>
+      <c r="C23" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="75"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="75"/>
     </row>
     <row r="24" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A24" s="211" t="s">
+      <c r="A24" s="196" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="211"/>
-      <c r="C24" s="74" t="s">
+      <c r="B24" s="196"/>
+      <c r="C24" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
     </row>
     <row r="25" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A25" s="211" t="s">
+      <c r="A25" s="196" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="211"/>
-      <c r="C25" s="74" t="s">
+      <c r="B25" s="196"/>
+      <c r="C25" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
     </row>
     <row r="26" spans="1:13" ht="17.45" customHeight="1">
-      <c r="A26" s="203"/>
-      <c r="B26" s="203"/>
+      <c r="A26" s="188"/>
+      <c r="B26" s="188"/>
     </row>
     <row r="27" spans="1:13" ht="17.45" customHeight="1">
-      <c r="A27" s="110" t="s">
+      <c r="A27" s="106" t="s">
         <v>180</v>
       </c>
     </row>
@@ -23569,28 +23697,28 @@
       <c r="A28" s="39"/>
     </row>
     <row r="29" spans="1:13" ht="17.45" customHeight="1">
-      <c r="A29" s="111"/>
+      <c r="A29" s="107"/>
     </row>
     <row r="30" spans="1:13" ht="17.45" customHeight="1"/>
     <row r="31" spans="1:13" ht="17.45" customHeight="1"/>
     <row r="32" spans="1:13" ht="17.45" customHeight="1"/>
     <row r="33" spans="1:13" ht="17.45" customHeight="1"/>
     <row r="34" spans="1:13">
-      <c r="A34" s="213" t="s">
+      <c r="A34" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="B34" s="213"/>
-      <c r="C34" s="213"/>
-      <c r="D34" s="213"/>
-      <c r="E34" s="213"/>
-      <c r="F34" s="213"/>
-      <c r="G34" s="213"/>
-      <c r="H34" s="213"/>
-      <c r="I34" s="213"/>
-      <c r="J34" s="213"/>
-      <c r="K34" s="213"/>
-      <c r="L34" s="213"/>
-      <c r="M34" s="213"/>
+      <c r="B34" s="198"/>
+      <c r="C34" s="198"/>
+      <c r="D34" s="198"/>
+      <c r="E34" s="198"/>
+      <c r="F34" s="198"/>
+      <c r="G34" s="198"/>
+      <c r="H34" s="198"/>
+      <c r="I34" s="198"/>
+      <c r="J34" s="198"/>
+      <c r="K34" s="198"/>
+      <c r="L34" s="198"/>
+      <c r="M34" s="198"/>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="36"/>
@@ -23986,106 +24114,106 @@
       <c r="A61" s="46"/>
       <c r="B61" s="46"/>
       <c r="C61" s="46"/>
-      <c r="D61" s="212"/>
-      <c r="E61" s="212"/>
-      <c r="F61" s="212"/>
-      <c r="G61" s="212"/>
+      <c r="D61" s="197"/>
+      <c r="E61" s="197"/>
+      <c r="F61" s="197"/>
+      <c r="G61" s="197"/>
       <c r="H61" s="47"/>
-      <c r="I61" s="212"/>
-      <c r="J61" s="212"/>
-      <c r="K61" s="212"/>
-      <c r="L61" s="212"/>
-      <c r="M61" s="212"/>
+      <c r="I61" s="197"/>
+      <c r="J61" s="197"/>
+      <c r="K61" s="197"/>
+      <c r="L61" s="197"/>
+      <c r="M61" s="197"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="46"/>
       <c r="B62" s="46"/>
       <c r="C62" s="46"/>
-      <c r="D62" s="212"/>
-      <c r="E62" s="212"/>
-      <c r="F62" s="212"/>
-      <c r="G62" s="212"/>
+      <c r="D62" s="197"/>
+      <c r="E62" s="197"/>
+      <c r="F62" s="197"/>
+      <c r="G62" s="197"/>
       <c r="H62" s="47"/>
-      <c r="I62" s="212"/>
-      <c r="J62" s="212"/>
-      <c r="K62" s="212"/>
-      <c r="L62" s="212"/>
-      <c r="M62" s="212"/>
+      <c r="I62" s="197"/>
+      <c r="J62" s="197"/>
+      <c r="K62" s="197"/>
+      <c r="L62" s="197"/>
+      <c r="M62" s="197"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="46"/>
       <c r="B63" s="46"/>
       <c r="C63" s="46"/>
-      <c r="D63" s="212"/>
-      <c r="E63" s="212"/>
-      <c r="F63" s="212"/>
-      <c r="G63" s="212"/>
+      <c r="D63" s="197"/>
+      <c r="E63" s="197"/>
+      <c r="F63" s="197"/>
+      <c r="G63" s="197"/>
       <c r="H63" s="47"/>
-      <c r="I63" s="212"/>
-      <c r="J63" s="212"/>
-      <c r="K63" s="212"/>
-      <c r="L63" s="212"/>
-      <c r="M63" s="212"/>
+      <c r="I63" s="197"/>
+      <c r="J63" s="197"/>
+      <c r="K63" s="197"/>
+      <c r="L63" s="197"/>
+      <c r="M63" s="197"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="46"/>
       <c r="B64" s="46"/>
       <c r="C64" s="46"/>
-      <c r="D64" s="212"/>
-      <c r="E64" s="212"/>
-      <c r="F64" s="212"/>
-      <c r="G64" s="212"/>
+      <c r="D64" s="197"/>
+      <c r="E64" s="197"/>
+      <c r="F64" s="197"/>
+      <c r="G64" s="197"/>
       <c r="H64" s="47"/>
-      <c r="I64" s="212"/>
-      <c r="J64" s="212"/>
-      <c r="K64" s="212"/>
-      <c r="L64" s="212"/>
-      <c r="M64" s="212"/>
+      <c r="I64" s="197"/>
+      <c r="J64" s="197"/>
+      <c r="K64" s="197"/>
+      <c r="L64" s="197"/>
+      <c r="M64" s="197"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="46"/>
       <c r="B65" s="46"/>
       <c r="C65" s="46"/>
-      <c r="D65" s="212"/>
-      <c r="E65" s="212"/>
-      <c r="F65" s="212"/>
-      <c r="G65" s="212"/>
+      <c r="D65" s="197"/>
+      <c r="E65" s="197"/>
+      <c r="F65" s="197"/>
+      <c r="G65" s="197"/>
       <c r="H65" s="47"/>
-      <c r="I65" s="212"/>
-      <c r="J65" s="212"/>
-      <c r="K65" s="212"/>
-      <c r="L65" s="212"/>
-      <c r="M65" s="212"/>
+      <c r="I65" s="197"/>
+      <c r="J65" s="197"/>
+      <c r="K65" s="197"/>
+      <c r="L65" s="197"/>
+      <c r="M65" s="197"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="46"/>
       <c r="B66" s="46"/>
       <c r="C66" s="46"/>
-      <c r="D66" s="212"/>
-      <c r="E66" s="212"/>
-      <c r="F66" s="212"/>
-      <c r="G66" s="212"/>
+      <c r="D66" s="197"/>
+      <c r="E66" s="197"/>
+      <c r="F66" s="197"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="47"/>
-      <c r="I66" s="212"/>
-      <c r="J66" s="212"/>
-      <c r="K66" s="212"/>
-      <c r="L66" s="212"/>
-      <c r="M66" s="212"/>
+      <c r="I66" s="197"/>
+      <c r="J66" s="197"/>
+      <c r="K66" s="197"/>
+      <c r="L66" s="197"/>
+      <c r="M66" s="197"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="46"/>
       <c r="B67" s="46"/>
       <c r="C67" s="46"/>
-      <c r="D67" s="212"/>
-      <c r="E67" s="212"/>
-      <c r="F67" s="212"/>
-      <c r="G67" s="212"/>
+      <c r="D67" s="197"/>
+      <c r="E67" s="197"/>
+      <c r="F67" s="197"/>
+      <c r="G67" s="197"/>
       <c r="H67" s="47"/>
-      <c r="I67" s="212"/>
-      <c r="J67" s="212"/>
-      <c r="K67" s="212"/>
-      <c r="L67" s="212"/>
-      <c r="M67" s="212"/>
+      <c r="I67" s="197"/>
+      <c r="J67" s="197"/>
+      <c r="K67" s="197"/>
+      <c r="L67" s="197"/>
+      <c r="M67" s="197"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="36"/>
@@ -24163,21 +24291,21 @@
       <c r="M72" s="36"/>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="213" t="s">
+      <c r="A73" s="198" t="s">
         <v>113</v>
       </c>
-      <c r="B73" s="213"/>
-      <c r="C73" s="213"/>
-      <c r="D73" s="213"/>
-      <c r="E73" s="213"/>
-      <c r="F73" s="213"/>
-      <c r="G73" s="213"/>
-      <c r="H73" s="213"/>
-      <c r="I73" s="213"/>
-      <c r="J73" s="213"/>
-      <c r="K73" s="213"/>
-      <c r="L73" s="213"/>
-      <c r="M73" s="213"/>
+      <c r="B73" s="198"/>
+      <c r="C73" s="198"/>
+      <c r="D73" s="198"/>
+      <c r="E73" s="198"/>
+      <c r="F73" s="198"/>
+      <c r="G73" s="198"/>
+      <c r="H73" s="198"/>
+      <c r="I73" s="198"/>
+      <c r="J73" s="198"/>
+      <c r="K73" s="198"/>
+      <c r="L73" s="198"/>
+      <c r="M73" s="198"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="52"/>
@@ -24225,46 +24353,46 @@
       <c r="M76" s="36"/>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="215" t="s">
+      <c r="A77" s="200" t="s">
         <v>114</v>
       </c>
-      <c r="B77" s="215"/>
-      <c r="C77" s="215"/>
-      <c r="D77" s="215"/>
-      <c r="E77" s="215"/>
-      <c r="F77" s="216" t="s">
+      <c r="B77" s="200"/>
+      <c r="C77" s="200"/>
+      <c r="D77" s="200"/>
+      <c r="E77" s="200"/>
+      <c r="F77" s="201" t="s">
         <v>115</v>
       </c>
-      <c r="G77" s="216"/>
-      <c r="H77" s="216"/>
-      <c r="I77" s="216"/>
-      <c r="J77" s="216"/>
-      <c r="K77" s="216" t="s">
+      <c r="G77" s="201"/>
+      <c r="H77" s="201"/>
+      <c r="I77" s="201"/>
+      <c r="J77" s="201"/>
+      <c r="K77" s="201" t="s">
         <v>116</v>
       </c>
-      <c r="L77" s="216"/>
-      <c r="M77" s="216"/>
+      <c r="L77" s="201"/>
+      <c r="M77" s="201"/>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" s="214" t="s">
+      <c r="A78" s="199" t="s">
         <v>117</v>
       </c>
-      <c r="B78" s="214"/>
-      <c r="C78" s="214"/>
-      <c r="D78" s="214"/>
-      <c r="E78" s="214"/>
-      <c r="F78" s="214" t="s">
+      <c r="B78" s="199"/>
+      <c r="C78" s="199"/>
+      <c r="D78" s="199"/>
+      <c r="E78" s="199"/>
+      <c r="F78" s="199" t="s">
         <v>118</v>
       </c>
-      <c r="G78" s="214"/>
-      <c r="H78" s="214"/>
-      <c r="I78" s="214"/>
-      <c r="J78" s="214"/>
-      <c r="K78" s="214" t="s">
+      <c r="G78" s="199"/>
+      <c r="H78" s="199"/>
+      <c r="I78" s="199"/>
+      <c r="J78" s="199"/>
+      <c r="K78" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="L78" s="214"/>
-      <c r="M78" s="214"/>
+      <c r="L78" s="199"/>
+      <c r="M78" s="199"/>
     </row>
     <row r="84" spans="15:27">
       <c r="O84" s="58"/>
@@ -24488,55 +24616,55 @@
     <row r="4" spans="1:14" ht="15" customHeight="1"/>
     <row r="5" spans="1:14" ht="15" customHeight="1"/>
     <row r="6" spans="1:14" ht="18">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="189" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="204"/>
-      <c r="C6" s="204"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="204"/>
-      <c r="I6" s="204"/>
-      <c r="J6" s="204"/>
-      <c r="K6" s="204"/>
-      <c r="L6" s="204"/>
-      <c r="M6" s="204"/>
+      <c r="B6" s="189"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="189"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+      <c r="M6" s="189"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="205" t="s">
+      <c r="A7" s="190" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="205"/>
-      <c r="L7" s="205"/>
-      <c r="M7" s="205"/>
+      <c r="B7" s="190"/>
+      <c r="C7" s="190"/>
+      <c r="D7" s="190"/>
+      <c r="E7" s="190"/>
+      <c r="F7" s="190"/>
+      <c r="G7" s="190"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="190"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="190"/>
+      <c r="L7" s="190"/>
+      <c r="M7" s="190"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="206" t="s">
+      <c r="A8" s="191" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="206"/>
-      <c r="C8" s="206"/>
-      <c r="D8" s="206"/>
-      <c r="E8" s="206"/>
-      <c r="F8" s="206"/>
-      <c r="G8" s="206"/>
-      <c r="H8" s="206"/>
-      <c r="I8" s="206"/>
-      <c r="J8" s="206"/>
-      <c r="K8" s="206"/>
-      <c r="L8" s="206"/>
-      <c r="M8" s="206"/>
+      <c r="B8" s="191"/>
+      <c r="C8" s="191"/>
+      <c r="D8" s="191"/>
+      <c r="E8" s="191"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="191"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="191"/>
+      <c r="J8" s="191"/>
+      <c r="K8" s="191"/>
+      <c r="L8" s="191"/>
+      <c r="M8" s="191"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="59"/>
@@ -24554,147 +24682,147 @@
       <c r="M9" s="59"/>
     </row>
     <row r="11" spans="1:14" ht="21.95" customHeight="1">
-      <c r="A11" s="199" t="s">
+      <c r="A11" s="184" t="s">
         <v>186</v>
       </c>
-      <c r="B11" s="199"/>
-      <c r="C11" s="199"/>
-      <c r="D11" s="199"/>
-      <c r="E11" s="199"/>
-      <c r="F11" s="199"/>
-      <c r="G11" s="199"/>
-      <c r="H11" s="199"/>
-      <c r="I11" s="199"/>
-      <c r="J11" s="199"/>
-      <c r="K11" s="199"/>
-      <c r="L11" s="199"/>
-      <c r="M11" s="199"/>
-      <c r="N11" s="199"/>
+      <c r="B11" s="184"/>
+      <c r="C11" s="184"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="184"/>
+      <c r="K11" s="184"/>
+      <c r="L11" s="184"/>
+      <c r="M11" s="184"/>
+      <c r="N11" s="184"/>
     </row>
     <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="200" t="s">
+      <c r="A12" s="185" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="200"/>
-      <c r="C12" s="209"/>
-      <c r="D12" s="209"/>
-      <c r="E12" s="209"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="194"/>
+      <c r="D12" s="194"/>
+      <c r="E12" s="194"/>
       <c r="F12" s="38"/>
-      <c r="G12" s="201" t="s">
+      <c r="G12" s="186" t="s">
         <v>192</v>
       </c>
-      <c r="H12" s="201"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="201"/>
-      <c r="K12" s="201"/>
-      <c r="L12" s="219"/>
-      <c r="M12" s="219"/>
-      <c r="N12" s="219"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="186"/>
+      <c r="L12" s="240"/>
+      <c r="M12" s="240"/>
+      <c r="N12" s="240"/>
     </row>
     <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="200" t="s">
+      <c r="A13" s="185" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="200"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
       <c r="F13" s="41"/>
-      <c r="G13" s="202" t="s">
+      <c r="G13" s="187" t="s">
         <v>193</v>
       </c>
-      <c r="H13" s="202"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="202"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="219"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="219"/>
+      <c r="H13" s="187"/>
+      <c r="I13" s="187"/>
+      <c r="J13" s="187"/>
+      <c r="K13" s="187"/>
+      <c r="L13" s="240"/>
+      <c r="M13" s="240"/>
+      <c r="N13" s="240"/>
     </row>
     <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="208" t="s">
+      <c r="A14" s="193" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="208"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
       <c r="F14" s="37"/>
-      <c r="G14" s="202" t="s">
+      <c r="G14" s="187" t="s">
         <v>194</v>
       </c>
-      <c r="H14" s="202"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="219"/>
-      <c r="M14" s="219"/>
-      <c r="N14" s="219"/>
+      <c r="H14" s="187"/>
+      <c r="I14" s="187"/>
+      <c r="J14" s="187"/>
+      <c r="K14" s="187"/>
+      <c r="L14" s="240"/>
+      <c r="M14" s="240"/>
+      <c r="N14" s="240"/>
     </row>
     <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="208" t="s">
+      <c r="A15" s="193" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="208"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="195"/>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195"/>
       <c r="F15" s="37"/>
-      <c r="G15" s="200" t="s">
+      <c r="G15" s="185" t="s">
         <v>195</v>
       </c>
-      <c r="H15" s="200"/>
-      <c r="I15" s="200"/>
-      <c r="J15" s="200"/>
-      <c r="K15" s="200"/>
-      <c r="L15" s="219"/>
-      <c r="M15" s="219"/>
-      <c r="N15" s="219"/>
+      <c r="H15" s="185"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="240"/>
+      <c r="M15" s="240"/>
+      <c r="N15" s="240"/>
     </row>
     <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="208" t="s">
+      <c r="A16" s="193" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="208"/>
-      <c r="C16" s="207"/>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="200" t="s">
+      <c r="B16" s="193"/>
+      <c r="C16" s="192"/>
+      <c r="D16" s="192"/>
+      <c r="E16" s="192"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="185" t="s">
         <v>196</v>
       </c>
-      <c r="H16" s="200"/>
-      <c r="I16" s="200"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="200"/>
-      <c r="L16" s="219"/>
-      <c r="M16" s="219"/>
-      <c r="N16" s="219"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="185"/>
+      <c r="L16" s="183"/>
+      <c r="M16" s="183"/>
+      <c r="N16" s="183"/>
     </row>
     <row r="17" spans="1:13" ht="21.95" customHeight="1"/>
     <row r="18" spans="1:13" ht="30" customHeight="1">
-      <c r="A18" s="218" t="s">
+      <c r="A18" s="203" t="s">
         <v>179</v>
       </c>
-      <c r="B18" s="218"/>
-      <c r="C18" s="218"/>
-      <c r="D18" s="218"/>
-      <c r="E18" s="218"/>
-      <c r="F18" s="218"/>
-      <c r="G18" s="218"/>
-      <c r="H18" s="218"/>
-      <c r="I18" s="218"/>
-      <c r="J18" s="218"/>
-      <c r="K18" s="218"/>
-      <c r="L18" s="218"/>
-      <c r="M18" s="218"/>
+      <c r="B18" s="203"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="203"/>
+      <c r="H18" s="203"/>
+      <c r="I18" s="203"/>
+      <c r="J18" s="203"/>
+      <c r="K18" s="203"/>
+      <c r="L18" s="203"/>
+      <c r="M18" s="203"/>
     </row>
     <row r="19" spans="1:13" ht="30" customHeight="1">
-      <c r="A19" s="217" t="s">
+      <c r="A19" s="202" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="217"/>
-      <c r="C19" s="73" t="s">
+      <c r="B19" s="202"/>
+      <c r="C19" s="72" t="s">
         <v>151</v>
       </c>
       <c r="D19" s="42">
@@ -24729,143 +24857,143 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A20" s="211" t="s">
+      <c r="A20" s="196" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="211"/>
-      <c r="C20" s="74" t="s">
+      <c r="B20" s="196"/>
+      <c r="C20" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="75"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="75"/>
-      <c r="L20" s="75"/>
-      <c r="M20" s="75"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="74"/>
     </row>
     <row r="21" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A21" s="211" t="s">
+      <c r="A21" s="196" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="211"/>
-      <c r="C21" s="74" t="s">
+      <c r="B21" s="196"/>
+      <c r="C21" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="75"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="75"/>
-      <c r="M21" s="75"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
     </row>
     <row r="22" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A22" s="211" t="s">
+      <c r="A22" s="196" t="s">
         <v>154</v>
       </c>
-      <c r="B22" s="211"/>
-      <c r="C22" s="74" t="s">
+      <c r="B22" s="196"/>
+      <c r="C22" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
     </row>
     <row r="23" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A23" s="211" t="s">
+      <c r="A23" s="196" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="211"/>
-      <c r="C23" s="74" t="s">
+      <c r="B23" s="196"/>
+      <c r="C23" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="75"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="75"/>
     </row>
     <row r="24" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A24" s="211" t="s">
+      <c r="A24" s="196" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="211"/>
-      <c r="C24" s="74" t="s">
+      <c r="B24" s="196"/>
+      <c r="C24" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
     </row>
     <row r="25" spans="1:13" ht="35.1" customHeight="1">
-      <c r="A25" s="211" t="s">
+      <c r="A25" s="196" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="211"/>
-      <c r="C25" s="74" t="s">
+      <c r="B25" s="196"/>
+      <c r="C25" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
     </row>
     <row r="26" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A26" s="203"/>
-      <c r="B26" s="203"/>
+      <c r="A26" s="188"/>
+      <c r="B26" s="188"/>
     </row>
     <row r="27" spans="1:13" ht="24.95" customHeight="1"/>
     <row r="28" spans="1:13" ht="24.95" customHeight="1"/>
     <row r="29" spans="1:13" ht="24.95" customHeight="1"/>
     <row r="30" spans="1:13" ht="24.95" customHeight="1"/>
     <row r="32" spans="1:13">
-      <c r="A32" s="213" t="s">
+      <c r="A32" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="213"/>
-      <c r="C32" s="213"/>
-      <c r="D32" s="213"/>
-      <c r="E32" s="213"/>
-      <c r="F32" s="213"/>
-      <c r="G32" s="213"/>
-      <c r="H32" s="213"/>
-      <c r="I32" s="213"/>
-      <c r="J32" s="213"/>
-      <c r="K32" s="213"/>
-      <c r="L32" s="213"/>
-      <c r="M32" s="213"/>
+      <c r="B32" s="198"/>
+      <c r="C32" s="198"/>
+      <c r="D32" s="198"/>
+      <c r="E32" s="198"/>
+      <c r="F32" s="198"/>
+      <c r="G32" s="198"/>
+      <c r="H32" s="198"/>
+      <c r="I32" s="198"/>
+      <c r="J32" s="198"/>
+      <c r="K32" s="198"/>
+      <c r="L32" s="198"/>
+      <c r="M32" s="198"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="36"/>
@@ -25261,106 +25389,106 @@
       <c r="A59" s="46"/>
       <c r="B59" s="46"/>
       <c r="C59" s="46"/>
-      <c r="D59" s="212"/>
-      <c r="E59" s="212"/>
-      <c r="F59" s="212"/>
-      <c r="G59" s="212"/>
+      <c r="D59" s="197"/>
+      <c r="E59" s="197"/>
+      <c r="F59" s="197"/>
+      <c r="G59" s="197"/>
       <c r="H59" s="47"/>
-      <c r="I59" s="212"/>
-      <c r="J59" s="212"/>
-      <c r="K59" s="212"/>
-      <c r="L59" s="212"/>
-      <c r="M59" s="212"/>
+      <c r="I59" s="197"/>
+      <c r="J59" s="197"/>
+      <c r="K59" s="197"/>
+      <c r="L59" s="197"/>
+      <c r="M59" s="197"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="46"/>
       <c r="B60" s="46"/>
       <c r="C60" s="46"/>
-      <c r="D60" s="212"/>
-      <c r="E60" s="212"/>
-      <c r="F60" s="212"/>
-      <c r="G60" s="212"/>
+      <c r="D60" s="197"/>
+      <c r="E60" s="197"/>
+      <c r="F60" s="197"/>
+      <c r="G60" s="197"/>
       <c r="H60" s="47"/>
-      <c r="I60" s="212"/>
-      <c r="J60" s="212"/>
-      <c r="K60" s="212"/>
-      <c r="L60" s="212"/>
-      <c r="M60" s="212"/>
+      <c r="I60" s="197"/>
+      <c r="J60" s="197"/>
+      <c r="K60" s="197"/>
+      <c r="L60" s="197"/>
+      <c r="M60" s="197"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="46"/>
       <c r="B61" s="46"/>
       <c r="C61" s="46"/>
-      <c r="D61" s="212"/>
-      <c r="E61" s="212"/>
-      <c r="F61" s="212"/>
-      <c r="G61" s="212"/>
+      <c r="D61" s="197"/>
+      <c r="E61" s="197"/>
+      <c r="F61" s="197"/>
+      <c r="G61" s="197"/>
       <c r="H61" s="47"/>
-      <c r="I61" s="212"/>
-      <c r="J61" s="212"/>
-      <c r="K61" s="212"/>
-      <c r="L61" s="212"/>
-      <c r="M61" s="212"/>
+      <c r="I61" s="197"/>
+      <c r="J61" s="197"/>
+      <c r="K61" s="197"/>
+      <c r="L61" s="197"/>
+      <c r="M61" s="197"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="46"/>
       <c r="B62" s="46"/>
       <c r="C62" s="46"/>
-      <c r="D62" s="212"/>
-      <c r="E62" s="212"/>
-      <c r="F62" s="212"/>
-      <c r="G62" s="212"/>
+      <c r="D62" s="197"/>
+      <c r="E62" s="197"/>
+      <c r="F62" s="197"/>
+      <c r="G62" s="197"/>
       <c r="H62" s="47"/>
-      <c r="I62" s="212"/>
-      <c r="J62" s="212"/>
-      <c r="K62" s="212"/>
-      <c r="L62" s="212"/>
-      <c r="M62" s="212"/>
+      <c r="I62" s="197"/>
+      <c r="J62" s="197"/>
+      <c r="K62" s="197"/>
+      <c r="L62" s="197"/>
+      <c r="M62" s="197"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="46"/>
       <c r="B63" s="46"/>
       <c r="C63" s="46"/>
-      <c r="D63" s="212"/>
-      <c r="E63" s="212"/>
-      <c r="F63" s="212"/>
-      <c r="G63" s="212"/>
+      <c r="D63" s="197"/>
+      <c r="E63" s="197"/>
+      <c r="F63" s="197"/>
+      <c r="G63" s="197"/>
       <c r="H63" s="47"/>
-      <c r="I63" s="212"/>
-      <c r="J63" s="212"/>
-      <c r="K63" s="212"/>
-      <c r="L63" s="212"/>
-      <c r="M63" s="212"/>
+      <c r="I63" s="197"/>
+      <c r="J63" s="197"/>
+      <c r="K63" s="197"/>
+      <c r="L63" s="197"/>
+      <c r="M63" s="197"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="46"/>
       <c r="B64" s="46"/>
       <c r="C64" s="46"/>
-      <c r="D64" s="212"/>
-      <c r="E64" s="212"/>
-      <c r="F64" s="212"/>
-      <c r="G64" s="212"/>
+      <c r="D64" s="197"/>
+      <c r="E64" s="197"/>
+      <c r="F64" s="197"/>
+      <c r="G64" s="197"/>
       <c r="H64" s="47"/>
-      <c r="I64" s="212"/>
-      <c r="J64" s="212"/>
-      <c r="K64" s="212"/>
-      <c r="L64" s="212"/>
-      <c r="M64" s="212"/>
+      <c r="I64" s="197"/>
+      <c r="J64" s="197"/>
+      <c r="K64" s="197"/>
+      <c r="L64" s="197"/>
+      <c r="M64" s="197"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="46"/>
       <c r="B65" s="46"/>
       <c r="C65" s="46"/>
-      <c r="D65" s="212"/>
-      <c r="E65" s="212"/>
-      <c r="F65" s="212"/>
-      <c r="G65" s="212"/>
+      <c r="D65" s="197"/>
+      <c r="E65" s="197"/>
+      <c r="F65" s="197"/>
+      <c r="G65" s="197"/>
       <c r="H65" s="47"/>
-      <c r="I65" s="212"/>
-      <c r="J65" s="212"/>
-      <c r="K65" s="212"/>
-      <c r="L65" s="212"/>
-      <c r="M65" s="212"/>
+      <c r="I65" s="197"/>
+      <c r="J65" s="197"/>
+      <c r="K65" s="197"/>
+      <c r="L65" s="197"/>
+      <c r="M65" s="197"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="36"/>
@@ -25438,21 +25566,21 @@
       <c r="M70" s="36"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="213" t="s">
+      <c r="A71" s="198" t="s">
         <v>113</v>
       </c>
-      <c r="B71" s="213"/>
-      <c r="C71" s="213"/>
-      <c r="D71" s="213"/>
-      <c r="E71" s="213"/>
-      <c r="F71" s="213"/>
-      <c r="G71" s="213"/>
-      <c r="H71" s="213"/>
-      <c r="I71" s="213"/>
-      <c r="J71" s="213"/>
-      <c r="K71" s="213"/>
-      <c r="L71" s="213"/>
-      <c r="M71" s="213"/>
+      <c r="B71" s="198"/>
+      <c r="C71" s="198"/>
+      <c r="D71" s="198"/>
+      <c r="E71" s="198"/>
+      <c r="F71" s="198"/>
+      <c r="G71" s="198"/>
+      <c r="H71" s="198"/>
+      <c r="I71" s="198"/>
+      <c r="J71" s="198"/>
+      <c r="K71" s="198"/>
+      <c r="L71" s="198"/>
+      <c r="M71" s="198"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="52"/>
@@ -25500,46 +25628,46 @@
       <c r="M74" s="36"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="215" t="s">
+      <c r="A75" s="200" t="s">
         <v>114</v>
       </c>
-      <c r="B75" s="215"/>
-      <c r="C75" s="215"/>
-      <c r="D75" s="215"/>
-      <c r="E75" s="215"/>
-      <c r="F75" s="216" t="s">
+      <c r="B75" s="200"/>
+      <c r="C75" s="200"/>
+      <c r="D75" s="200"/>
+      <c r="E75" s="200"/>
+      <c r="F75" s="201" t="s">
         <v>115</v>
       </c>
-      <c r="G75" s="216"/>
-      <c r="H75" s="216"/>
-      <c r="I75" s="216"/>
-      <c r="J75" s="216"/>
-      <c r="K75" s="216" t="s">
+      <c r="G75" s="201"/>
+      <c r="H75" s="201"/>
+      <c r="I75" s="201"/>
+      <c r="J75" s="201"/>
+      <c r="K75" s="201" t="s">
         <v>116</v>
       </c>
-      <c r="L75" s="216"/>
-      <c r="M75" s="216"/>
+      <c r="L75" s="201"/>
+      <c r="M75" s="201"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="214" t="s">
+      <c r="A76" s="199" t="s">
         <v>117</v>
       </c>
-      <c r="B76" s="214"/>
-      <c r="C76" s="214"/>
-      <c r="D76" s="214"/>
-      <c r="E76" s="214"/>
-      <c r="F76" s="214" t="s">
+      <c r="B76" s="199"/>
+      <c r="C76" s="199"/>
+      <c r="D76" s="199"/>
+      <c r="E76" s="199"/>
+      <c r="F76" s="199" t="s">
         <v>118</v>
       </c>
-      <c r="G76" s="214"/>
-      <c r="H76" s="214"/>
-      <c r="I76" s="214"/>
-      <c r="J76" s="214"/>
-      <c r="K76" s="214" t="s">
+      <c r="G76" s="199"/>
+      <c r="H76" s="199"/>
+      <c r="I76" s="199"/>
+      <c r="J76" s="199"/>
+      <c r="K76" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="L76" s="214"/>
-      <c r="M76" s="214"/>
+      <c r="L76" s="199"/>
+      <c r="M76" s="199"/>
     </row>
     <row r="82" spans="15:27">
       <c r="O82" s="58"/>
@@ -25764,55 +25892,55 @@
     <row r="4" spans="1:14" ht="15" customHeight="1"/>
     <row r="5" spans="1:14" ht="15" customHeight="1"/>
     <row r="6" spans="1:14" ht="18">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="189" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="204"/>
-      <c r="C6" s="204"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="204"/>
-      <c r="I6" s="204"/>
-      <c r="J6" s="204"/>
-      <c r="K6" s="204"/>
-      <c r="L6" s="204"/>
-      <c r="M6" s="204"/>
+      <c r="B6" s="189"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="189"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+      <c r="M6" s="189"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="205" t="s">
+      <c r="A7" s="190" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="205"/>
-      <c r="L7" s="205"/>
-      <c r="M7" s="205"/>
+      <c r="B7" s="190"/>
+      <c r="C7" s="190"/>
+      <c r="D7" s="190"/>
+      <c r="E7" s="190"/>
+      <c r="F7" s="190"/>
+      <c r="G7" s="190"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="190"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="190"/>
+      <c r="L7" s="190"/>
+      <c r="M7" s="190"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="206" t="s">
+      <c r="A8" s="191" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="206"/>
-      <c r="C8" s="206"/>
-      <c r="D8" s="220"/>
-      <c r="E8" s="220"/>
-      <c r="F8" s="220"/>
-      <c r="G8" s="220"/>
-      <c r="H8" s="220"/>
-      <c r="I8" s="220"/>
-      <c r="J8" s="220"/>
-      <c r="K8" s="220"/>
-      <c r="L8" s="220"/>
-      <c r="M8" s="220"/>
+      <c r="B8" s="191"/>
+      <c r="C8" s="191"/>
+      <c r="D8" s="204"/>
+      <c r="E8" s="204"/>
+      <c r="F8" s="204"/>
+      <c r="G8" s="204"/>
+      <c r="H8" s="204"/>
+      <c r="I8" s="204"/>
+      <c r="J8" s="204"/>
+      <c r="K8" s="204"/>
+      <c r="L8" s="204"/>
+      <c r="M8" s="204"/>
     </row>
     <row r="9" spans="1:14" ht="14.1" customHeight="1">
       <c r="A9" s="37"/>
@@ -25825,8 +25953,8 @@
       <c r="I9" s="40"/>
       <c r="J9" s="39"/>
       <c r="K9" s="38"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="92"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="88"/>
     </row>
     <row r="10" spans="1:14" ht="14.1" customHeight="1">
       <c r="A10" s="37"/>
@@ -25839,224 +25967,224 @@
       <c r="I10" s="41"/>
       <c r="J10" s="39"/>
       <c r="K10" s="41"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="92"/>
+      <c r="L10" s="90"/>
+      <c r="M10" s="88"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1">
-      <c r="A11" s="199" t="s">
+      <c r="A11" s="184" t="s">
         <v>186</v>
       </c>
-      <c r="B11" s="199"/>
-      <c r="C11" s="199"/>
-      <c r="D11" s="199"/>
-      <c r="E11" s="199"/>
-      <c r="F11" s="199"/>
-      <c r="G11" s="199"/>
-      <c r="H11" s="199"/>
-      <c r="I11" s="199"/>
-      <c r="J11" s="199"/>
-      <c r="K11" s="199"/>
-      <c r="L11" s="199"/>
-      <c r="M11" s="199"/>
-      <c r="N11" s="199"/>
+      <c r="B11" s="184"/>
+      <c r="C11" s="184"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="184"/>
+      <c r="K11" s="184"/>
+      <c r="L11" s="184"/>
+      <c r="M11" s="184"/>
+      <c r="N11" s="184"/>
     </row>
     <row r="12" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A12" s="200" t="s">
+      <c r="A12" s="185" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="200"/>
-      <c r="C12" s="209"/>
-      <c r="D12" s="209"/>
-      <c r="E12" s="209"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="194"/>
+      <c r="D12" s="194"/>
+      <c r="E12" s="194"/>
       <c r="F12" s="38"/>
-      <c r="G12" s="201" t="s">
+      <c r="G12" s="186" t="s">
         <v>192</v>
       </c>
-      <c r="H12" s="201"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="201"/>
-      <c r="K12" s="201"/>
-      <c r="L12" s="219"/>
-      <c r="M12" s="219"/>
-      <c r="N12" s="219"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="186"/>
+      <c r="L12" s="240"/>
+      <c r="M12" s="240"/>
+      <c r="N12" s="240"/>
     </row>
     <row r="13" spans="1:14" ht="21" customHeight="1">
-      <c r="A13" s="200" t="s">
+      <c r="A13" s="185" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="200"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
       <c r="F13" s="41"/>
-      <c r="G13" s="202" t="s">
+      <c r="G13" s="187" t="s">
         <v>193</v>
       </c>
-      <c r="H13" s="202"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="202"/>
-      <c r="K13" s="202"/>
-      <c r="L13" s="219"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="219"/>
+      <c r="H13" s="187"/>
+      <c r="I13" s="187"/>
+      <c r="J13" s="187"/>
+      <c r="K13" s="187"/>
+      <c r="L13" s="240"/>
+      <c r="M13" s="240"/>
+      <c r="N13" s="240"/>
     </row>
     <row r="14" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A14" s="208" t="s">
+      <c r="A14" s="193" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="208"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
       <c r="F14" s="37"/>
-      <c r="G14" s="202" t="s">
+      <c r="G14" s="187" t="s">
         <v>194</v>
       </c>
-      <c r="H14" s="202"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="202"/>
-      <c r="K14" s="202"/>
-      <c r="L14" s="219"/>
-      <c r="M14" s="219"/>
-      <c r="N14" s="219"/>
+      <c r="H14" s="187"/>
+      <c r="I14" s="187"/>
+      <c r="J14" s="187"/>
+      <c r="K14" s="187"/>
+      <c r="L14" s="240"/>
+      <c r="M14" s="240"/>
+      <c r="N14" s="240"/>
     </row>
     <row r="15" spans="1:14" ht="21" customHeight="1">
-      <c r="A15" s="208" t="s">
+      <c r="A15" s="193" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="208"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="195"/>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195"/>
       <c r="F15" s="37"/>
-      <c r="G15" s="200" t="s">
+      <c r="G15" s="185" t="s">
         <v>195</v>
       </c>
-      <c r="H15" s="200"/>
-      <c r="I15" s="200"/>
-      <c r="J15" s="200"/>
-      <c r="K15" s="200"/>
-      <c r="L15" s="219"/>
-      <c r="M15" s="219"/>
-      <c r="N15" s="219"/>
+      <c r="H15" s="185"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="240"/>
+      <c r="M15" s="240"/>
+      <c r="N15" s="240"/>
     </row>
     <row r="16" spans="1:14" ht="21" customHeight="1">
-      <c r="A16" s="208" t="s">
+      <c r="A16" s="193" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="208"/>
-      <c r="C16" s="207"/>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="200" t="s">
+      <c r="B16" s="193"/>
+      <c r="C16" s="192"/>
+      <c r="D16" s="192"/>
+      <c r="E16" s="192"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="185" t="s">
         <v>196</v>
       </c>
-      <c r="H16" s="200"/>
-      <c r="I16" s="200"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="200"/>
-      <c r="L16" s="219"/>
-      <c r="M16" s="219"/>
-      <c r="N16" s="219"/>
+      <c r="H16" s="185"/>
+      <c r="I16" s="185"/>
+      <c r="J16" s="185"/>
+      <c r="K16" s="185"/>
+      <c r="L16" s="183"/>
+      <c r="M16" s="183"/>
+      <c r="N16" s="183"/>
     </row>
     <row r="17" spans="1:14" ht="14.1" customHeight="1" thickBot="1">
-      <c r="A17" s="114"/>
-      <c r="B17" s="114"/>
-      <c r="C17" s="113"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="112"/>
-      <c r="M17" s="112"/>
-      <c r="N17" s="112"/>
+      <c r="A17" s="110"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="109"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
     </row>
     <row r="18" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A18" s="221" t="s">
+      <c r="A18" s="205" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="222"/>
-      <c r="C18" s="222"/>
-      <c r="D18" s="222"/>
-      <c r="E18" s="222"/>
-      <c r="F18" s="222"/>
-      <c r="G18" s="222"/>
-      <c r="H18" s="222"/>
-      <c r="I18" s="222"/>
-      <c r="J18" s="222"/>
-      <c r="K18" s="222"/>
-      <c r="L18" s="222"/>
-      <c r="M18" s="223"/>
+      <c r="B18" s="206"/>
+      <c r="C18" s="206"/>
+      <c r="D18" s="206"/>
+      <c r="E18" s="206"/>
+      <c r="F18" s="206"/>
+      <c r="G18" s="206"/>
+      <c r="H18" s="206"/>
+      <c r="I18" s="206"/>
+      <c r="J18" s="206"/>
+      <c r="K18" s="206"/>
+      <c r="L18" s="206"/>
+      <c r="M18" s="207"/>
     </row>
     <row r="19" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A19" s="228" t="s">
+      <c r="A19" s="212" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="229"/>
-      <c r="C19" s="88" t="s">
+      <c r="B19" s="213"/>
+      <c r="C19" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="D19" s="87">
+      <c r="D19" s="83">
         <v>1</v>
       </c>
-      <c r="E19" s="87">
+      <c r="E19" s="83">
         <v>2</v>
       </c>
-      <c r="F19" s="87">
+      <c r="F19" s="83">
         <v>3</v>
       </c>
-      <c r="G19" s="87">
+      <c r="G19" s="83">
         <v>4</v>
       </c>
-      <c r="H19" s="87">
+      <c r="H19" s="83">
         <v>5</v>
       </c>
-      <c r="I19" s="87">
+      <c r="I19" s="83">
         <v>6</v>
       </c>
-      <c r="J19" s="87">
+      <c r="J19" s="83">
         <v>7</v>
       </c>
-      <c r="K19" s="87">
+      <c r="K19" s="83">
         <v>8</v>
       </c>
-      <c r="L19" s="87">
+      <c r="L19" s="83">
         <v>9</v>
       </c>
-      <c r="M19" s="95">
+      <c r="M19" s="91">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A20" s="230" t="s">
+      <c r="A20" s="214" t="s">
         <v>168</v>
       </c>
-      <c r="B20" s="231"/>
-      <c r="C20" s="74" t="s">
+      <c r="B20" s="215"/>
+      <c r="C20" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="96"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="92"/>
     </row>
     <row r="21" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A21" s="224" t="s">
+      <c r="A21" s="208" t="s">
         <v>169</v>
       </c>
-      <c r="B21" s="225"/>
-      <c r="C21" s="74" t="s">
+      <c r="B21" s="209"/>
+      <c r="C21" s="73" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="50"/>
@@ -26068,14 +26196,14 @@
       <c r="J21" s="50"/>
       <c r="K21" s="50"/>
       <c r="L21" s="50"/>
-      <c r="M21" s="97"/>
+      <c r="M21" s="93"/>
     </row>
     <row r="22" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A22" s="224" t="s">
+      <c r="A22" s="208" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="225"/>
-      <c r="C22" s="74" t="s">
+      <c r="B22" s="209"/>
+      <c r="C22" s="73" t="s">
         <v>32</v>
       </c>
       <c r="D22" s="51"/>
@@ -26087,50 +26215,50 @@
       <c r="J22" s="51"/>
       <c r="K22" s="51"/>
       <c r="L22" s="51"/>
-      <c r="M22" s="98"/>
+      <c r="M22" s="94"/>
     </row>
     <row r="23" spans="1:14" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A23" s="226" t="s">
+      <c r="A23" s="210" t="s">
         <v>171</v>
       </c>
-      <c r="B23" s="227"/>
-      <c r="C23" s="99" t="s">
+      <c r="B23" s="211"/>
+      <c r="C23" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="100"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="100"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="101"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="96"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="96"/>
+      <c r="L23" s="96"/>
+      <c r="M23" s="97"/>
     </row>
     <row r="24" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A24" s="232" t="s">
+      <c r="A24" s="216" t="s">
         <v>172</v>
       </c>
-      <c r="B24" s="233"/>
-      <c r="C24" s="233"/>
-      <c r="D24" s="233"/>
-      <c r="E24" s="233"/>
-      <c r="F24" s="233"/>
-      <c r="G24" s="233"/>
-      <c r="H24" s="233"/>
-      <c r="I24" s="233"/>
-      <c r="J24" s="233"/>
-      <c r="K24" s="233"/>
-      <c r="L24" s="233"/>
-      <c r="M24" s="234"/>
+      <c r="B24" s="217"/>
+      <c r="C24" s="217"/>
+      <c r="D24" s="217"/>
+      <c r="E24" s="217"/>
+      <c r="F24" s="217"/>
+      <c r="G24" s="217"/>
+      <c r="H24" s="217"/>
+      <c r="I24" s="217"/>
+      <c r="J24" s="217"/>
+      <c r="K24" s="217"/>
+      <c r="L24" s="217"/>
+      <c r="M24" s="218"/>
     </row>
     <row r="25" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A25" s="230" t="s">
+      <c r="A25" s="214" t="s">
         <v>168</v>
       </c>
-      <c r="B25" s="231"/>
-      <c r="C25" s="74" t="s">
+      <c r="B25" s="215"/>
+      <c r="C25" s="73" t="s">
         <v>111</v>
       </c>
       <c r="D25" s="50"/>
@@ -26142,14 +26270,14 @@
       <c r="J25" s="50"/>
       <c r="K25" s="50"/>
       <c r="L25" s="50"/>
-      <c r="M25" s="97"/>
+      <c r="M25" s="93"/>
     </row>
     <row r="26" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A26" s="224" t="s">
+      <c r="A26" s="208" t="s">
         <v>169</v>
       </c>
-      <c r="B26" s="225"/>
-      <c r="C26" s="74" t="s">
+      <c r="B26" s="209"/>
+      <c r="C26" s="73" t="s">
         <v>31</v>
       </c>
       <c r="D26" s="50"/>
@@ -26161,14 +26289,14 @@
       <c r="J26" s="50"/>
       <c r="K26" s="50"/>
       <c r="L26" s="50"/>
-      <c r="M26" s="97"/>
+      <c r="M26" s="93"/>
     </row>
     <row r="27" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A27" s="224" t="s">
+      <c r="A27" s="208" t="s">
         <v>170</v>
       </c>
-      <c r="B27" s="225"/>
-      <c r="C27" s="74" t="s">
+      <c r="B27" s="209"/>
+      <c r="C27" s="73" t="s">
         <v>32</v>
       </c>
       <c r="D27" s="51"/>
@@ -26180,151 +26308,151 @@
       <c r="J27" s="51"/>
       <c r="K27" s="51"/>
       <c r="L27" s="51"/>
-      <c r="M27" s="98"/>
+      <c r="M27" s="94"/>
     </row>
     <row r="28" spans="1:14" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A28" s="226" t="s">
+      <c r="A28" s="210" t="s">
         <v>171</v>
       </c>
-      <c r="B28" s="227"/>
-      <c r="C28" s="99" t="s">
+      <c r="B28" s="211"/>
+      <c r="C28" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="100"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="100"/>
-      <c r="G28" s="100"/>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="100"/>
-      <c r="M28" s="101"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="96"/>
+      <c r="L28" s="96"/>
+      <c r="M28" s="97"/>
     </row>
     <row r="29" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A29" s="232" t="s">
+      <c r="A29" s="216" t="s">
         <v>173</v>
       </c>
-      <c r="B29" s="233"/>
-      <c r="C29" s="233"/>
-      <c r="D29" s="233"/>
-      <c r="E29" s="233"/>
-      <c r="F29" s="233"/>
-      <c r="G29" s="233"/>
-      <c r="H29" s="233"/>
-      <c r="I29" s="233"/>
-      <c r="J29" s="233"/>
-      <c r="K29" s="233"/>
-      <c r="L29" s="233"/>
-      <c r="M29" s="234"/>
+      <c r="B29" s="217"/>
+      <c r="C29" s="217"/>
+      <c r="D29" s="217"/>
+      <c r="E29" s="217"/>
+      <c r="F29" s="217"/>
+      <c r="G29" s="217"/>
+      <c r="H29" s="217"/>
+      <c r="I29" s="217"/>
+      <c r="J29" s="217"/>
+      <c r="K29" s="217"/>
+      <c r="L29" s="217"/>
+      <c r="M29" s="218"/>
     </row>
     <row r="30" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A30" s="230" t="s">
+      <c r="A30" s="214" t="s">
         <v>168</v>
       </c>
-      <c r="B30" s="231"/>
-      <c r="C30" s="74" t="s">
+      <c r="B30" s="215"/>
+      <c r="C30" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="96"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="92"/>
     </row>
     <row r="31" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A31" s="224" t="s">
+      <c r="A31" s="208" t="s">
         <v>169</v>
       </c>
-      <c r="B31" s="225"/>
-      <c r="C31" s="74" t="s">
+      <c r="B31" s="209"/>
+      <c r="C31" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="89"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="89"/>
-      <c r="K31" s="89"/>
-      <c r="L31" s="89"/>
-      <c r="M31" s="96"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="92"/>
     </row>
     <row r="32" spans="1:14" ht="27.95" customHeight="1">
-      <c r="A32" s="224" t="s">
+      <c r="A32" s="208" t="s">
         <v>170</v>
       </c>
-      <c r="B32" s="225"/>
-      <c r="C32" s="74" t="s">
+      <c r="B32" s="209"/>
+      <c r="C32" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="90"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="90"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="90"/>
-      <c r="K32" s="90"/>
-      <c r="L32" s="90"/>
-      <c r="M32" s="102"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="K32" s="86"/>
+      <c r="L32" s="86"/>
+      <c r="M32" s="98"/>
     </row>
     <row r="33" spans="1:13" ht="27.95" customHeight="1" thickBot="1">
-      <c r="A33" s="226" t="s">
+      <c r="A33" s="210" t="s">
         <v>171</v>
       </c>
-      <c r="B33" s="227"/>
-      <c r="C33" s="99" t="s">
+      <c r="B33" s="211"/>
+      <c r="C33" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103"/>
-      <c r="G33" s="103"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="103"/>
-      <c r="J33" s="103"/>
-      <c r="K33" s="103"/>
-      <c r="L33" s="103"/>
-      <c r="M33" s="104"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="99"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="99"/>
+      <c r="K33" s="99"/>
+      <c r="L33" s="99"/>
+      <c r="M33" s="100"/>
     </row>
     <row r="34" spans="1:13" ht="24.95" customHeight="1">
-      <c r="A34" s="91"/>
-      <c r="B34" s="91"/>
-      <c r="C34" s="91"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="91"/>
-      <c r="G34" s="91"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="91"/>
-      <c r="J34" s="91"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="91"/>
-      <c r="M34" s="91"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="87"/>
+      <c r="H34" s="87"/>
+      <c r="I34" s="87"/>
+      <c r="J34" s="87"/>
+      <c r="K34" s="87"/>
+      <c r="L34" s="87"/>
+      <c r="M34" s="87"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="213" t="s">
+      <c r="A35" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="213"/>
-      <c r="C35" s="213"/>
-      <c r="D35" s="213"/>
-      <c r="E35" s="213"/>
-      <c r="F35" s="213"/>
-      <c r="G35" s="213"/>
-      <c r="H35" s="213"/>
-      <c r="I35" s="213"/>
-      <c r="J35" s="213"/>
-      <c r="K35" s="213"/>
-      <c r="L35" s="213"/>
-      <c r="M35" s="213"/>
+      <c r="B35" s="198"/>
+      <c r="C35" s="198"/>
+      <c r="D35" s="198"/>
+      <c r="E35" s="198"/>
+      <c r="F35" s="198"/>
+      <c r="G35" s="198"/>
+      <c r="H35" s="198"/>
+      <c r="I35" s="198"/>
+      <c r="J35" s="198"/>
+      <c r="K35" s="198"/>
+      <c r="L35" s="198"/>
+      <c r="M35" s="198"/>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="36"/>
@@ -26720,106 +26848,106 @@
       <c r="A62" s="46"/>
       <c r="B62" s="46"/>
       <c r="C62" s="46"/>
-      <c r="D62" s="212"/>
-      <c r="E62" s="212"/>
-      <c r="F62" s="212"/>
-      <c r="G62" s="212"/>
+      <c r="D62" s="197"/>
+      <c r="E62" s="197"/>
+      <c r="F62" s="197"/>
+      <c r="G62" s="197"/>
       <c r="H62" s="47"/>
-      <c r="I62" s="212"/>
-      <c r="J62" s="212"/>
-      <c r="K62" s="212"/>
-      <c r="L62" s="212"/>
-      <c r="M62" s="212"/>
+      <c r="I62" s="197"/>
+      <c r="J62" s="197"/>
+      <c r="K62" s="197"/>
+      <c r="L62" s="197"/>
+      <c r="M62" s="197"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="46"/>
       <c r="B63" s="46"/>
       <c r="C63" s="46"/>
-      <c r="D63" s="212"/>
-      <c r="E63" s="212"/>
-      <c r="F63" s="212"/>
-      <c r="G63" s="212"/>
+      <c r="D63" s="197"/>
+      <c r="E63" s="197"/>
+      <c r="F63" s="197"/>
+      <c r="G63" s="197"/>
       <c r="H63" s="47"/>
-      <c r="I63" s="212"/>
-      <c r="J63" s="212"/>
-      <c r="K63" s="212"/>
-      <c r="L63" s="212"/>
-      <c r="M63" s="212"/>
+      <c r="I63" s="197"/>
+      <c r="J63" s="197"/>
+      <c r="K63" s="197"/>
+      <c r="L63" s="197"/>
+      <c r="M63" s="197"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="46"/>
       <c r="B64" s="46"/>
       <c r="C64" s="46"/>
-      <c r="D64" s="212"/>
-      <c r="E64" s="212"/>
-      <c r="F64" s="212"/>
-      <c r="G64" s="212"/>
+      <c r="D64" s="197"/>
+      <c r="E64" s="197"/>
+      <c r="F64" s="197"/>
+      <c r="G64" s="197"/>
       <c r="H64" s="47"/>
-      <c r="I64" s="212"/>
-      <c r="J64" s="212"/>
-      <c r="K64" s="212"/>
-      <c r="L64" s="212"/>
-      <c r="M64" s="212"/>
+      <c r="I64" s="197"/>
+      <c r="J64" s="197"/>
+      <c r="K64" s="197"/>
+      <c r="L64" s="197"/>
+      <c r="M64" s="197"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="46"/>
       <c r="B65" s="46"/>
       <c r="C65" s="46"/>
-      <c r="D65" s="212"/>
-      <c r="E65" s="212"/>
-      <c r="F65" s="212"/>
-      <c r="G65" s="212"/>
+      <c r="D65" s="197"/>
+      <c r="E65" s="197"/>
+      <c r="F65" s="197"/>
+      <c r="G65" s="197"/>
       <c r="H65" s="47"/>
-      <c r="I65" s="212"/>
-      <c r="J65" s="212"/>
-      <c r="K65" s="212"/>
-      <c r="L65" s="212"/>
-      <c r="M65" s="212"/>
+      <c r="I65" s="197"/>
+      <c r="J65" s="197"/>
+      <c r="K65" s="197"/>
+      <c r="L65" s="197"/>
+      <c r="M65" s="197"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="46"/>
       <c r="B66" s="46"/>
       <c r="C66" s="46"/>
-      <c r="D66" s="212"/>
-      <c r="E66" s="212"/>
-      <c r="F66" s="212"/>
-      <c r="G66" s="212"/>
+      <c r="D66" s="197"/>
+      <c r="E66" s="197"/>
+      <c r="F66" s="197"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="47"/>
-      <c r="I66" s="212"/>
-      <c r="J66" s="212"/>
-      <c r="K66" s="212"/>
-      <c r="L66" s="212"/>
-      <c r="M66" s="212"/>
+      <c r="I66" s="197"/>
+      <c r="J66" s="197"/>
+      <c r="K66" s="197"/>
+      <c r="L66" s="197"/>
+      <c r="M66" s="197"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="46"/>
       <c r="B67" s="46"/>
       <c r="C67" s="46"/>
-      <c r="D67" s="212"/>
-      <c r="E67" s="212"/>
-      <c r="F67" s="212"/>
-      <c r="G67" s="212"/>
+      <c r="D67" s="197"/>
+      <c r="E67" s="197"/>
+      <c r="F67" s="197"/>
+      <c r="G67" s="197"/>
       <c r="H67" s="47"/>
-      <c r="I67" s="212"/>
-      <c r="J67" s="212"/>
-      <c r="K67" s="212"/>
-      <c r="L67" s="212"/>
-      <c r="M67" s="212"/>
+      <c r="I67" s="197"/>
+      <c r="J67" s="197"/>
+      <c r="K67" s="197"/>
+      <c r="L67" s="197"/>
+      <c r="M67" s="197"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="46"/>
       <c r="B68" s="46"/>
       <c r="C68" s="46"/>
-      <c r="D68" s="212"/>
-      <c r="E68" s="212"/>
-      <c r="F68" s="212"/>
-      <c r="G68" s="212"/>
+      <c r="D68" s="197"/>
+      <c r="E68" s="197"/>
+      <c r="F68" s="197"/>
+      <c r="G68" s="197"/>
       <c r="H68" s="47"/>
-      <c r="I68" s="212"/>
-      <c r="J68" s="212"/>
-      <c r="K68" s="212"/>
-      <c r="L68" s="212"/>
-      <c r="M68" s="212"/>
+      <c r="I68" s="197"/>
+      <c r="J68" s="197"/>
+      <c r="K68" s="197"/>
+      <c r="L68" s="197"/>
+      <c r="M68" s="197"/>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="36"/>
@@ -26852,21 +26980,21 @@
       <c r="M70" s="36"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="213" t="s">
+      <c r="A71" s="198" t="s">
         <v>113</v>
       </c>
-      <c r="B71" s="213"/>
-      <c r="C71" s="213"/>
-      <c r="D71" s="213"/>
-      <c r="E71" s="213"/>
-      <c r="F71" s="213"/>
-      <c r="G71" s="213"/>
-      <c r="H71" s="213"/>
-      <c r="I71" s="213"/>
-      <c r="J71" s="213"/>
-      <c r="K71" s="213"/>
-      <c r="L71" s="213"/>
-      <c r="M71" s="213"/>
+      <c r="B71" s="198"/>
+      <c r="C71" s="198"/>
+      <c r="D71" s="198"/>
+      <c r="E71" s="198"/>
+      <c r="F71" s="198"/>
+      <c r="G71" s="198"/>
+      <c r="H71" s="198"/>
+      <c r="I71" s="198"/>
+      <c r="J71" s="198"/>
+      <c r="K71" s="198"/>
+      <c r="L71" s="198"/>
+      <c r="M71" s="198"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="52"/>
@@ -26914,46 +27042,46 @@
       <c r="M74" s="36"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="215" t="s">
+      <c r="A75" s="200" t="s">
         <v>114</v>
       </c>
-      <c r="B75" s="215"/>
-      <c r="C75" s="215"/>
-      <c r="D75" s="215"/>
-      <c r="E75" s="215"/>
-      <c r="F75" s="216" t="s">
+      <c r="B75" s="200"/>
+      <c r="C75" s="200"/>
+      <c r="D75" s="200"/>
+      <c r="E75" s="200"/>
+      <c r="F75" s="201" t="s">
         <v>115</v>
       </c>
-      <c r="G75" s="216"/>
-      <c r="H75" s="216"/>
-      <c r="I75" s="216"/>
-      <c r="J75" s="216"/>
-      <c r="K75" s="216" t="s">
+      <c r="G75" s="201"/>
+      <c r="H75" s="201"/>
+      <c r="I75" s="201"/>
+      <c r="J75" s="201"/>
+      <c r="K75" s="201" t="s">
         <v>116</v>
       </c>
-      <c r="L75" s="216"/>
-      <c r="M75" s="216"/>
+      <c r="L75" s="201"/>
+      <c r="M75" s="201"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="214" t="s">
+      <c r="A76" s="199" t="s">
         <v>117</v>
       </c>
-      <c r="B76" s="214"/>
-      <c r="C76" s="214"/>
-      <c r="D76" s="214"/>
-      <c r="E76" s="214"/>
-      <c r="F76" s="214" t="s">
+      <c r="B76" s="199"/>
+      <c r="C76" s="199"/>
+      <c r="D76" s="199"/>
+      <c r="E76" s="199"/>
+      <c r="F76" s="199" t="s">
         <v>118</v>
       </c>
-      <c r="G76" s="214"/>
-      <c r="H76" s="214"/>
-      <c r="I76" s="214"/>
-      <c r="J76" s="214"/>
-      <c r="K76" s="214" t="s">
+      <c r="G76" s="199"/>
+      <c r="H76" s="199"/>
+      <c r="I76" s="199"/>
+      <c r="J76" s="199"/>
+      <c r="K76" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="L76" s="214"/>
-      <c r="M76" s="214"/>
+      <c r="L76" s="199"/>
+      <c r="M76" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="76">
